--- a/src/main/resources/doc/PONKIDS-테이블정의서_v4.5.xlsx
+++ b/src/main/resources/doc/PONKIDS-테이블정의서_v4.5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10212"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\jjeovi\ponkids\eclipse\workspace\ponkids\src\main\resources\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jjeoV/Desktop/jjeoV/2023/pioneerKids/workspace/ponkidsDev/ponkids/src/main/resources/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D8F67A-66E0-4A76-9E6C-D8B04309E7BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07EE9B8-4CAD-C04B-8869-041F905B6BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="15360" windowHeight="7155" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1000" windowWidth="34200" windowHeight="21100" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="테이블정의서" sheetId="26" r:id="rId1"/>
@@ -25,6 +25,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'테이블 목록'!$D$163:$D$504</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">테이블정의서!$B$4:$Y$495</definedName>
+    <definedName name="ㄴ" localSheetId="0">#REF!</definedName>
+    <definedName name="ㄴ">#REF!</definedName>
+    <definedName name="버전" localSheetId="0">#REF!</definedName>
+    <definedName name="버전">#REF!</definedName>
+    <definedName name="사업명">[2]표지!$B$43</definedName>
     <definedName name="baseline" localSheetId="0">'[1]2.일정추적'!#REF!</definedName>
     <definedName name="baseline">'[1]2.일정추적'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'테이블 목록'!$A$1:$F$18</definedName>
@@ -34,13 +39,18 @@
     <definedName name="T01_컬럼정보_Query" localSheetId="0">#REF!</definedName>
     <definedName name="T01_컬럼정보_Query">#REF!</definedName>
     <definedName name="tol">'[1]4.1공수분석_개발'!$J$6</definedName>
-    <definedName name="ㄴ" localSheetId="0">#REF!</definedName>
-    <definedName name="ㄴ">#REF!</definedName>
-    <definedName name="버전" localSheetId="0">#REF!</definedName>
-    <definedName name="버전">#REF!</definedName>
-    <definedName name="사업명">[2]표지!$B$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -3563,16 +3573,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="10">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\$#,##0.00_);&quot;₩&quot;&quot;₩&quot;\(&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\$#,##0.00&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\)"/>
-    <numFmt numFmtId="180" formatCode="_-* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="181" formatCode="&quot;₩&quot;#,##0;[Red]&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;#,##0"/>
-    <numFmt numFmtId="182" formatCode="_-&quot;₩&quot;* #,##0_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="183" formatCode="&quot;₩&quot;#,##0.00;[Red]&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;#,##0.00"/>
-    <numFmt numFmtId="184" formatCode="0_ "/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\$#,##0.00_);&quot;₩&quot;&quot;₩&quot;\(&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\$#,##0.00&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\)"/>
+    <numFmt numFmtId="181" formatCode="_-* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="182" formatCode="&quot;₩&quot;#,##0;[Red]&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;#,##0"/>
+    <numFmt numFmtId="183" formatCode="_-&quot;₩&quot;* #,##0_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="184" formatCode="&quot;₩&quot;#,##0.00;[Red]&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;#,##0.00"/>
+    <numFmt numFmtId="185" formatCode="0_ "/>
   </numFmts>
   <fonts count="42">
     <font>
@@ -4188,17 +4198,17 @@
   <cellStyleXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="184" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="183" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="182" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment horizontal="left"/>
@@ -4212,7 +4222,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="10" fontId="7" fillId="2" borderId="3" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="181" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
@@ -4221,10 +4231,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4235,61 +4245,61 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -4488,7 +4498,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="21" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="21" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4527,7 +4537,7 @@
     <xf numFmtId="0" fontId="28" fillId="6" borderId="14" xfId="88" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="28" fillId="6" borderId="14" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="28" fillId="6" borderId="14" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="6" borderId="14" xfId="88" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4863,10 +4873,10 @@
     <xf numFmtId="0" fontId="28" fillId="5" borderId="15" xfId="88" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="28" fillId="5" borderId="15" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="28" fillId="5" borderId="15" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="184" fontId="28" fillId="5" borderId="15" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="28" fillId="5" borderId="15" xfId="88" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="88" applyFont="1" applyAlignment="1">
@@ -4895,29 +4905,6 @@
     </xf>
   </cellXfs>
   <cellStyles count="100">
-    <cellStyle name="AeE­ [0]_PERSONAL" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="AeE­_PERSONAL" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="ALIGNMENT" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="C￥AØ_PERSONAL" xfId="7" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="category" xfId="8" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Comma [0] 2" xfId="26" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Comma [0]_MACRO1.XLM" xfId="9" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="comma zerodec" xfId="10" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Currency1" xfId="11" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Dollar (zero dec)" xfId="12" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Grey" xfId="13" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="HEADER" xfId="14" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Header1" xfId="15" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Header2" xfId="16" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Hyperlink_NEGS" xfId="17" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Input [yellow]" xfId="18" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Model" xfId="19" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Normal - Style1" xfId="20" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="Normal 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="Normal_#26-PSS Rev and Drivers " xfId="33" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="Percent [2]" xfId="21" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="Percent 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="subhead" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
     <cellStyle name="백분율 2" xfId="28" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
     <cellStyle name="백분율 3" xfId="32" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
     <cellStyle name="쉼표 [0] 10" xfId="34" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
@@ -4995,6 +4982,29 @@
     <cellStyle name="표준 8" xfId="86" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
     <cellStyle name="표준 9" xfId="87" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
     <cellStyle name="하이퍼링크" xfId="93" builtinId="8"/>
+    <cellStyle name="AeE­ [0]_PERSONAL" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="AeE­_PERSONAL" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="ALIGNMENT" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="C￥AØ_PERSONAL" xfId="7" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="category" xfId="8" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Comma [0] 2" xfId="26" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Comma [0]_MACRO1.XLM" xfId="9" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="comma zerodec" xfId="10" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Currency1" xfId="11" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Dollar (zero dec)" xfId="12" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Grey" xfId="13" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="HEADER" xfId="14" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Header1" xfId="15" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Header2" xfId="16" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Hyperlink_NEGS" xfId="17" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Input [yellow]" xfId="18" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Model" xfId="19" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Normal - Style1" xfId="20" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Normal 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Normal_#26-PSS Rev and Drivers " xfId="33" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Percent [2]" xfId="21" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Percent 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="subhead" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5015,7 +5025,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="2.일정추적"/>
@@ -5032,7 +5042,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="표지"/>
@@ -5393,45 +5403,45 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:AJ546"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="16.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="2.77734375" style="124" customWidth="1"/>
-    <col min="2" max="2" width="6.77734375" style="84" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" style="124" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" style="84" customWidth="1"/>
     <col min="3" max="3" width="9" style="84" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" style="84" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="84" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" style="88" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.6640625" style="88" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.6640625" style="89" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.44140625" style="88" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.77734375" style="88" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.77734375" style="84" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.44140625" style="84" customWidth="1"/>
-    <col min="12" max="12" width="6.44140625" style="84" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5" style="88" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.83203125" style="88" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" style="84" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5" style="84" customWidth="1"/>
+    <col min="12" max="12" width="6.5" style="84" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20.33203125" style="84" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.77734375" style="84" customWidth="1"/>
-    <col min="15" max="16" width="18.44140625" style="84" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.44140625" style="88" customWidth="1"/>
-    <col min="18" max="18" width="7.77734375" style="89" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.83203125" style="84" customWidth="1"/>
+    <col min="15" max="16" width="18.5" style="84" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.5" style="88" customWidth="1"/>
+    <col min="18" max="18" width="7.83203125" style="89" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18.6640625" style="84" customWidth="1"/>
     <col min="20" max="20" width="24.33203125" style="88" customWidth="1"/>
     <col min="21" max="21" width="29.6640625" style="124" customWidth="1"/>
-    <col min="22" max="22" width="23.44140625" style="124" customWidth="1"/>
-    <col min="23" max="23" width="91.77734375" style="88" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.44140625" style="84" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.5" style="124" customWidth="1"/>
+    <col min="23" max="23" width="91.83203125" style="88" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.5" style="84" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="18.33203125" style="124" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="68.109375" style="124" customWidth="1"/>
-    <col min="27" max="27" width="40.77734375" style="124" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="68.1640625" style="124" customWidth="1"/>
+    <col min="27" max="27" width="40.83203125" style="124" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="159.6640625" style="124" customWidth="1"/>
-    <col min="29" max="29" width="41.44140625" style="124" customWidth="1"/>
-    <col min="30" max="30" width="83.109375" style="124" customWidth="1"/>
+    <col min="29" max="29" width="41.5" style="124" customWidth="1"/>
+    <col min="30" max="30" width="83.1640625" style="124" customWidth="1"/>
     <col min="31" max="31" width="80.6640625" style="124" customWidth="1"/>
-    <col min="32" max="32" width="86.44140625" style="124" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="86.5" style="124" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="80.6640625" style="124" bestFit="1" customWidth="1"/>
     <col min="34" max="35" width="80.6640625" style="124" customWidth="1"/>
-    <col min="36" max="16384" width="8.77734375" style="124"/>
+    <col min="36" max="16384" width="8.83203125" style="124"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:36" s="41" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="1" spans="2:36" s="41" customFormat="1" ht="20" customHeight="1" thickBot="1">
       <c r="B1" s="29" t="s">
         <v>54</v>
       </c>
@@ -5487,7 +5497,7 @@
       <c r="W2" s="42"/>
       <c r="X2" s="40"/>
     </row>
-    <row r="3" spans="2:36" s="41" customFormat="1" ht="24.95" customHeight="1">
+    <row r="3" spans="2:36" s="41" customFormat="1" ht="25" customHeight="1">
       <c r="B3" s="154"/>
       <c r="C3" s="155"/>
       <c r="D3" s="155"/>
@@ -5543,7 +5553,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="4" spans="2:36" s="41" customFormat="1" ht="27" thickBot="1">
+    <row r="4" spans="2:36" s="41" customFormat="1" ht="33" thickBot="1">
       <c r="B4" s="146" t="s">
         <v>6</v>
       </c>
@@ -5648,7 +5658,7 @@
       </c>
       <c r="AJ4" s="149"/>
     </row>
-    <row r="5" spans="2:36" s="50" customFormat="1" ht="20.100000000000001" customHeight="1" thickTop="1">
+    <row r="5" spans="2:36" s="50" customFormat="1" ht="20" customHeight="1" thickTop="1">
       <c r="B5" s="135">
         <v>1</v>
       </c>
@@ -5741,7 +5751,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN USER_SN;</v>
       </c>
     </row>
-    <row r="6" spans="2:36" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="2:36" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B6" s="55">
         <v>2</v>
       </c>
@@ -5833,7 +5843,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN USER_ID;</v>
       </c>
     </row>
-    <row r="7" spans="2:36" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="7" spans="2:36" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B7" s="55">
         <v>3</v>
       </c>
@@ -5925,7 +5935,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN PASSWORD;</v>
       </c>
     </row>
-    <row r="8" spans="2:36" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="8" spans="2:36" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B8" s="55">
         <v>4</v>
       </c>
@@ -6015,7 +6025,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN USER_NM;</v>
       </c>
     </row>
-    <row r="9" spans="2:36" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="9" spans="2:36" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B9" s="135">
         <v>5</v>
       </c>
@@ -6107,7 +6117,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN GENDER;</v>
       </c>
     </row>
-    <row r="10" spans="2:36" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="10" spans="2:36" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B10" s="55">
         <v>6</v>
       </c>
@@ -6197,7 +6207,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN BRDT_DATE;</v>
       </c>
     </row>
-    <row r="11" spans="2:36" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="11" spans="2:36" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B11" s="55">
         <v>7</v>
       </c>
@@ -6287,7 +6297,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN TEL_NO;</v>
       </c>
     </row>
-    <row r="12" spans="2:36" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="12" spans="2:36" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B12" s="55">
         <v>8</v>
       </c>
@@ -6377,7 +6387,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN RESIDE_AREA;</v>
       </c>
     </row>
-    <row r="13" spans="2:36" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="13" spans="2:36" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B13" s="135">
         <v>9</v>
       </c>
@@ -6465,7 +6475,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN ZIP;</v>
       </c>
     </row>
-    <row r="14" spans="2:36" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="14" spans="2:36" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B14" s="55">
         <v>10</v>
       </c>
@@ -6553,7 +6563,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN RDNM_ADR;</v>
       </c>
     </row>
-    <row r="15" spans="2:36" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="15" spans="2:36" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B15" s="55">
         <v>11</v>
       </c>
@@ -6641,7 +6651,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN DETAIL_ADR;</v>
       </c>
     </row>
-    <row r="16" spans="2:36" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="16" spans="2:36" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B16" s="55">
         <v>12</v>
       </c>
@@ -6737,7 +6747,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN ATCH_FILE_SN;</v>
       </c>
     </row>
-    <row r="17" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="17" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B17" s="135">
         <v>13</v>
       </c>
@@ -6829,7 +6839,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN MNGR_YN;</v>
       </c>
     </row>
-    <row r="18" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="18" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B18" s="55">
         <v>14</v>
       </c>
@@ -6919,7 +6929,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN MNGR_CONFM_YN;</v>
       </c>
     </row>
-    <row r="19" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="19" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B19" s="55">
         <v>15</v>
       </c>
@@ -7009,7 +7019,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN CONFMER_ID;</v>
       </c>
     </row>
-    <row r="20" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="20" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B20" s="55">
         <v>16</v>
       </c>
@@ -7097,7 +7107,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN CONFMER_IP;</v>
       </c>
     </row>
-    <row r="21" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="21" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B21" s="135">
         <v>17</v>
       </c>
@@ -7183,7 +7193,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN CONFM_DT;</v>
       </c>
     </row>
-    <row r="22" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="22" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B22" s="55">
         <v>18</v>
       </c>
@@ -7271,7 +7281,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN SNS_KAKAO_CNTN_YN;</v>
       </c>
     </row>
-    <row r="23" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="23" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B23" s="55">
         <v>19</v>
       </c>
@@ -7357,7 +7367,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN SNS_KAKAO_CNTN_DT;</v>
       </c>
     </row>
-    <row r="24" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="24" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B24" s="55">
         <v>20</v>
       </c>
@@ -7445,7 +7455,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN SNS_GOOGLE_CNTN_YN;</v>
       </c>
     </row>
-    <row r="25" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="25" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B25" s="135">
         <v>21</v>
       </c>
@@ -7531,7 +7541,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN SNS_GOOGLE_CNTN_DT;</v>
       </c>
     </row>
-    <row r="26" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="26" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B26" s="55">
         <v>22</v>
       </c>
@@ -7619,7 +7629,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN SNS_NAVER_CNTN_YN;</v>
       </c>
     </row>
-    <row r="27" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="27" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B27" s="55">
         <v>23</v>
       </c>
@@ -7705,7 +7715,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN SNS_NAVER_CNTN_DT;</v>
       </c>
     </row>
-    <row r="28" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="28" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B28" s="55">
         <v>24</v>
       </c>
@@ -7793,7 +7803,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN SNS_FACEBOOK_CNTN_YN;</v>
       </c>
     </row>
-    <row r="29" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="29" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B29" s="135">
         <v>25</v>
       </c>
@@ -7879,7 +7889,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN SNS_FACEBOOK_CNTN_DT;</v>
       </c>
     </row>
-    <row r="30" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="30" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B30" s="55">
         <v>26</v>
       </c>
@@ -7967,7 +7977,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN SNS_APPLE_CNTN_YN;</v>
       </c>
     </row>
-    <row r="31" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="31" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B31" s="55">
         <v>27</v>
       </c>
@@ -8053,7 +8063,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN SNS_APPLE_CNTN_DT;</v>
       </c>
     </row>
-    <row r="32" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="32" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B32" s="55">
         <v>28</v>
       </c>
@@ -8139,7 +8149,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN LAST_LOGIN_DT;</v>
       </c>
     </row>
-    <row r="33" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="33" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B33" s="135">
         <v>29</v>
       </c>
@@ -8231,7 +8241,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="34" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="34" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B34" s="55">
         <v>30</v>
       </c>
@@ -8321,7 +8331,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="35" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="35" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B35" s="55">
         <v>31</v>
       </c>
@@ -8411,7 +8421,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="36" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="36" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B36" s="55">
         <v>32</v>
       </c>
@@ -8499,7 +8509,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="37" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="37" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B37" s="135">
         <v>33</v>
       </c>
@@ -8585,7 +8595,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="38" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="38" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B38" s="55">
         <v>34</v>
       </c>
@@ -8677,7 +8687,7 @@
         <v>ALTER TABLE TB_USER DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="39" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="39" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B39" s="55">
         <v>35</v>
       </c>
@@ -8770,7 +8780,7 @@
         <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN CHLDRN_SN;</v>
       </c>
     </row>
-    <row r="40" spans="2:35" s="50" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="40" spans="2:35" s="50" customFormat="1" ht="20" customHeight="1">
       <c r="B40" s="55">
         <v>36</v>
       </c>
@@ -8868,7 +8878,7 @@
         <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN USER_SN;</v>
       </c>
     </row>
-    <row r="41" spans="2:35" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="41" spans="2:35" s="41" customFormat="1" ht="20" customHeight="1">
       <c r="B41" s="135">
         <v>37</v>
       </c>
@@ -8956,7 +8966,7 @@
         <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN USER_CHLDRN_SEQ;</v>
       </c>
     </row>
-    <row r="42" spans="2:35" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="42" spans="2:35" s="41" customFormat="1" ht="20" customHeight="1">
       <c r="B42" s="55">
         <v>38</v>
       </c>
@@ -9046,7 +9056,7 @@
         <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN CHLDRN_NM;</v>
       </c>
     </row>
-    <row r="43" spans="2:35" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="43" spans="2:35" s="41" customFormat="1" ht="20" customHeight="1">
       <c r="B43" s="55">
         <v>39</v>
       </c>
@@ -9136,7 +9146,7 @@
         <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN CHLDRN_GENDER;</v>
       </c>
     </row>
-    <row r="44" spans="2:35" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="44" spans="2:35" s="41" customFormat="1" ht="20" customHeight="1">
       <c r="B44" s="55">
         <v>40</v>
       </c>
@@ -9226,7 +9236,7 @@
         <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN CHLDRN_BRDT_DATE;</v>
       </c>
     </row>
-    <row r="45" spans="2:35" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="45" spans="2:35" s="41" customFormat="1" ht="20" customHeight="1">
       <c r="B45" s="135">
         <v>41</v>
       </c>
@@ -9314,7 +9324,7 @@
         <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN CHLDRN_EMAIL;</v>
       </c>
     </row>
-    <row r="46" spans="2:35" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="46" spans="2:35" s="41" customFormat="1" ht="20" customHeight="1">
       <c r="B46" s="55">
         <v>42</v>
       </c>
@@ -9402,7 +9412,7 @@
         <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN CHLDRN_TEL_NO;</v>
       </c>
     </row>
-    <row r="47" spans="2:35" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="47" spans="2:35" s="41" customFormat="1" ht="20" customHeight="1">
       <c r="B47" s="55">
         <v>43</v>
       </c>
@@ -9498,7 +9508,7 @@
         <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN ATCH_FILE_SN;</v>
       </c>
     </row>
-    <row r="48" spans="2:35" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="48" spans="2:35" s="41" customFormat="1" ht="20" customHeight="1">
       <c r="B48" s="55">
         <v>44</v>
       </c>
@@ -9590,7 +9600,7 @@
         <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="49" spans="2:35" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="49" spans="2:35" s="41" customFormat="1" ht="20" customHeight="1">
       <c r="B49" s="135">
         <v>45</v>
       </c>
@@ -9680,7 +9690,7 @@
         <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="50" spans="2:35" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="50" spans="2:35" s="41" customFormat="1" ht="20" customHeight="1">
       <c r="B50" s="55">
         <v>46</v>
       </c>
@@ -9768,7 +9778,7 @@
         <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="51" spans="2:35" s="41" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="51" spans="2:35" s="41" customFormat="1" ht="20" customHeight="1">
       <c r="B51" s="55">
         <v>47</v>
       </c>
@@ -9858,7 +9868,7 @@
         <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="52" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="52" spans="2:35" ht="20" customHeight="1">
       <c r="B52" s="55">
         <v>48</v>
       </c>
@@ -9946,7 +9956,7 @@
         <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="53" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="53" spans="2:35" ht="20" customHeight="1">
       <c r="B53" s="135">
         <v>49</v>
       </c>
@@ -10032,7 +10042,7 @@
         <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="54" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="54" spans="2:35" ht="20" customHeight="1">
       <c r="B54" s="55">
         <v>50</v>
       </c>
@@ -10124,7 +10134,7 @@
         <v>ALTER TABLE TB_USER_CHLDRN DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="55" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="55" spans="2:35" ht="20" customHeight="1">
       <c r="B55" s="55">
         <v>51</v>
       </c>
@@ -10217,7 +10227,7 @@
         <v>ALTER TABLE TB_ROLE DROP COLUMN ROLE_SN;</v>
       </c>
     </row>
-    <row r="56" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="56" spans="2:35" ht="20" customHeight="1">
       <c r="B56" s="55">
         <v>52</v>
       </c>
@@ -10307,7 +10317,7 @@
         <v>ALTER TABLE TB_ROLE DROP COLUMN ROLE_NM;</v>
       </c>
     </row>
-    <row r="57" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="57" spans="2:35" ht="20" customHeight="1">
       <c r="B57" s="135">
         <v>53</v>
       </c>
@@ -10395,7 +10405,7 @@
         <v>ALTER TABLE TB_ROLE DROP COLUMN ROLE_DC;</v>
       </c>
     </row>
-    <row r="58" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="58" spans="2:35" ht="20" customHeight="1">
       <c r="B58" s="55">
         <v>54</v>
       </c>
@@ -10487,7 +10497,7 @@
         <v>ALTER TABLE TB_ROLE DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="59" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="59" spans="2:35" ht="20" customHeight="1">
       <c r="B59" s="55">
         <v>55</v>
       </c>
@@ -10577,7 +10587,7 @@
         <v>ALTER TABLE TB_ROLE DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="60" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="60" spans="2:35" ht="20" customHeight="1">
       <c r="B60" s="55">
         <v>56</v>
       </c>
@@ -10665,7 +10675,7 @@
         <v>ALTER TABLE TB_ROLE DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="61" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="61" spans="2:35" ht="20" customHeight="1">
       <c r="B61" s="135">
         <v>57</v>
       </c>
@@ -10755,7 +10765,7 @@
         <v>ALTER TABLE TB_ROLE DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="62" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="62" spans="2:35" ht="20" customHeight="1">
       <c r="B62" s="55">
         <v>58</v>
       </c>
@@ -10843,7 +10853,7 @@
         <v>ALTER TABLE TB_ROLE DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="63" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="63" spans="2:35" ht="20" customHeight="1">
       <c r="B63" s="55">
         <v>59</v>
       </c>
@@ -10929,7 +10939,7 @@
         <v>ALTER TABLE TB_ROLE DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="64" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="64" spans="2:35" ht="20" customHeight="1">
       <c r="B64" s="55">
         <v>60</v>
       </c>
@@ -11021,7 +11031,7 @@
         <v>ALTER TABLE TB_ROLE DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="65" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="65" spans="2:35" ht="20" customHeight="1">
       <c r="B65" s="135">
         <v>61</v>
       </c>
@@ -11114,7 +11124,7 @@
         <v>ALTER TABLE TB_USER_ROLE DROP COLUMN USER_ROLE_SN;</v>
       </c>
     </row>
-    <row r="66" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="66" spans="2:35" ht="20" customHeight="1">
       <c r="B66" s="55">
         <v>62</v>
       </c>
@@ -11212,7 +11222,7 @@
         <v>ALTER TABLE TB_USER_ROLE DROP COLUMN USER_SN;</v>
       </c>
     </row>
-    <row r="67" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="67" spans="2:35" ht="20" customHeight="1">
       <c r="B67" s="55">
         <v>63</v>
       </c>
@@ -11310,7 +11320,7 @@
         <v>ALTER TABLE TB_USER_ROLE DROP COLUMN ROLE_SN;</v>
       </c>
     </row>
-    <row r="68" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="68" spans="2:35" ht="20" customHeight="1">
       <c r="B68" s="55">
         <v>64</v>
       </c>
@@ -11402,7 +11412,7 @@
         <v>ALTER TABLE TB_USER_ROLE DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="69" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="69" spans="2:35" ht="20" customHeight="1">
       <c r="B69" s="135">
         <v>65</v>
       </c>
@@ -11492,7 +11502,7 @@
         <v>ALTER TABLE TB_USER_ROLE DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="70" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="70" spans="2:35" ht="20" customHeight="1">
       <c r="B70" s="55">
         <v>66</v>
       </c>
@@ -11580,7 +11590,7 @@
         <v>ALTER TABLE TB_USER_ROLE DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="71" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="71" spans="2:35" ht="20" customHeight="1">
       <c r="B71" s="55">
         <v>67</v>
       </c>
@@ -11670,7 +11680,7 @@
         <v>ALTER TABLE TB_USER_ROLE DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="72" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="72" spans="2:35" ht="20" customHeight="1">
       <c r="B72" s="55">
         <v>68</v>
       </c>
@@ -11758,7 +11768,7 @@
         <v>ALTER TABLE TB_USER_ROLE DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="73" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="73" spans="2:35" ht="20" customHeight="1">
       <c r="B73" s="135">
         <v>69</v>
       </c>
@@ -11844,7 +11854,7 @@
         <v>ALTER TABLE TB_USER_ROLE DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="74" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="74" spans="2:35" ht="20" customHeight="1">
       <c r="B74" s="55">
         <v>70</v>
       </c>
@@ -11936,7 +11946,7 @@
         <v>ALTER TABLE TB_USER_ROLE DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="75" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="75" spans="2:35" ht="20" customHeight="1">
       <c r="B75" s="55">
         <v>71</v>
       </c>
@@ -12029,7 +12039,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN CLASS_SN;</v>
       </c>
     </row>
-    <row r="76" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="76" spans="2:35" ht="20" customHeight="1">
       <c r="B76" s="55">
         <v>72</v>
       </c>
@@ -12117,7 +12127,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN CTGRY_SN;</v>
       </c>
     </row>
-    <row r="77" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="77" spans="2:35" ht="20" customHeight="1">
       <c r="B77" s="135">
         <v>73</v>
       </c>
@@ -12205,7 +12215,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN CRSE_SN;</v>
       </c>
     </row>
-    <row r="78" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="78" spans="2:35" ht="20" customHeight="1">
       <c r="B78" s="55">
         <v>74</v>
       </c>
@@ -12295,7 +12305,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN CLASS_SJ;</v>
       </c>
     </row>
-    <row r="79" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="79" spans="2:35" ht="20" customHeight="1">
       <c r="B79" s="55">
         <v>75</v>
       </c>
@@ -12383,7 +12393,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN CLASS_SUMRY;</v>
       </c>
     </row>
-    <row r="80" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="80" spans="2:35" ht="20" customHeight="1">
       <c r="B80" s="55">
         <v>76</v>
       </c>
@@ -12471,7 +12481,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN CLASS_DC;</v>
       </c>
     </row>
-    <row r="81" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="81" spans="2:35" ht="20" customHeight="1">
       <c r="B81" s="135">
         <v>77</v>
       </c>
@@ -12559,7 +12569,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN CLASS_AMT;</v>
       </c>
     </row>
-    <row r="82" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="82" spans="2:35" ht="20" customHeight="1">
       <c r="B82" s="55">
         <v>78</v>
       </c>
@@ -12649,7 +12659,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN CLASS_DSCNT_BFE_AMT;</v>
       </c>
     </row>
-    <row r="83" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="83" spans="2:35" ht="20" customHeight="1">
       <c r="B83" s="55">
         <v>79</v>
       </c>
@@ -12739,7 +12749,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN CLASS_TRGT_CD;</v>
       </c>
     </row>
-    <row r="84" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="84" spans="2:35" ht="20" customHeight="1">
       <c r="B84" s="55">
         <v>80</v>
       </c>
@@ -12829,7 +12839,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN CLASS_PD_SET_YN;</v>
       </c>
     </row>
-    <row r="85" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="85" spans="2:35" ht="20" customHeight="1">
       <c r="B85" s="135">
         <v>81</v>
       </c>
@@ -12917,7 +12927,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN CLASS_BEGIN_DT;</v>
       </c>
     </row>
-    <row r="86" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="86" spans="2:35" ht="20" customHeight="1">
       <c r="B86" s="55">
         <v>82</v>
       </c>
@@ -13005,7 +13015,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN CLASS_END_DT;</v>
       </c>
     </row>
-    <row r="87" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="87" spans="2:35" ht="20" customHeight="1">
       <c r="B87" s="55">
         <v>83</v>
       </c>
@@ -13101,7 +13111,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN THUMB_ATCH_FILE_SN;</v>
       </c>
     </row>
-    <row r="88" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="88" spans="2:35" ht="20" customHeight="1">
       <c r="B88" s="55">
         <v>84</v>
       </c>
@@ -13197,7 +13207,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN ATCH_FILE_SN;</v>
       </c>
     </row>
-    <row r="89" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="89" spans="2:35" ht="20" customHeight="1">
       <c r="B89" s="135">
         <v>85</v>
       </c>
@@ -13289,7 +13299,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN CLASS_EXPSR_YN;</v>
       </c>
     </row>
-    <row r="90" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="90" spans="2:35" ht="20" customHeight="1">
       <c r="B90" s="55">
         <v>86</v>
       </c>
@@ -13381,7 +13391,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="91" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="91" spans="2:35" ht="20" customHeight="1">
       <c r="B91" s="55">
         <v>87</v>
       </c>
@@ -13471,7 +13481,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="92" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="92" spans="2:35" ht="20" customHeight="1">
       <c r="B92" s="55">
         <v>88</v>
       </c>
@@ -13559,7 +13569,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="93" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="93" spans="2:35" ht="20" customHeight="1">
       <c r="B93" s="135">
         <v>89</v>
       </c>
@@ -13649,7 +13659,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="94" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="94" spans="2:35" ht="20" customHeight="1">
       <c r="B94" s="55">
         <v>90</v>
       </c>
@@ -13737,7 +13747,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="95" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="95" spans="2:35" ht="20" customHeight="1">
       <c r="B95" s="55">
         <v>91</v>
       </c>
@@ -13823,7 +13833,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="96" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="96" spans="2:35" ht="20" customHeight="1">
       <c r="B96" s="55">
         <v>92</v>
       </c>
@@ -13915,7 +13925,7 @@
         <v>ALTER TABLE TB_CLASS DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="97" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="97" spans="2:35" ht="20" customHeight="1">
       <c r="B97" s="135">
         <v>93</v>
       </c>
@@ -14008,7 +14018,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL01 DROP COLUMN CL_SN;</v>
       </c>
     </row>
-    <row r="98" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="98" spans="2:35" ht="20" customHeight="1">
       <c r="B98" s="55">
         <v>94</v>
       </c>
@@ -14098,7 +14108,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL01 DROP COLUMN CL_NM;</v>
       </c>
     </row>
-    <row r="99" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="99" spans="2:35" ht="20" customHeight="1">
       <c r="B99" s="55">
         <v>95</v>
       </c>
@@ -14186,7 +14196,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL01 DROP COLUMN CL_SEQ;</v>
       </c>
     </row>
-    <row r="100" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="100" spans="2:35" ht="20" customHeight="1">
       <c r="B100" s="55">
         <v>96</v>
       </c>
@@ -14278,7 +14288,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL01 DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="101" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="101" spans="2:35" ht="20" customHeight="1">
       <c r="B101" s="135">
         <v>97</v>
       </c>
@@ -14368,7 +14378,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL01 DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="102" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="102" spans="2:35" ht="20" customHeight="1">
       <c r="B102" s="55">
         <v>98</v>
       </c>
@@ -14456,7 +14466,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL01 DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="103" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="103" spans="2:35" ht="20" customHeight="1">
       <c r="B103" s="55">
         <v>99</v>
       </c>
@@ -14546,7 +14556,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL01 DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="104" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="104" spans="2:35" ht="20" customHeight="1">
       <c r="B104" s="55">
         <v>100</v>
       </c>
@@ -14634,7 +14644,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL01 DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="105" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="105" spans="2:35" ht="20" customHeight="1">
       <c r="B105" s="135">
         <v>101</v>
       </c>
@@ -14720,7 +14730,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL01 DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="106" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="106" spans="2:35" ht="20" customHeight="1">
       <c r="B106" s="55">
         <v>102</v>
       </c>
@@ -14812,7 +14822,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL01 DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="107" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="107" spans="2:35" ht="20" customHeight="1">
       <c r="B107" s="55">
         <v>103</v>
       </c>
@@ -14905,7 +14915,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL02 DROP COLUMN CL_SN;</v>
       </c>
     </row>
-    <row r="108" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="108" spans="2:35" ht="20" customHeight="1">
       <c r="B108" s="55">
         <v>104</v>
       </c>
@@ -15003,7 +15013,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL02 DROP COLUMN PARNTS_CL_SN;</v>
       </c>
     </row>
-    <row r="109" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="109" spans="2:35" ht="20" customHeight="1">
       <c r="B109" s="135">
         <v>105</v>
       </c>
@@ -15093,7 +15103,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL02 DROP COLUMN CL_NM;</v>
       </c>
     </row>
-    <row r="110" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="110" spans="2:35" ht="20" customHeight="1">
       <c r="B110" s="55">
         <v>106</v>
       </c>
@@ -15181,7 +15191,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL02 DROP COLUMN CL_SEQ;</v>
       </c>
     </row>
-    <row r="111" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="111" spans="2:35" ht="20" customHeight="1">
       <c r="B111" s="55">
         <v>107</v>
       </c>
@@ -15273,7 +15283,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL02 DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="112" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="112" spans="2:35" ht="20" customHeight="1">
       <c r="B112" s="55">
         <v>108</v>
       </c>
@@ -15363,7 +15373,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL02 DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="113" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="113" spans="2:35" ht="20" customHeight="1">
       <c r="B113" s="135">
         <v>109</v>
       </c>
@@ -15451,7 +15461,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL02 DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="114" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="114" spans="2:35" ht="20" customHeight="1">
       <c r="B114" s="55">
         <v>110</v>
       </c>
@@ -15541,7 +15551,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL02 DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="115" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="115" spans="2:35" ht="20" customHeight="1">
       <c r="B115" s="55">
         <v>111</v>
       </c>
@@ -15629,7 +15639,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL02 DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="116" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="116" spans="2:35" ht="20" customHeight="1">
       <c r="B116" s="55">
         <v>112</v>
       </c>
@@ -15715,7 +15725,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL02 DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="117" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="117" spans="2:35" ht="20" customHeight="1">
       <c r="B117" s="135">
         <v>113</v>
       </c>
@@ -15807,7 +15817,7 @@
         <v>ALTER TABLE TB_CLASS_CATEGORY_CL02 DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="118" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="118" spans="2:35" ht="20" customHeight="1">
       <c r="B118" s="55">
         <v>114</v>
       </c>
@@ -15900,7 +15910,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL DROP COLUMN CLASS_DETAIL_SN;</v>
       </c>
     </row>
-    <row r="119" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="119" spans="2:35" ht="20" customHeight="1">
       <c r="B119" s="55">
         <v>115</v>
       </c>
@@ -15998,7 +16008,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL DROP COLUMN CLASS_SN;</v>
       </c>
     </row>
-    <row r="120" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="120" spans="2:35" ht="20" customHeight="1">
       <c r="B120" s="55">
         <v>116</v>
       </c>
@@ -16086,7 +16096,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL DROP COLUMN CLASS_DETAIL_SEQ;</v>
       </c>
     </row>
-    <row r="121" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="121" spans="2:35" ht="20" customHeight="1">
       <c r="B121" s="135">
         <v>117</v>
       </c>
@@ -16180,7 +16190,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL DROP COLUMN CLASS_DETAIL_ITEM_TY_CD;</v>
       </c>
     </row>
-    <row r="122" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="122" spans="2:35" ht="20" customHeight="1">
       <c r="B122" s="55">
         <v>118</v>
       </c>
@@ -16268,7 +16278,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL DROP COLUMN CLASS_DETAIL_ITEM_CN;</v>
       </c>
     </row>
-    <row r="123" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="123" spans="2:35" ht="20" customHeight="1">
       <c r="B123" s="55">
         <v>119</v>
       </c>
@@ -16360,7 +16370,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL DROP COLUMN CLASS_DETAIL_ESSNTL_YN;</v>
       </c>
     </row>
-    <row r="124" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="124" spans="2:35" ht="20" customHeight="1">
       <c r="B124" s="55">
         <v>120</v>
       </c>
@@ -16452,7 +16462,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="125" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="125" spans="2:35" ht="20" customHeight="1">
       <c r="B125" s="135">
         <v>121</v>
       </c>
@@ -16542,7 +16552,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="126" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="126" spans="2:35" ht="20" customHeight="1">
       <c r="B126" s="55">
         <v>122</v>
       </c>
@@ -16630,7 +16640,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="127" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="127" spans="2:35" ht="20" customHeight="1">
       <c r="B127" s="55">
         <v>123</v>
       </c>
@@ -16720,7 +16730,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="128" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="128" spans="2:35" ht="20" customHeight="1">
       <c r="B128" s="55">
         <v>124</v>
       </c>
@@ -16808,7 +16818,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="129" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="129" spans="2:35" ht="20" customHeight="1">
       <c r="B129" s="135">
         <v>125</v>
       </c>
@@ -16894,7 +16904,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="130" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="130" spans="2:35" ht="20" customHeight="1">
       <c r="B130" s="55">
         <v>126</v>
       </c>
@@ -16986,7 +16996,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="131" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="131" spans="2:35" ht="20" customHeight="1">
       <c r="B131" s="55">
         <v>127</v>
       </c>
@@ -17081,7 +17091,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL_OPTN DROP COLUMN CLASS_DETAIL_OPTN_SN;</v>
       </c>
     </row>
-    <row r="132" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="132" spans="2:35" ht="20" customHeight="1">
       <c r="B132" s="55">
         <v>128</v>
       </c>
@@ -17179,7 +17189,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL_OPTN DROP COLUMN CLASS_DETAIL_SN;</v>
       </c>
     </row>
-    <row r="133" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="133" spans="2:35" ht="20" customHeight="1">
       <c r="B133" s="135">
         <v>129</v>
       </c>
@@ -17265,7 +17275,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL_OPTN DROP COLUMN CLASS_DETAIL_OPTN_SEQ;</v>
       </c>
     </row>
-    <row r="134" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="134" spans="2:35" ht="20" customHeight="1">
       <c r="B134" s="55">
         <v>130</v>
       </c>
@@ -17353,7 +17363,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL_OPTN DROP COLUMN CLASS_DETAIL_OPTN_CN;</v>
       </c>
     </row>
-    <row r="135" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="135" spans="2:35" ht="20" customHeight="1">
       <c r="B135" s="55">
         <v>131</v>
       </c>
@@ -17445,7 +17455,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL_OPTN DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="136" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="136" spans="2:35" ht="20" customHeight="1">
       <c r="B136" s="55">
         <v>132</v>
       </c>
@@ -17535,7 +17545,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL_OPTN DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="137" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="137" spans="2:35" ht="20" customHeight="1">
       <c r="B137" s="135">
         <v>133</v>
       </c>
@@ -17623,7 +17633,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL_OPTN DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="138" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="138" spans="2:35" ht="20" customHeight="1">
       <c r="B138" s="55">
         <v>134</v>
       </c>
@@ -17713,7 +17723,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL_OPTN DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="139" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="139" spans="2:35" ht="20" customHeight="1">
       <c r="B139" s="55">
         <v>135</v>
       </c>
@@ -17801,7 +17811,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL_OPTN DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="140" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="140" spans="2:35" ht="20" customHeight="1">
       <c r="B140" s="55">
         <v>136</v>
       </c>
@@ -17887,7 +17897,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL_OPTN DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="141" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="141" spans="2:35" ht="20" customHeight="1">
       <c r="B141" s="135">
         <v>137</v>
       </c>
@@ -17979,7 +17989,7 @@
         <v>ALTER TABLE TB_CLASS_DETAIL_OPTN DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="142" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="142" spans="2:35" ht="20" customHeight="1">
       <c r="B142" s="55">
         <v>138</v>
       </c>
@@ -18072,7 +18082,7 @@
         <v>ALTER TABLE TB_CLASS_WEEK DROP COLUMN CLASS_WEEK_SN;</v>
       </c>
     </row>
-    <row r="143" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="143" spans="2:35" ht="20" customHeight="1">
       <c r="B143" s="55">
         <v>139</v>
       </c>
@@ -18170,7 +18180,7 @@
         <v>ALTER TABLE TB_CLASS_WEEK DROP COLUMN CLASS_SN;</v>
       </c>
     </row>
-    <row r="144" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="144" spans="2:35" ht="20" customHeight="1">
       <c r="B144" s="55">
         <v>140</v>
       </c>
@@ -18260,7 +18270,7 @@
         <v>ALTER TABLE TB_CLASS_WEEK DROP COLUMN CLASS_DAY_CD;</v>
       </c>
     </row>
-    <row r="145" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="145" spans="2:35" ht="20" customHeight="1">
       <c r="B145" s="135">
         <v>141</v>
       </c>
@@ -18352,7 +18362,7 @@
         <v>ALTER TABLE TB_CLASS_WEEK DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="146" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="146" spans="2:35" ht="20" customHeight="1">
       <c r="B146" s="55">
         <v>142</v>
       </c>
@@ -18442,7 +18452,7 @@
         <v>ALTER TABLE TB_CLASS_WEEK DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="147" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="147" spans="2:35" ht="20" customHeight="1">
       <c r="B147" s="55">
         <v>143</v>
       </c>
@@ -18530,7 +18540,7 @@
         <v>ALTER TABLE TB_CLASS_WEEK DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="148" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="148" spans="2:35" ht="20" customHeight="1">
       <c r="B148" s="55">
         <v>144</v>
       </c>
@@ -18620,7 +18630,7 @@
         <v>ALTER TABLE TB_CLASS_WEEK DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="149" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="149" spans="2:35" ht="20" customHeight="1">
       <c r="B149" s="135">
         <v>145</v>
       </c>
@@ -18708,7 +18718,7 @@
         <v>ALTER TABLE TB_CLASS_WEEK DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="150" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="150" spans="2:35" ht="20" customHeight="1">
       <c r="B150" s="55">
         <v>146</v>
       </c>
@@ -18794,7 +18804,7 @@
         <v>ALTER TABLE TB_CLASS_WEEK DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="151" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="151" spans="2:35" ht="20" customHeight="1">
       <c r="B151" s="55">
         <v>147</v>
       </c>
@@ -18886,7 +18896,7 @@
         <v>ALTER TABLE TB_CLASS_WEEK DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="152" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="152" spans="2:35" ht="20" customHeight="1">
       <c r="B152" s="55">
         <v>148</v>
       </c>
@@ -18979,7 +18989,7 @@
         <v>ALTER TABLE TB_CLASS_LIKE DROP COLUMN CLASS_LIKE_SN;</v>
       </c>
     </row>
-    <row r="153" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="153" spans="2:35" ht="20" customHeight="1">
       <c r="B153" s="135">
         <v>149</v>
       </c>
@@ -19077,7 +19087,7 @@
         <v>ALTER TABLE TB_CLASS_LIKE DROP COLUMN CLASS_SN;</v>
       </c>
     </row>
-    <row r="154" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="154" spans="2:35" ht="20" customHeight="1">
       <c r="B154" s="55">
         <v>150</v>
       </c>
@@ -19175,7 +19185,7 @@
         <v>ALTER TABLE TB_CLASS_LIKE DROP COLUMN USER_SN;</v>
       </c>
     </row>
-    <row r="155" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="155" spans="2:35" ht="20" customHeight="1">
       <c r="B155" s="55">
         <v>151</v>
       </c>
@@ -19267,7 +19277,7 @@
         <v>ALTER TABLE TB_CLASS_LIKE DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="156" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="156" spans="2:35" ht="20" customHeight="1">
       <c r="B156" s="55">
         <v>152</v>
       </c>
@@ -19357,7 +19367,7 @@
         <v>ALTER TABLE TB_CLASS_LIKE DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="157" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="157" spans="2:35" ht="20" customHeight="1">
       <c r="B157" s="135">
         <v>153</v>
       </c>
@@ -19445,7 +19455,7 @@
         <v>ALTER TABLE TB_CLASS_LIKE DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="158" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="158" spans="2:35" ht="20" customHeight="1">
       <c r="B158" s="55">
         <v>154</v>
       </c>
@@ -19535,7 +19545,7 @@
         <v>ALTER TABLE TB_CLASS_LIKE DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="159" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="159" spans="2:35" ht="20" customHeight="1">
       <c r="B159" s="55">
         <v>155</v>
       </c>
@@ -19623,7 +19633,7 @@
         <v>ALTER TABLE TB_CLASS_LIKE DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="160" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="160" spans="2:35" ht="20" customHeight="1">
       <c r="B160" s="55">
         <v>156</v>
       </c>
@@ -19709,7 +19719,7 @@
         <v>ALTER TABLE TB_CLASS_LIKE DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="161" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="161" spans="2:35" ht="20" customHeight="1">
       <c r="B161" s="135">
         <v>157</v>
       </c>
@@ -19801,7 +19811,7 @@
         <v>ALTER TABLE TB_CLASS_LIKE DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="162" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="162" spans="2:35" ht="20" customHeight="1">
       <c r="B162" s="55">
         <v>158</v>
       </c>
@@ -19894,7 +19904,7 @@
         <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN CLASS_REVIEW_SN;</v>
       </c>
     </row>
-    <row r="163" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="163" spans="2:35" ht="20" customHeight="1">
       <c r="B163" s="55">
         <v>159</v>
       </c>
@@ -19992,7 +20002,7 @@
         <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN CLASS_SN;</v>
       </c>
     </row>
-    <row r="164" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="164" spans="2:35" ht="20" customHeight="1">
       <c r="B164" s="55">
         <v>160</v>
       </c>
@@ -20090,7 +20100,7 @@
         <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN USER_SN;</v>
       </c>
     </row>
-    <row r="165" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="165" spans="2:35" ht="20" customHeight="1">
       <c r="B165" s="135">
         <v>161</v>
       </c>
@@ -20180,7 +20190,7 @@
         <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN STEP;</v>
       </c>
     </row>
-    <row r="166" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="166" spans="2:35" ht="20" customHeight="1">
       <c r="B166" s="55">
         <v>162</v>
       </c>
@@ -20268,7 +20278,7 @@
         <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN PARNTS_REVIEW_SN;</v>
       </c>
     </row>
-    <row r="167" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="167" spans="2:35" ht="20" customHeight="1">
       <c r="B167" s="55">
         <v>163</v>
       </c>
@@ -20358,7 +20368,7 @@
         <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN REVIEW_CN;</v>
       </c>
     </row>
-    <row r="168" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="168" spans="2:35" ht="20" customHeight="1">
       <c r="B168" s="55">
         <v>164</v>
       </c>
@@ -20448,7 +20458,7 @@
         <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN REVIEW_GRADE;</v>
       </c>
     </row>
-    <row r="169" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="169" spans="2:35" ht="20" customHeight="1">
       <c r="B169" s="135">
         <v>165</v>
       </c>
@@ -20544,7 +20554,7 @@
         <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN ATCH_FILE_SN;</v>
       </c>
     </row>
-    <row r="170" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="170" spans="2:35" ht="20" customHeight="1">
       <c r="B170" s="135">
         <v>165</v>
       </c>
@@ -20561,7 +20571,7 @@
         <v>12</v>
       </c>
       <c r="G170" s="92">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H170" s="101" t="s">
         <v>328</v>
@@ -20634,7 +20644,7 @@
         <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN OPEN_YN;</v>
       </c>
     </row>
-    <row r="171" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="171" spans="2:35" ht="20" customHeight="1">
       <c r="B171" s="55">
         <v>166</v>
       </c>
@@ -20651,7 +20661,7 @@
         <v>12</v>
       </c>
       <c r="G171" s="92">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H171" s="97" t="s">
         <v>107</v>
@@ -20726,7 +20736,7 @@
         <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="172" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="172" spans="2:35" ht="20" customHeight="1">
       <c r="B172" s="55">
         <v>167</v>
       </c>
@@ -20743,7 +20753,7 @@
         <v>12</v>
       </c>
       <c r="G172" s="92">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H172" s="97" t="s">
         <v>91</v>
@@ -20816,7 +20826,7 @@
         <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="173" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="173" spans="2:35" ht="20" customHeight="1">
       <c r="B173" s="55">
         <v>168</v>
       </c>
@@ -20833,7 +20843,7 @@
         <v>12</v>
       </c>
       <c r="G173" s="92">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H173" s="97" t="s">
         <v>92</v>
@@ -20904,7 +20914,7 @@
         <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="174" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="174" spans="2:35" ht="20" customHeight="1">
       <c r="B174" s="135">
         <v>169</v>
       </c>
@@ -20921,7 +20931,7 @@
         <v>12</v>
       </c>
       <c r="G174" s="92">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H174" s="97" t="s">
         <v>93</v>
@@ -20994,7 +21004,7 @@
         <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="175" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="175" spans="2:35" ht="20" customHeight="1">
       <c r="B175" s="55">
         <v>170</v>
       </c>
@@ -21011,7 +21021,7 @@
         <v>12</v>
       </c>
       <c r="G175" s="92">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H175" s="97" t="s">
         <v>94</v>
@@ -21082,7 +21092,7 @@
         <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="176" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="176" spans="2:35" ht="20" customHeight="1">
       <c r="B176" s="55">
         <v>171</v>
       </c>
@@ -21099,7 +21109,7 @@
         <v>12</v>
       </c>
       <c r="G176" s="92">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H176" s="98" t="s">
         <v>95</v>
@@ -21168,7 +21178,7 @@
         <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="177" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="177" spans="2:35" ht="20" customHeight="1">
       <c r="B177" s="55">
         <v>172</v>
       </c>
@@ -21185,7 +21195,7 @@
         <v>12</v>
       </c>
       <c r="G177" s="92">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H177" s="97" t="s">
         <v>96</v>
@@ -21260,7 +21270,7 @@
         <v>ALTER TABLE TB_CLASS_REVIEW DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="178" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="178" spans="2:35" ht="20" customHeight="1">
       <c r="B178" s="135">
         <v>173</v>
       </c>
@@ -21353,7 +21363,7 @@
         <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN CLASS_INQRY_SN;</v>
       </c>
     </row>
-    <row r="179" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="179" spans="2:35" ht="20" customHeight="1">
       <c r="B179" s="55">
         <v>174</v>
       </c>
@@ -21451,7 +21461,7 @@
         <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN CLASS_SN;</v>
       </c>
     </row>
-    <row r="180" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="180" spans="2:35" ht="20" customHeight="1">
       <c r="B180" s="55">
         <v>175</v>
       </c>
@@ -21541,7 +21551,7 @@
         <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN STEP;</v>
       </c>
     </row>
-    <row r="181" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="181" spans="2:35" ht="20" customHeight="1">
       <c r="B181" s="55">
         <v>176</v>
       </c>
@@ -21627,7 +21637,7 @@
         <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN PARNTS_INQRY_SN;</v>
       </c>
     </row>
-    <row r="182" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="182" spans="2:35" ht="20" customHeight="1">
       <c r="B182" s="135">
         <v>177</v>
       </c>
@@ -21725,7 +21735,7 @@
         <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN USER_SN;</v>
       </c>
     </row>
-    <row r="183" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="183" spans="2:35" ht="20" customHeight="1">
       <c r="B183" s="55">
         <v>178</v>
       </c>
@@ -21815,7 +21825,7 @@
         <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN INQRY_SJ;</v>
       </c>
     </row>
-    <row r="184" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="184" spans="2:35" ht="20" customHeight="1">
       <c r="B184" s="55">
         <v>179</v>
       </c>
@@ -21903,7 +21913,7 @@
         <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN INQRY_CN;</v>
       </c>
     </row>
-    <row r="185" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="185" spans="2:35" ht="20" customHeight="1">
       <c r="B185" s="55">
         <v>180</v>
       </c>
@@ -21993,7 +22003,7 @@
         <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN OPEN_YN;</v>
       </c>
     </row>
-    <row r="186" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="186" spans="2:35" ht="20" customHeight="1">
       <c r="B186" s="135">
         <v>181</v>
       </c>
@@ -22085,7 +22095,7 @@
         <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="187" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="187" spans="2:35" ht="20" customHeight="1">
       <c r="B187" s="55">
         <v>182</v>
       </c>
@@ -22175,7 +22185,7 @@
         <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="188" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="188" spans="2:35" ht="20" customHeight="1">
       <c r="B188" s="55">
         <v>183</v>
       </c>
@@ -22263,7 +22273,7 @@
         <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="189" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="189" spans="2:35" ht="20" customHeight="1">
       <c r="B189" s="55">
         <v>184</v>
       </c>
@@ -22353,7 +22363,7 @@
         <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="190" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="190" spans="2:35" ht="20" customHeight="1">
       <c r="B190" s="135">
         <v>185</v>
       </c>
@@ -22441,7 +22451,7 @@
         <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="191" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="191" spans="2:35" ht="20" customHeight="1">
       <c r="B191" s="55">
         <v>186</v>
       </c>
@@ -22527,7 +22537,7 @@
         <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="192" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="192" spans="2:35" ht="20" customHeight="1">
       <c r="B192" s="55">
         <v>187</v>
       </c>
@@ -22619,7 +22629,7 @@
         <v>ALTER TABLE TB_CLASS_INQRY DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="193" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="193" spans="2:35" ht="20" customHeight="1">
       <c r="B193" s="55">
         <v>188</v>
       </c>
@@ -22714,7 +22724,7 @@
         <v>ALTER TABLE TB_CLASS_REQST DROP COLUMN CLASS_REQST_SN;</v>
       </c>
     </row>
-    <row r="194" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="194" spans="2:35" ht="20" customHeight="1">
       <c r="B194" s="135">
         <v>189</v>
       </c>
@@ -22812,7 +22822,7 @@
         <v>ALTER TABLE TB_CLASS_REQST DROP COLUMN CLASS_SN;</v>
       </c>
     </row>
-    <row r="195" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="195" spans="2:35" ht="20" customHeight="1">
       <c r="B195" s="55">
         <v>190</v>
       </c>
@@ -22910,7 +22920,7 @@
         <v>ALTER TABLE TB_CLASS_REQST DROP COLUMN USER_SN;</v>
       </c>
     </row>
-    <row r="196" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="196" spans="2:35" ht="20" customHeight="1">
       <c r="B196" s="135">
         <v>189</v>
       </c>
@@ -22998,7 +23008,7 @@
         <v>ALTER TABLE TB_CLASS_REQST DROP COLUMN TOT_REQST_CNT;</v>
       </c>
     </row>
-    <row r="197" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="197" spans="2:35" ht="20" customHeight="1">
       <c r="B197" s="55">
         <v>190</v>
       </c>
@@ -23088,7 +23098,7 @@
         <v>ALTER TABLE TB_CLASS_REQST DROP COLUMN TOT_REQST_AMT;</v>
       </c>
     </row>
-    <row r="198" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="198" spans="2:35" ht="20" customHeight="1">
       <c r="B198" s="55">
         <v>191</v>
       </c>
@@ -23180,7 +23190,7 @@
         <v>ALTER TABLE TB_CLASS_REQST DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="199" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="199" spans="2:35" ht="20" customHeight="1">
       <c r="B199" s="55">
         <v>192</v>
       </c>
@@ -23270,7 +23280,7 @@
         <v>ALTER TABLE TB_CLASS_REQST DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="200" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="200" spans="2:35" ht="20" customHeight="1">
       <c r="B200" s="135">
         <v>193</v>
       </c>
@@ -23358,7 +23368,7 @@
         <v>ALTER TABLE TB_CLASS_REQST DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="201" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="201" spans="2:35" ht="20" customHeight="1">
       <c r="B201" s="55">
         <v>194</v>
       </c>
@@ -23448,7 +23458,7 @@
         <v>ALTER TABLE TB_CLASS_REQST DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="202" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="202" spans="2:35" ht="20" customHeight="1">
       <c r="B202" s="55">
         <v>195</v>
       </c>
@@ -23536,7 +23546,7 @@
         <v>ALTER TABLE TB_CLASS_REQST DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="203" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="203" spans="2:35" ht="20" customHeight="1">
       <c r="B203" s="55">
         <v>196</v>
       </c>
@@ -23622,7 +23632,7 @@
         <v>ALTER TABLE TB_CLASS_REQST DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="204" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="204" spans="2:35" ht="20" customHeight="1">
       <c r="B204" s="135">
         <v>197</v>
       </c>
@@ -23714,7 +23724,7 @@
         <v>ALTER TABLE TB_CLASS_REQST DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="205" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="205" spans="2:35" ht="20" customHeight="1">
       <c r="B205" s="55">
         <v>198</v>
       </c>
@@ -23807,7 +23817,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN LCTRE_SN;</v>
       </c>
     </row>
-    <row r="206" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="206" spans="2:35" ht="20" customHeight="1">
       <c r="B206" s="55">
         <v>199</v>
       </c>
@@ -23905,7 +23915,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN CLASS_SN;</v>
       </c>
     </row>
-    <row r="207" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="207" spans="2:35" ht="20" customHeight="1">
       <c r="B207" s="55">
         <v>200</v>
       </c>
@@ -23995,7 +24005,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN CLASS_DAY_CD;</v>
       </c>
     </row>
-    <row r="208" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="208" spans="2:35" ht="20" customHeight="1">
       <c r="B208" s="135">
         <v>201</v>
       </c>
@@ -24083,7 +24093,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN LCTRE_SEQ;</v>
       </c>
     </row>
-    <row r="209" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="209" spans="2:35" ht="20" customHeight="1">
       <c r="B209" s="55">
         <v>202</v>
       </c>
@@ -24171,7 +24181,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN LCTRE_SJ;</v>
       </c>
     </row>
-    <row r="210" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="210" spans="2:35" ht="20" customHeight="1">
       <c r="B210" s="55">
         <v>202</v>
       </c>
@@ -24259,7 +24269,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN LCTRE_DT;</v>
       </c>
     </row>
-    <row r="211" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="211" spans="2:35" ht="20" customHeight="1">
       <c r="B211" s="55">
         <v>203</v>
       </c>
@@ -24347,7 +24357,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN LCTRE_AMT;</v>
       </c>
     </row>
-    <row r="212" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="212" spans="2:35" ht="20" customHeight="1">
       <c r="B212" s="55">
         <v>204</v>
       </c>
@@ -24435,7 +24445,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN LCTRE_DC;</v>
       </c>
     </row>
-    <row r="213" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="213" spans="2:35" ht="20" customHeight="1">
       <c r="B213" s="135">
         <v>205</v>
       </c>
@@ -24523,7 +24533,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN LCTRE_APPLCNT_GUIDANCE;</v>
       </c>
     </row>
-    <row r="214" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="214" spans="2:35" ht="20" customHeight="1">
       <c r="B214" s="55">
         <v>206</v>
       </c>
@@ -24613,7 +24623,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN RCRIT_NMPR_SET_YN;</v>
       </c>
     </row>
-    <row r="215" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="215" spans="2:35" ht="20" customHeight="1">
       <c r="B215" s="55">
         <v>207</v>
       </c>
@@ -24699,7 +24709,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN RCRIT_NMPR_CO;</v>
       </c>
     </row>
-    <row r="216" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="216" spans="2:35" ht="20" customHeight="1">
       <c r="B216" s="55">
         <v>208</v>
       </c>
@@ -24789,7 +24799,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN PREPAR_RCRIT_NMPR_SET_YN;</v>
       </c>
     </row>
-    <row r="217" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="217" spans="2:35" ht="20" customHeight="1">
       <c r="B217" s="135">
         <v>209</v>
       </c>
@@ -24875,7 +24885,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN PREPAR_RCRIT_NMPR_CO;</v>
       </c>
     </row>
-    <row r="218" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="218" spans="2:35" ht="20" customHeight="1">
       <c r="B218" s="55">
         <v>210</v>
       </c>
@@ -24967,7 +24977,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="219" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="219" spans="2:35" ht="20" customHeight="1">
       <c r="B219" s="55">
         <v>211</v>
       </c>
@@ -25057,7 +25067,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="220" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="220" spans="2:35" ht="20" customHeight="1">
       <c r="B220" s="55">
         <v>212</v>
       </c>
@@ -25145,7 +25155,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="221" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="221" spans="2:35" ht="20" customHeight="1">
       <c r="B221" s="135">
         <v>213</v>
       </c>
@@ -25235,7 +25245,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="222" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="222" spans="2:35" ht="20" customHeight="1">
       <c r="B222" s="55">
         <v>214</v>
       </c>
@@ -25323,7 +25333,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="223" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="223" spans="2:35" ht="20" customHeight="1">
       <c r="B223" s="55">
         <v>215</v>
       </c>
@@ -25409,7 +25419,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="224" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="224" spans="2:35" ht="20" customHeight="1">
       <c r="B224" s="55">
         <v>216</v>
       </c>
@@ -25501,7 +25511,7 @@
         <v>ALTER TABLE TB_LCTRE DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="225" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="225" spans="2:35" ht="20" customHeight="1">
       <c r="B225" s="135">
         <v>217</v>
       </c>
@@ -25594,7 +25604,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST DROP COLUMN LCTRE_REQST_SN;</v>
       </c>
     </row>
-    <row r="226" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="226" spans="2:35" ht="20" customHeight="1">
       <c r="B226" s="55">
         <v>218</v>
       </c>
@@ -25692,7 +25702,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST DROP COLUMN CLASS_REQST_SN;</v>
       </c>
     </row>
-    <row r="227" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="227" spans="2:35" ht="20" customHeight="1">
       <c r="B227" s="55">
         <v>219</v>
       </c>
@@ -25790,7 +25800,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST DROP COLUMN LCTRE_SN;</v>
       </c>
     </row>
-    <row r="228" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="228" spans="2:35" ht="20" customHeight="1">
       <c r="B228" s="55">
         <v>220</v>
       </c>
@@ -25886,7 +25896,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST DROP COLUMN CHLDRN_SN;</v>
       </c>
     </row>
-    <row r="229" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="229" spans="2:35" ht="20" customHeight="1">
       <c r="B229" s="135">
         <v>221</v>
       </c>
@@ -25978,7 +25988,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="230" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="230" spans="2:35" ht="20" customHeight="1">
       <c r="B230" s="55">
         <v>222</v>
       </c>
@@ -26068,7 +26078,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="231" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="231" spans="2:35" ht="20" customHeight="1">
       <c r="B231" s="55">
         <v>223</v>
       </c>
@@ -26156,7 +26166,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="232" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="232" spans="2:35" ht="20" customHeight="1">
       <c r="B232" s="55">
         <v>224</v>
       </c>
@@ -26246,7 +26256,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="233" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="233" spans="2:35" ht="20" customHeight="1">
       <c r="B233" s="135">
         <v>225</v>
       </c>
@@ -26334,7 +26344,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="234" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="234" spans="2:35" ht="20" customHeight="1">
       <c r="B234" s="55">
         <v>226</v>
       </c>
@@ -26420,7 +26430,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="235" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="235" spans="2:35" ht="20" customHeight="1">
       <c r="B235" s="55">
         <v>227</v>
       </c>
@@ -26512,7 +26522,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="236" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="236" spans="2:35" ht="20" customHeight="1">
       <c r="B236" s="55">
         <v>228</v>
       </c>
@@ -26605,7 +26615,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST_DETAIL DROP COLUMN LCTRE_REQST_DETAIL_SN;</v>
       </c>
     </row>
-    <row r="237" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="237" spans="2:35" ht="20" customHeight="1">
       <c r="B237" s="135">
         <v>229</v>
       </c>
@@ -26703,7 +26713,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST_DETAIL DROP COLUMN LCTRE_REQST_SN;</v>
       </c>
     </row>
-    <row r="238" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="238" spans="2:35" ht="20" customHeight="1">
       <c r="B238" s="55">
         <v>230</v>
       </c>
@@ -26801,7 +26811,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST_DETAIL DROP COLUMN CLASS_DETAIL_SN;</v>
       </c>
     </row>
-    <row r="239" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="239" spans="2:35" ht="20" customHeight="1">
       <c r="B239" s="55">
         <v>231</v>
       </c>
@@ -26891,7 +26901,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST_DETAIL DROP COLUMN CLASS_DETAIL_ANSWER;</v>
       </c>
     </row>
-    <row r="240" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="240" spans="2:35" ht="20" customHeight="1">
       <c r="B240" s="55">
         <v>232</v>
       </c>
@@ -26979,7 +26989,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST_DETAIL DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="241" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="241" spans="2:35" ht="20" customHeight="1">
       <c r="B241" s="135">
         <v>233</v>
       </c>
@@ -27071,7 +27081,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST_DETAIL DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="242" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="242" spans="2:35" ht="20" customHeight="1">
       <c r="B242" s="55">
         <v>234</v>
       </c>
@@ -27159,7 +27169,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST_DETAIL DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="243" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="243" spans="2:35" ht="20" customHeight="1">
       <c r="B243" s="55">
         <v>235</v>
       </c>
@@ -27249,7 +27259,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST_DETAIL DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="244" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="244" spans="2:35" ht="20" customHeight="1">
       <c r="B244" s="55">
         <v>236</v>
       </c>
@@ -27339,7 +27349,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST_DETAIL DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="245" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="245" spans="2:35" ht="20" customHeight="1">
       <c r="B245" s="135">
         <v>237</v>
       </c>
@@ -27425,7 +27435,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST_DETAIL DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="246" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="246" spans="2:35" ht="20" customHeight="1">
       <c r="B246" s="55">
         <v>238</v>
       </c>
@@ -27515,7 +27525,7 @@
         <v>ALTER TABLE TB_LCTRE_REQST_DETAIL DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="247" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="247" spans="2:35" ht="20" customHeight="1">
       <c r="B247" s="55">
         <v>239</v>
       </c>
@@ -27608,7 +27618,7 @@
         <v>ALTER TABLE TB_BBS DROP COLUMN BBS_SN;</v>
       </c>
     </row>
-    <row r="248" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="248" spans="2:35" ht="20" customHeight="1">
       <c r="B248" s="55">
         <v>240</v>
       </c>
@@ -27702,7 +27712,7 @@
         <v>ALTER TABLE TB_BBS DROP COLUMN BBS_SE_CD;</v>
       </c>
     </row>
-    <row r="249" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="249" spans="2:35" ht="20" customHeight="1">
       <c r="B249" s="135">
         <v>241</v>
       </c>
@@ -27792,7 +27802,7 @@
         <v>ALTER TABLE TB_BBS DROP COLUMN BBS_NM;</v>
       </c>
     </row>
-    <row r="250" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="250" spans="2:35" ht="20" customHeight="1">
       <c r="B250" s="55">
         <v>242</v>
       </c>
@@ -27878,7 +27888,7 @@
         <v>ALTER TABLE TB_BBS DROP COLUMN BBS_GDCC;</v>
       </c>
     </row>
-    <row r="251" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="251" spans="2:35" ht="20" customHeight="1">
       <c r="B251" s="55">
         <v>243</v>
       </c>
@@ -27966,7 +27976,7 @@
         <v>ALTER TABLE TB_BBS DROP COLUMN BBS_DC;</v>
       </c>
     </row>
-    <row r="252" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="252" spans="2:35" ht="20" customHeight="1">
       <c r="B252" s="55">
         <v>244</v>
       </c>
@@ -28054,7 +28064,7 @@
         <v>ALTER TABLE TB_BBS DROP COLUMN REPLY_SET_YN;</v>
       </c>
     </row>
-    <row r="253" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="253" spans="2:35" ht="20" customHeight="1">
       <c r="B253" s="135">
         <v>245</v>
       </c>
@@ -28146,7 +28156,7 @@
         <v>ALTER TABLE TB_BBS DROP COLUMN OPEN_YN;</v>
       </c>
     </row>
-    <row r="254" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="254" spans="2:35" ht="20" customHeight="1">
       <c r="B254" s="55">
         <v>246</v>
       </c>
@@ -28236,7 +28246,7 @@
         <v>ALTER TABLE TB_BBS DROP COLUMN USE_YN;</v>
       </c>
     </row>
-    <row r="255" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="255" spans="2:35" ht="20" customHeight="1">
       <c r="B255" s="55">
         <v>247</v>
       </c>
@@ -28328,7 +28338,7 @@
         <v>ALTER TABLE TB_BBS DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="256" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="256" spans="2:35" ht="20" customHeight="1">
       <c r="B256" s="55">
         <v>248</v>
       </c>
@@ -28418,7 +28428,7 @@
         <v>ALTER TABLE TB_BBS DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="257" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="257" spans="2:35" ht="20" customHeight="1">
       <c r="B257" s="135">
         <v>249</v>
       </c>
@@ -28506,7 +28516,7 @@
         <v>ALTER TABLE TB_BBS DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="258" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="258" spans="2:35" ht="20" customHeight="1">
       <c r="B258" s="55">
         <v>250</v>
       </c>
@@ -28596,7 +28606,7 @@
         <v>ALTER TABLE TB_BBS DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="259" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="259" spans="2:35" ht="20" customHeight="1">
       <c r="B259" s="55">
         <v>251</v>
       </c>
@@ -28684,7 +28694,7 @@
         <v>ALTER TABLE TB_BBS DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="260" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="260" spans="2:35" ht="20" customHeight="1">
       <c r="B260" s="55">
         <v>252</v>
       </c>
@@ -28770,7 +28780,7 @@
         <v>ALTER TABLE TB_BBS DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="261" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="261" spans="2:35" ht="20" customHeight="1">
       <c r="B261" s="135">
         <v>253</v>
       </c>
@@ -28862,7 +28872,7 @@
         <v>ALTER TABLE TB_BBS DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="262" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="262" spans="2:35" ht="20" customHeight="1">
       <c r="B262" s="55">
         <v>254</v>
       </c>
@@ -28955,7 +28965,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN NTT_SN;</v>
       </c>
     </row>
-    <row r="263" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="263" spans="2:35" ht="20" customHeight="1">
       <c r="B263" s="55">
         <v>255</v>
       </c>
@@ -29053,7 +29063,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN BBS_SN;</v>
       </c>
     </row>
-    <row r="264" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="264" spans="2:35" ht="20" customHeight="1">
       <c r="B264" s="55">
         <v>256</v>
       </c>
@@ -29141,7 +29151,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN NTT_SEQ;</v>
       </c>
     </row>
-    <row r="265" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="265" spans="2:35" ht="20" customHeight="1">
       <c r="B265" s="135">
         <v>257</v>
       </c>
@@ -29229,7 +29239,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN NTT_NM;</v>
       </c>
     </row>
-    <row r="266" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="266" spans="2:35" ht="20" customHeight="1">
       <c r="B266" s="55">
         <v>258</v>
       </c>
@@ -29325,7 +29335,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN THUMB_ATCH_FILE_SN;</v>
       </c>
     </row>
-    <row r="267" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="267" spans="2:35" ht="20" customHeight="1">
       <c r="B267" s="55">
         <v>259</v>
       </c>
@@ -29411,7 +29421,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN NTT_CN;</v>
       </c>
     </row>
-    <row r="268" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="268" spans="2:35" ht="20" customHeight="1">
       <c r="B268" s="55">
         <v>260</v>
       </c>
@@ -29507,7 +29517,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN ATCH_FILE_SN;</v>
       </c>
     </row>
-    <row r="269" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="269" spans="2:35" ht="20" customHeight="1">
       <c r="B269" s="135">
         <v>261</v>
       </c>
@@ -29593,7 +29603,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN NTT_RDCNT;</v>
       </c>
     </row>
-    <row r="270" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="270" spans="2:35" ht="20" customHeight="1">
       <c r="B270" s="55">
         <v>262</v>
       </c>
@@ -29683,7 +29693,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN OPEN_YN;</v>
       </c>
     </row>
-    <row r="271" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="271" spans="2:35" ht="20" customHeight="1">
       <c r="B271" s="55">
         <v>263</v>
       </c>
@@ -29771,7 +29781,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN NOTICE_SET_YN;</v>
       </c>
     </row>
-    <row r="272" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="272" spans="2:35" ht="20" customHeight="1">
       <c r="B272" s="55">
         <v>264</v>
       </c>
@@ -29857,7 +29867,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN NOTICE_SEQ;</v>
       </c>
     </row>
-    <row r="273" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="273" spans="2:35" ht="20" customHeight="1">
       <c r="B273" s="135">
         <v>265</v>
       </c>
@@ -29949,7 +29959,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="274" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="274" spans="2:35" ht="20" customHeight="1">
       <c r="B274" s="55">
         <v>266</v>
       </c>
@@ -30039,7 +30049,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="275" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="275" spans="2:35" ht="20" customHeight="1">
       <c r="B275" s="55">
         <v>267</v>
       </c>
@@ -30127,7 +30137,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="276" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="276" spans="2:35" ht="20" customHeight="1">
       <c r="B276" s="55">
         <v>268</v>
       </c>
@@ -30217,7 +30227,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="277" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="277" spans="2:35" ht="20" customHeight="1">
       <c r="B277" s="135">
         <v>269</v>
       </c>
@@ -30305,7 +30315,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="278" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="278" spans="2:35" ht="20" customHeight="1">
       <c r="B278" s="55">
         <v>270</v>
       </c>
@@ -30391,7 +30401,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="279" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="279" spans="2:35" ht="20" customHeight="1">
       <c r="B279" s="55">
         <v>271</v>
       </c>
@@ -30483,7 +30493,7 @@
         <v>ALTER TABLE TB_NTT DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="280" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="280" spans="2:35" ht="20" customHeight="1">
       <c r="B280" s="55">
         <v>272</v>
       </c>
@@ -30576,7 +30586,7 @@
         <v>ALTER TABLE TB_NTT_REPLY DROP COLUMN NTT_REPLY_SN;</v>
       </c>
     </row>
-    <row r="281" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="281" spans="2:35" ht="20" customHeight="1">
       <c r="B281" s="135">
         <v>273</v>
       </c>
@@ -30674,7 +30684,7 @@
         <v>ALTER TABLE TB_NTT_REPLY DROP COLUMN NTT_SN;</v>
       </c>
     </row>
-    <row r="282" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="282" spans="2:35" ht="20" customHeight="1">
       <c r="B282" s="55">
         <v>274</v>
       </c>
@@ -30762,7 +30772,7 @@
         <v>ALTER TABLE TB_NTT_REPLY DROP COLUMN STEP;</v>
       </c>
     </row>
-    <row r="283" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="283" spans="2:35" ht="20" customHeight="1">
       <c r="B283" s="55">
         <v>275</v>
       </c>
@@ -30850,7 +30860,7 @@
         <v>ALTER TABLE TB_NTT_REPLY DROP COLUMN PARNTS_REPLY_SN;</v>
       </c>
     </row>
-    <row r="284" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="284" spans="2:35" ht="20" customHeight="1">
       <c r="B284" s="55">
         <v>276</v>
       </c>
@@ -30938,7 +30948,7 @@
         <v>ALTER TABLE TB_NTT_REPLY DROP COLUMN NTT_REPLY_SEQ;</v>
       </c>
     </row>
-    <row r="285" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="285" spans="2:35" ht="20" customHeight="1">
       <c r="B285" s="135">
         <v>277</v>
       </c>
@@ -31026,7 +31036,7 @@
         <v>ALTER TABLE TB_NTT_REPLY DROP COLUMN NTT_REPLY_CN;</v>
       </c>
     </row>
-    <row r="286" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="286" spans="2:35" ht="20" customHeight="1">
       <c r="B286" s="55">
         <v>278</v>
       </c>
@@ -31116,7 +31126,7 @@
         <v>ALTER TABLE TB_NTT_REPLY DROP COLUMN OPEN_YN;</v>
       </c>
     </row>
-    <row r="287" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="287" spans="2:35" ht="20" customHeight="1">
       <c r="B287" s="55">
         <v>279</v>
       </c>
@@ -31208,7 +31218,7 @@
         <v>ALTER TABLE TB_NTT_REPLY DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="288" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="288" spans="2:35" ht="20" customHeight="1">
       <c r="B288" s="55">
         <v>280</v>
       </c>
@@ -31298,7 +31308,7 @@
         <v>ALTER TABLE TB_NTT_REPLY DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="289" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="289" spans="2:35" ht="20" customHeight="1">
       <c r="B289" s="135">
         <v>281</v>
       </c>
@@ -31386,7 +31396,7 @@
         <v>ALTER TABLE TB_NTT_REPLY DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="290" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="290" spans="2:35" ht="20" customHeight="1">
       <c r="B290" s="55">
         <v>282</v>
       </c>
@@ -31476,7 +31486,7 @@
         <v>ALTER TABLE TB_NTT_REPLY DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="291" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="291" spans="2:35" ht="20" customHeight="1">
       <c r="B291" s="55">
         <v>283</v>
       </c>
@@ -31564,7 +31574,7 @@
         <v>ALTER TABLE TB_NTT_REPLY DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="292" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="292" spans="2:35" ht="20" customHeight="1">
       <c r="B292" s="55">
         <v>284</v>
       </c>
@@ -31650,7 +31660,7 @@
         <v>ALTER TABLE TB_NTT_REPLY DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="293" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="293" spans="2:35" ht="20" customHeight="1">
       <c r="B293" s="135">
         <v>285</v>
       </c>
@@ -31742,7 +31752,7 @@
         <v>ALTER TABLE TB_NTT_REPLY DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="294" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="294" spans="2:35" ht="20" customHeight="1">
       <c r="B294" s="55">
         <v>286</v>
       </c>
@@ -31835,7 +31845,7 @@
         <v>ALTER TABLE TB_POPUP DROP COLUMN POPUP_SN;</v>
       </c>
     </row>
-    <row r="295" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="295" spans="2:35" ht="20" customHeight="1">
       <c r="B295" s="55">
         <v>287</v>
       </c>
@@ -31923,7 +31933,7 @@
         <v>ALTER TABLE TB_POPUP DROP COLUMN POPUP_SJ;</v>
       </c>
     </row>
-    <row r="296" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="296" spans="2:35" ht="20" customHeight="1">
       <c r="B296" s="55">
         <v>288</v>
       </c>
@@ -32011,7 +32021,7 @@
         <v>ALTER TABLE TB_POPUP DROP COLUMN POPUP_CN;</v>
       </c>
     </row>
-    <row r="297" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="297" spans="2:35" ht="20" customHeight="1">
       <c r="B297" s="135">
         <v>289</v>
       </c>
@@ -32101,7 +32111,7 @@
         <v>ALTER TABLE TB_POPUP DROP COLUMN USE_YN;</v>
       </c>
     </row>
-    <row r="298" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="298" spans="2:35" ht="20" customHeight="1">
       <c r="B298" s="55">
         <v>290</v>
       </c>
@@ -32191,7 +32201,7 @@
         <v>ALTER TABLE TB_POPUP DROP COLUMN POPUP_BEGIN_DT;</v>
       </c>
     </row>
-    <row r="299" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="299" spans="2:35" ht="20" customHeight="1">
       <c r="B299" s="55">
         <v>291</v>
       </c>
@@ -32281,7 +32291,7 @@
         <v>ALTER TABLE TB_POPUP DROP COLUMN POPUP_END_DT;</v>
       </c>
     </row>
-    <row r="300" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="300" spans="2:35" ht="20" customHeight="1">
       <c r="B300" s="55">
         <v>292</v>
       </c>
@@ -32379,7 +32389,7 @@
         <v>ALTER TABLE TB_POPUP DROP COLUMN ATCH_FILE_SN;</v>
       </c>
     </row>
-    <row r="301" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="301" spans="2:35" ht="20" customHeight="1">
       <c r="B301" s="135">
         <v>293</v>
       </c>
@@ -32467,7 +32477,7 @@
         <v>ALTER TABLE TB_POPUP DROP COLUMN MOVE_URL;</v>
       </c>
     </row>
-    <row r="302" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="302" spans="2:35" ht="20" customHeight="1">
       <c r="B302" s="55">
         <v>294</v>
       </c>
@@ -32559,7 +32569,7 @@
         <v>ALTER TABLE TB_POPUP DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="303" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="303" spans="2:35" ht="20" customHeight="1">
       <c r="B303" s="55">
         <v>295</v>
       </c>
@@ -32649,7 +32659,7 @@
         <v>ALTER TABLE TB_POPUP DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="304" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="304" spans="2:35" ht="20" customHeight="1">
       <c r="B304" s="55">
         <v>296</v>
       </c>
@@ -32737,7 +32747,7 @@
         <v>ALTER TABLE TB_POPUP DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="305" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="305" spans="2:35" ht="20" customHeight="1">
       <c r="B305" s="135">
         <v>297</v>
       </c>
@@ -32827,7 +32837,7 @@
         <v>ALTER TABLE TB_POPUP DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="306" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="306" spans="2:35" ht="20" customHeight="1">
       <c r="B306" s="55">
         <v>298</v>
       </c>
@@ -32915,7 +32925,7 @@
         <v>ALTER TABLE TB_POPUP DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="307" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="307" spans="2:35" ht="20" customHeight="1">
       <c r="B307" s="55">
         <v>299</v>
       </c>
@@ -33001,7 +33011,7 @@
         <v>ALTER TABLE TB_POPUP DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="308" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="308" spans="2:35" ht="20" customHeight="1">
       <c r="B308" s="55">
         <v>300</v>
       </c>
@@ -33093,7 +33103,7 @@
         <v>ALTER TABLE TB_POPUP DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="309" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="309" spans="2:35" ht="20" customHeight="1">
       <c r="B309" s="135">
         <v>301</v>
       </c>
@@ -33186,7 +33196,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN QESTNAR_GROUP_SN;</v>
       </c>
     </row>
-    <row r="310" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="310" spans="2:35" ht="20" customHeight="1">
       <c r="B310" s="135">
         <v>301</v>
       </c>
@@ -33280,7 +33290,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN QESTNAR_GROUP_CD;</v>
       </c>
     </row>
-    <row r="311" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="311" spans="2:35" ht="20" customHeight="1">
       <c r="B311" s="55">
         <v>303</v>
       </c>
@@ -33368,7 +33378,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN QESTNAR_GROUP_NM;</v>
       </c>
     </row>
-    <row r="312" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="312" spans="2:35" ht="20" customHeight="1">
       <c r="B312" s="55">
         <v>304</v>
       </c>
@@ -33456,7 +33466,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN QESTNAR_GROUP_DC;</v>
       </c>
     </row>
-    <row r="313" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="313" spans="2:35" ht="20" customHeight="1">
       <c r="B313" s="55">
         <v>304</v>
       </c>
@@ -33546,7 +33556,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN UPEND_GDCC_SET_YN;</v>
       </c>
     </row>
-    <row r="314" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="314" spans="2:35" ht="20" customHeight="1">
       <c r="B314" s="55">
         <v>304</v>
       </c>
@@ -33634,7 +33644,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN UPEND_GDCC;</v>
       </c>
     </row>
-    <row r="315" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="315" spans="2:35" ht="20" customHeight="1">
       <c r="B315" s="55">
         <v>304</v>
       </c>
@@ -33724,7 +33734,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN LPT_GDCC_SET_YN;</v>
       </c>
     </row>
-    <row r="316" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="316" spans="2:35" ht="20" customHeight="1">
       <c r="B316" s="55">
         <v>304</v>
       </c>
@@ -33812,7 +33822,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN LPT_GDCC;</v>
       </c>
     </row>
-    <row r="317" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="317" spans="2:35" ht="20" customHeight="1">
       <c r="B317" s="135">
         <v>305</v>
       </c>
@@ -33904,7 +33914,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN PRIVCY_YN;</v>
       </c>
     </row>
-    <row r="318" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="318" spans="2:35" ht="20" customHeight="1">
       <c r="B318" s="135">
         <v>305</v>
       </c>
@@ -33995,7 +34005,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN LOGIN_ESSNTL_YN;</v>
       </c>
     </row>
-    <row r="319" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="319" spans="2:35" ht="20" customHeight="1">
       <c r="B319" s="135">
         <v>305</v>
       </c>
@@ -34086,7 +34096,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN REPLY_SET_YN;</v>
       </c>
     </row>
-    <row r="320" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="320" spans="2:35" ht="20" customHeight="1">
       <c r="B320" s="55">
         <v>306</v>
       </c>
@@ -34176,7 +34186,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN USE_YN;</v>
       </c>
     </row>
-    <row r="321" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="321" spans="2:35" ht="20" customHeight="1">
       <c r="B321" s="55">
         <v>307</v>
       </c>
@@ -34268,7 +34278,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="322" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="322" spans="2:35" ht="20" customHeight="1">
       <c r="B322" s="55">
         <v>308</v>
       </c>
@@ -34358,7 +34368,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="323" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="323" spans="2:35" ht="20" customHeight="1">
       <c r="B323" s="135">
         <v>309</v>
       </c>
@@ -34446,7 +34456,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="324" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="324" spans="2:35" ht="20" customHeight="1">
       <c r="B324" s="55">
         <v>310</v>
       </c>
@@ -34536,7 +34546,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="325" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="325" spans="2:35" ht="20" customHeight="1">
       <c r="B325" s="55">
         <v>311</v>
       </c>
@@ -34624,7 +34634,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="326" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="326" spans="2:35" ht="20" customHeight="1">
       <c r="B326" s="55">
         <v>312</v>
       </c>
@@ -34710,7 +34720,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="327" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="327" spans="2:35" ht="20" customHeight="1">
       <c r="B327" s="135">
         <v>313</v>
       </c>
@@ -34802,7 +34812,7 @@
         <v>ALTER TABLE TB_QESTNAR_GROUP DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="328" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="328" spans="2:35" ht="20" customHeight="1">
       <c r="B328" s="55">
         <v>314</v>
       </c>
@@ -34895,7 +34905,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN DROP COLUMN QESTNAR_QESTN_SN;</v>
       </c>
     </row>
-    <row r="329" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="329" spans="2:35" ht="20" customHeight="1">
       <c r="B329" s="55">
         <v>315</v>
       </c>
@@ -34993,7 +35003,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN DROP COLUMN QESTNAR_GROUP_SN;</v>
       </c>
     </row>
-    <row r="330" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="330" spans="2:35" ht="20" customHeight="1">
       <c r="B330" s="55">
         <v>316</v>
       </c>
@@ -35081,7 +35091,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN DROP COLUMN QESTNAR_QESTN_SEQ;</v>
       </c>
     </row>
-    <row r="331" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="331" spans="2:35" ht="20" customHeight="1">
       <c r="B331" s="135">
         <v>317</v>
       </c>
@@ -35175,7 +35185,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN DROP COLUMN QESTNAR_QESTN_ITEM_TY_CD;</v>
       </c>
     </row>
-    <row r="332" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="332" spans="2:35" ht="20" customHeight="1">
       <c r="B332" s="55">
         <v>318</v>
       </c>
@@ -35263,7 +35273,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN DROP COLUMN QESTNAR_QESTN_ITEM_CN;</v>
       </c>
     </row>
-    <row r="333" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="333" spans="2:35" ht="20" customHeight="1">
       <c r="B333" s="55">
         <v>319</v>
       </c>
@@ -35355,7 +35365,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN DROP COLUMN QESTNAR_QESTN_ESSNTL_YN;</v>
       </c>
     </row>
-    <row r="334" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="334" spans="2:35" ht="20" customHeight="1">
       <c r="B334" s="55">
         <v>319</v>
       </c>
@@ -35451,7 +35461,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN DROP COLUMN ATCH_FILE_SN;</v>
       </c>
     </row>
-    <row r="335" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="335" spans="2:35" ht="20" customHeight="1">
       <c r="B335" s="55">
         <v>320</v>
       </c>
@@ -35543,7 +35553,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="336" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="336" spans="2:35" ht="20" customHeight="1">
       <c r="B336" s="135">
         <v>321</v>
       </c>
@@ -35633,7 +35643,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="337" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="337" spans="2:35" ht="20" customHeight="1">
       <c r="B337" s="55">
         <v>322</v>
       </c>
@@ -35721,7 +35731,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="338" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="338" spans="2:35" ht="20" customHeight="1">
       <c r="B338" s="55">
         <v>323</v>
       </c>
@@ -35811,7 +35821,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="339" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="339" spans="2:35" ht="20" customHeight="1">
       <c r="B339" s="55">
         <v>324</v>
       </c>
@@ -35899,7 +35909,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="340" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="340" spans="2:35" ht="20" customHeight="1">
       <c r="B340" s="135">
         <v>325</v>
       </c>
@@ -35985,7 +35995,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="341" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="341" spans="2:35" ht="20" customHeight="1">
       <c r="B341" s="55">
         <v>326</v>
       </c>
@@ -36077,7 +36087,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="342" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="342" spans="2:35" ht="20" customHeight="1">
       <c r="B342" s="55">
         <v>327</v>
       </c>
@@ -36172,7 +36182,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN_DETAIL DROP COLUMN QESTNAR_QESTN_DETAIL_SN;</v>
       </c>
     </row>
-    <row r="343" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="343" spans="2:35" ht="20" customHeight="1">
       <c r="B343" s="55">
         <v>328</v>
       </c>
@@ -36270,7 +36280,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN_DETAIL DROP COLUMN QESTNAR_QESTN_SN;</v>
       </c>
     </row>
-    <row r="344" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="344" spans="2:35" ht="20" customHeight="1">
       <c r="B344" s="135">
         <v>329</v>
       </c>
@@ -36356,7 +36366,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN_DETAIL DROP COLUMN QESTNAR_QESTN_DETAIL_SEQ;</v>
       </c>
     </row>
-    <row r="345" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="345" spans="2:35" ht="20" customHeight="1">
       <c r="B345" s="55">
         <v>330</v>
       </c>
@@ -36444,7 +36454,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN_DETAIL DROP COLUMN QESTNAR_QESTN_DETAIL_CN;</v>
       </c>
     </row>
-    <row r="346" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="346" spans="2:35" ht="20" customHeight="1">
       <c r="B346" s="55">
         <v>331</v>
       </c>
@@ -36536,7 +36546,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN_DETAIL DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="347" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="347" spans="2:35" ht="20" customHeight="1">
       <c r="B347" s="55">
         <v>332</v>
       </c>
@@ -36626,7 +36636,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN_DETAIL DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="348" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="348" spans="2:35" ht="20" customHeight="1">
       <c r="B348" s="135">
         <v>333</v>
       </c>
@@ -36714,7 +36724,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN_DETAIL DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="349" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="349" spans="2:35" ht="20" customHeight="1">
       <c r="B349" s="55">
         <v>334</v>
       </c>
@@ -36804,7 +36814,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN_DETAIL DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="350" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="350" spans="2:35" ht="20" customHeight="1">
       <c r="B350" s="55">
         <v>335</v>
       </c>
@@ -36892,7 +36902,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN_DETAIL DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="351" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="351" spans="2:35" ht="20" customHeight="1">
       <c r="B351" s="55">
         <v>336</v>
       </c>
@@ -36978,7 +36988,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN_DETAIL DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="352" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="352" spans="2:35" ht="20" customHeight="1">
       <c r="B352" s="135">
         <v>337</v>
       </c>
@@ -37070,7 +37080,7 @@
         <v>ALTER TABLE TB_QESTNAR_QESTN_DETAIL DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="353" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="353" spans="2:35" ht="20" customHeight="1">
       <c r="B353" s="55">
         <v>338</v>
       </c>
@@ -37163,7 +37173,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER DROP COLUMN QESTNAR_ANSWER_SN;</v>
       </c>
     </row>
-    <row r="354" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="354" spans="2:35" ht="20" customHeight="1">
       <c r="B354" s="55">
         <v>339</v>
       </c>
@@ -37261,7 +37271,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER DROP COLUMN QESTNAR_GROUP_SN;</v>
       </c>
     </row>
-    <row r="355" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="355" spans="2:35" ht="20" customHeight="1">
       <c r="B355" s="55">
         <v>340</v>
       </c>
@@ -37349,7 +37359,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER DROP COLUMN USER_SN;</v>
       </c>
     </row>
-    <row r="356" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="356" spans="2:35" ht="20" customHeight="1">
       <c r="B356" s="135">
         <v>341</v>
       </c>
@@ -37439,7 +37449,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="357" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="357" spans="2:35" ht="20" customHeight="1">
       <c r="B357" s="55">
         <v>342</v>
       </c>
@@ -37529,7 +37539,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="358" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="358" spans="2:35" ht="20" customHeight="1">
       <c r="B358" s="55">
         <v>343</v>
       </c>
@@ -37617,7 +37627,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="359" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="359" spans="2:35" ht="20" customHeight="1">
       <c r="B359" s="55">
         <v>344</v>
       </c>
@@ -37707,7 +37717,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="360" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="360" spans="2:35" ht="20" customHeight="1">
       <c r="B360" s="135">
         <v>345</v>
       </c>
@@ -37795,7 +37805,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="361" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="361" spans="2:35" ht="20" customHeight="1">
       <c r="B361" s="55">
         <v>346</v>
       </c>
@@ -37881,7 +37891,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="362" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="362" spans="2:35" ht="20" customHeight="1">
       <c r="B362" s="55">
         <v>347</v>
       </c>
@@ -37973,7 +37983,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="363" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="363" spans="2:35" ht="20" customHeight="1">
       <c r="B363" s="55">
         <v>348</v>
       </c>
@@ -38066,7 +38076,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_DETAIL DROP COLUMN QESTNAR_ANSWER_DETAIL_SN;</v>
       </c>
     </row>
-    <row r="364" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="364" spans="2:35" ht="20" customHeight="1">
       <c r="B364" s="135">
         <v>349</v>
       </c>
@@ -38164,7 +38174,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_DETAIL DROP COLUMN QESTNAR_ANSWER_SN;</v>
       </c>
     </row>
-    <row r="365" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="365" spans="2:35" ht="20" customHeight="1">
       <c r="B365" s="55">
         <v>350</v>
       </c>
@@ -38262,7 +38272,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_DETAIL DROP COLUMN QESTNAR_QESTN_SN;</v>
       </c>
     </row>
-    <row r="366" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="366" spans="2:35" ht="20" customHeight="1">
       <c r="B366" s="55">
         <v>351</v>
       </c>
@@ -38352,7 +38362,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_DETAIL DROP COLUMN QESTNAR_ANSWER;</v>
       </c>
     </row>
-    <row r="367" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="367" spans="2:35" ht="20" customHeight="1">
       <c r="B367" s="55">
         <v>352</v>
       </c>
@@ -38450,7 +38460,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_DETAIL DROP COLUMN QESTNAR_QESTN_DETAIL_SN;</v>
       </c>
     </row>
-    <row r="368" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="368" spans="2:35" ht="20" customHeight="1">
       <c r="B368" s="135">
         <v>353</v>
       </c>
@@ -38550,7 +38560,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_DETAIL DROP COLUMN ATCH_FILE_SN;</v>
       </c>
     </row>
-    <row r="369" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="369" spans="2:35" ht="20" customHeight="1">
       <c r="B369" s="55">
         <v>354</v>
       </c>
@@ -38640,7 +38650,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_DETAIL DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="370" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="370" spans="2:35" ht="20" customHeight="1">
       <c r="B370" s="55">
         <v>355</v>
       </c>
@@ -38730,7 +38740,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_DETAIL DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="371" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="371" spans="2:35" ht="20" customHeight="1">
       <c r="B371" s="55">
         <v>356</v>
       </c>
@@ -38818,7 +38828,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_DETAIL DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="372" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="372" spans="2:35" ht="20" customHeight="1">
       <c r="B372" s="135">
         <v>357</v>
       </c>
@@ -38908,7 +38918,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_DETAIL DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="373" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="373" spans="2:35" ht="20" customHeight="1">
       <c r="B373" s="55">
         <v>358</v>
       </c>
@@ -38996,7 +39006,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_DETAIL DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="374" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="374" spans="2:35" ht="20" customHeight="1">
       <c r="B374" s="55">
         <v>359</v>
       </c>
@@ -39082,7 +39092,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_DETAIL DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="375" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="375" spans="2:35" ht="20" customHeight="1">
       <c r="B375" s="55">
         <v>360</v>
       </c>
@@ -39174,7 +39184,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_DETAIL DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="376" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="376" spans="2:35" ht="20" customHeight="1">
       <c r="B376" s="55">
         <v>360</v>
       </c>
@@ -39267,7 +39277,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_REPLY DROP COLUMN QESTNAR_ANSWER_REPLY_SN;</v>
       </c>
     </row>
-    <row r="377" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="377" spans="2:35" ht="20" customHeight="1">
       <c r="B377" s="55">
         <v>360</v>
       </c>
@@ -39365,7 +39375,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_REPLY DROP COLUMN QESTNAR_ANSWER_SN;</v>
       </c>
     </row>
-    <row r="378" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="378" spans="2:35" ht="20" customHeight="1">
       <c r="B378" s="55">
         <v>360</v>
       </c>
@@ -39465,7 +39475,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_REPLY DROP COLUMN USER_SN;</v>
       </c>
     </row>
-    <row r="379" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="379" spans="2:35" ht="20" customHeight="1">
       <c r="B379" s="55">
         <v>360</v>
       </c>
@@ -39555,7 +39565,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_REPLY DROP COLUMN QESTNAR_ANSWER_REPLY_CN;</v>
       </c>
     </row>
-    <row r="380" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="380" spans="2:35" ht="20" customHeight="1">
       <c r="B380" s="55">
         <v>360</v>
       </c>
@@ -39651,7 +39661,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_REPLY DROP COLUMN ATCH_FILE_SN;</v>
       </c>
     </row>
-    <row r="381" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="381" spans="2:35" ht="20" customHeight="1">
       <c r="B381" s="55">
         <v>360</v>
       </c>
@@ -39743,7 +39753,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_REPLY DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="382" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="382" spans="2:35" ht="20" customHeight="1">
       <c r="B382" s="55">
         <v>360</v>
       </c>
@@ -39833,7 +39843,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_REPLY DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="383" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="383" spans="2:35" ht="20" customHeight="1">
       <c r="B383" s="55">
         <v>360</v>
       </c>
@@ -39921,7 +39931,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_REPLY DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="384" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="384" spans="2:35" ht="20" customHeight="1">
       <c r="B384" s="55">
         <v>360</v>
       </c>
@@ -40011,7 +40021,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_REPLY DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="385" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="385" spans="2:35" ht="20" customHeight="1">
       <c r="B385" s="55">
         <v>360</v>
       </c>
@@ -40099,7 +40109,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_REPLY DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="386" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="386" spans="2:35" ht="20" customHeight="1">
       <c r="B386" s="55">
         <v>360</v>
       </c>
@@ -40185,7 +40195,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_REPLY DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="387" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="387" spans="2:35" ht="20" customHeight="1">
       <c r="B387" s="55">
         <v>360</v>
       </c>
@@ -40277,7 +40287,7 @@
         <v>ALTER TABLE TB_QESTNAR_ANSWER_REPLY DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="388" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="388" spans="2:35" ht="20" customHeight="1">
       <c r="B388" s="135">
         <v>361</v>
       </c>
@@ -40370,7 +40380,7 @@
         <v>ALTER TABLE TB_ATCH_FILE DROP COLUMN ATCH_FILE_SN;</v>
       </c>
     </row>
-    <row r="389" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="389" spans="2:35" ht="20" customHeight="1">
       <c r="B389" s="55">
         <v>362</v>
       </c>
@@ -40458,7 +40468,7 @@
         <v>ALTER TABLE TB_ATCH_FILE DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="390" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="390" spans="2:35" ht="20" customHeight="1">
       <c r="B390" s="55">
         <v>363</v>
       </c>
@@ -40550,7 +40560,7 @@
         <v>ALTER TABLE TB_ATCH_FILE DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="391" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="391" spans="2:35" ht="20" customHeight="1">
       <c r="B391" s="55">
         <v>364</v>
       </c>
@@ -40650,7 +40660,7 @@
         <v>ALTER TABLE TB_ATCH_FILE_DETAIL DROP COLUMN ATCH_FILE_SN;</v>
       </c>
     </row>
-    <row r="392" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="392" spans="2:35" ht="20" customHeight="1">
       <c r="B392" s="135">
         <v>365</v>
       </c>
@@ -40740,7 +40750,7 @@
         <v>ALTER TABLE TB_ATCH_FILE_DETAIL DROP COLUMN FILE_SEQ;</v>
       </c>
     </row>
-    <row r="393" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="393" spans="2:35" ht="20" customHeight="1">
       <c r="B393" s="55">
         <v>366</v>
       </c>
@@ -40830,7 +40840,7 @@
         <v>ALTER TABLE TB_ATCH_FILE_DETAIL DROP COLUMN FILE_STRE_PATH;</v>
       </c>
     </row>
-    <row r="394" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="394" spans="2:35" ht="20" customHeight="1">
       <c r="B394" s="55">
         <v>367</v>
       </c>
@@ -40920,7 +40930,7 @@
         <v>ALTER TABLE TB_ATCH_FILE_DETAIL DROP COLUMN STRE_FILE_NM;</v>
       </c>
     </row>
-    <row r="395" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="395" spans="2:35" ht="20" customHeight="1">
       <c r="B395" s="55">
         <v>368</v>
       </c>
@@ -41010,7 +41020,7 @@
         <v>ALTER TABLE TB_ATCH_FILE_DETAIL DROP COLUMN ORIGNL_FILE_NM;</v>
       </c>
     </row>
-    <row r="396" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="396" spans="2:35" ht="20" customHeight="1">
       <c r="B396" s="135">
         <v>369</v>
       </c>
@@ -41100,7 +41110,7 @@
         <v>ALTER TABLE TB_ATCH_FILE_DETAIL DROP COLUMN FILE_EXTSN;</v>
       </c>
     </row>
-    <row r="397" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="397" spans="2:35" ht="20" customHeight="1">
       <c r="B397" s="55">
         <v>370</v>
       </c>
@@ -41186,7 +41196,7 @@
         <v>ALTER TABLE TB_ATCH_FILE_DETAIL DROP COLUMN FILE_CN;</v>
       </c>
     </row>
-    <row r="398" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="398" spans="2:35" ht="20" customHeight="1">
       <c r="B398" s="55">
         <v>371</v>
       </c>
@@ -41276,7 +41286,7 @@
         <v>ALTER TABLE TB_ATCH_FILE_DETAIL DROP COLUMN FILE_SIZE;</v>
       </c>
     </row>
-    <row r="399" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="399" spans="2:35" ht="20" customHeight="1">
       <c r="B399" s="55">
         <v>372</v>
       </c>
@@ -41369,7 +41379,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN MENU_SN;</v>
       </c>
     </row>
-    <row r="400" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="400" spans="2:35" ht="20" customHeight="1">
       <c r="B400" s="135">
         <v>373</v>
       </c>
@@ -41455,7 +41465,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN UPPER_MENU_SN;</v>
       </c>
     </row>
-    <row r="401" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="401" spans="2:35" ht="20" customHeight="1">
       <c r="B401" s="55">
         <v>374</v>
       </c>
@@ -41547,7 +41557,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN MENU_NM;</v>
       </c>
     </row>
-    <row r="402" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="402" spans="2:35" ht="20" customHeight="1">
       <c r="B402" s="55">
         <v>375</v>
       </c>
@@ -41637,7 +41647,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN MENU_CD;</v>
       </c>
     </row>
-    <row r="403" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="403" spans="2:35" ht="20" customHeight="1">
       <c r="B403" s="55">
         <v>376</v>
       </c>
@@ -41725,7 +41735,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN MENU_URL;</v>
       </c>
     </row>
-    <row r="404" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="404" spans="2:35" ht="20" customHeight="1">
       <c r="B404" s="135">
         <v>377</v>
       </c>
@@ -41817,7 +41827,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN PARNTS_MENU_YN;</v>
       </c>
     </row>
-    <row r="405" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="405" spans="2:35" ht="20" customHeight="1">
       <c r="B405" s="55">
         <v>378</v>
       </c>
@@ -41905,7 +41915,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN MENU_SEQ;</v>
       </c>
     </row>
-    <row r="406" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="406" spans="2:35" ht="20" customHeight="1">
       <c r="B406" s="55">
         <v>379</v>
       </c>
@@ -41993,7 +42003,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN MENU_DC_SET_YN;</v>
       </c>
     </row>
-    <row r="407" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="407" spans="2:35" ht="20" customHeight="1">
       <c r="B407" s="55">
         <v>380</v>
       </c>
@@ -42083,7 +42093,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN MENU_DC;</v>
       </c>
     </row>
-    <row r="408" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="408" spans="2:35" ht="20" customHeight="1">
       <c r="B408" s="135">
         <v>381</v>
       </c>
@@ -42171,7 +42181,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN MENU_DETAIL_DC;</v>
       </c>
     </row>
-    <row r="409" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="409" spans="2:35" ht="20" customHeight="1">
       <c r="B409" s="55">
         <v>382</v>
       </c>
@@ -42263,7 +42273,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN NEW_WINDOW_YN;</v>
       </c>
     </row>
-    <row r="410" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="410" spans="2:35" ht="20" customHeight="1">
       <c r="B410" s="55">
         <v>383</v>
       </c>
@@ -42361,7 +42371,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN ATCH_FILE_SN;</v>
       </c>
     </row>
-    <row r="411" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="411" spans="2:35" ht="20" customHeight="1">
       <c r="B411" s="55">
         <v>384</v>
       </c>
@@ -42451,7 +42461,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN USE_YN;</v>
       </c>
     </row>
-    <row r="412" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="412" spans="2:35" ht="20" customHeight="1">
       <c r="B412" s="135">
         <v>385</v>
       </c>
@@ -42543,7 +42553,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="413" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="413" spans="2:35" ht="20" customHeight="1">
       <c r="B413" s="55">
         <v>386</v>
       </c>
@@ -42633,7 +42643,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="414" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="414" spans="2:35" ht="20" customHeight="1">
       <c r="B414" s="55">
         <v>387</v>
       </c>
@@ -42721,7 +42731,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="415" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="415" spans="2:35" ht="20" customHeight="1">
       <c r="B415" s="55">
         <v>388</v>
       </c>
@@ -42811,7 +42821,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="416" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="416" spans="2:35" ht="20" customHeight="1">
       <c r="B416" s="135">
         <v>389</v>
       </c>
@@ -42899,7 +42909,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="417" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="417" spans="2:35" ht="20" customHeight="1">
       <c r="B417" s="55">
         <v>390</v>
       </c>
@@ -42985,7 +42995,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="418" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="418" spans="2:35" ht="20" customHeight="1">
       <c r="B418" s="55">
         <v>391</v>
       </c>
@@ -43077,7 +43087,7 @@
         <v>ALTER TABLE TB_MENU DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="419" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="419" spans="2:35" ht="20" customHeight="1">
       <c r="B419" s="55">
         <v>392</v>
       </c>
@@ -43170,7 +43180,7 @@
         <v>ALTER TABLE TB_MENU_ROLE DROP COLUMN MENU_ROLE_SN;</v>
       </c>
     </row>
-    <row r="420" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="420" spans="2:35" ht="20" customHeight="1">
       <c r="B420" s="135">
         <v>393</v>
       </c>
@@ -43268,7 +43278,7 @@
         <v>ALTER TABLE TB_MENU_ROLE DROP COLUMN MENU_SN;</v>
       </c>
     </row>
-    <row r="421" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="421" spans="2:35" ht="20" customHeight="1">
       <c r="B421" s="55">
         <v>394</v>
       </c>
@@ -43366,7 +43376,7 @@
         <v>ALTER TABLE TB_MENU_ROLE DROP COLUMN ROLE_SN;</v>
       </c>
     </row>
-    <row r="422" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="422" spans="2:35" ht="20" customHeight="1">
       <c r="B422" s="55">
         <v>395</v>
       </c>
@@ -43458,7 +43468,7 @@
         <v>ALTER TABLE TB_MENU_ROLE DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="423" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="423" spans="2:35" ht="20" customHeight="1">
       <c r="B423" s="55">
         <v>396</v>
       </c>
@@ -43548,7 +43558,7 @@
         <v>ALTER TABLE TB_MENU_ROLE DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="424" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="424" spans="2:35" ht="20" customHeight="1">
       <c r="B424" s="135">
         <v>397</v>
       </c>
@@ -43636,7 +43646,7 @@
         <v>ALTER TABLE TB_MENU_ROLE DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="425" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="425" spans="2:35" ht="20" customHeight="1">
       <c r="B425" s="55">
         <v>398</v>
       </c>
@@ -43726,7 +43736,7 @@
         <v>ALTER TABLE TB_MENU_ROLE DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="426" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="426" spans="2:35" ht="20" customHeight="1">
       <c r="B426" s="55">
         <v>399</v>
       </c>
@@ -43814,7 +43824,7 @@
         <v>ALTER TABLE TB_MENU_ROLE DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="427" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="427" spans="2:35" ht="20" customHeight="1">
       <c r="B427" s="55">
         <v>400</v>
       </c>
@@ -43900,7 +43910,7 @@
         <v>ALTER TABLE TB_MENU_ROLE DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="428" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="428" spans="2:35" ht="20" customHeight="1">
       <c r="B428" s="135">
         <v>401</v>
       </c>
@@ -43992,7 +44002,7 @@
         <v>ALTER TABLE TB_MENU_ROLE DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="429" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="429" spans="2:35" ht="20" customHeight="1">
       <c r="B429" s="55">
         <v>402</v>
       </c>
@@ -44085,7 +44095,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN CD_SN;</v>
       </c>
     </row>
-    <row r="430" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="430" spans="2:35" ht="20" customHeight="1">
       <c r="B430" s="55">
         <v>403</v>
       </c>
@@ -44177,7 +44187,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN CD_NM;</v>
       </c>
     </row>
-    <row r="431" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="431" spans="2:35" ht="20" customHeight="1">
       <c r="B431" s="55">
         <v>404</v>
       </c>
@@ -44263,7 +44273,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN CD_DC;</v>
       </c>
     </row>
-    <row r="432" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="432" spans="2:35" ht="20" customHeight="1">
       <c r="B432" s="135">
         <v>405</v>
       </c>
@@ -44351,7 +44361,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN CD_VAL1;</v>
       </c>
     </row>
-    <row r="433" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="433" spans="2:35" ht="20" customHeight="1">
       <c r="B433" s="55">
         <v>406</v>
       </c>
@@ -44439,7 +44449,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN CD_VAL2;</v>
       </c>
     </row>
-    <row r="434" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="434" spans="2:35" ht="20" customHeight="1">
       <c r="B434" s="55">
         <v>407</v>
       </c>
@@ -44527,7 +44537,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN CD_VAL3;</v>
       </c>
     </row>
-    <row r="435" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="435" spans="2:35" ht="20" customHeight="1">
       <c r="B435" s="55">
         <v>408</v>
       </c>
@@ -44615,7 +44625,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN CD_VAL4;</v>
       </c>
     </row>
-    <row r="436" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="436" spans="2:35" ht="20" customHeight="1">
       <c r="B436" s="135">
         <v>409</v>
       </c>
@@ -44703,7 +44713,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN CD_VAL5;</v>
       </c>
     </row>
-    <row r="437" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="437" spans="2:35" ht="20" customHeight="1">
       <c r="B437" s="55">
         <v>410</v>
       </c>
@@ -44793,7 +44803,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN USE_YN;</v>
       </c>
     </row>
-    <row r="438" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="438" spans="2:35" ht="20" customHeight="1">
       <c r="B438" s="55">
         <v>411</v>
       </c>
@@ -44885,7 +44895,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN SYS_ESSNTL_CMMN_YN;</v>
       </c>
     </row>
-    <row r="439" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="439" spans="2:35" ht="20" customHeight="1">
       <c r="B439" s="55">
         <v>412</v>
       </c>
@@ -44975,7 +44985,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN CL_CD;</v>
       </c>
     </row>
-    <row r="440" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="440" spans="2:35" ht="20" customHeight="1">
       <c r="B440" s="135">
         <v>413</v>
       </c>
@@ -45061,7 +45071,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN REMARK;</v>
       </c>
     </row>
-    <row r="441" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="441" spans="2:35" ht="20" customHeight="1">
       <c r="B441" s="55">
         <v>414</v>
       </c>
@@ -45153,7 +45163,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="442" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="442" spans="2:35" ht="20" customHeight="1">
       <c r="B442" s="55">
         <v>415</v>
       </c>
@@ -45243,7 +45253,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="443" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="443" spans="2:35" ht="20" customHeight="1">
       <c r="B443" s="55">
         <v>416</v>
       </c>
@@ -45331,7 +45341,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="444" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="444" spans="2:35" ht="20" customHeight="1">
       <c r="B444" s="135">
         <v>417</v>
       </c>
@@ -45421,7 +45431,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="445" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="445" spans="2:35" ht="20" customHeight="1">
       <c r="B445" s="55">
         <v>418</v>
       </c>
@@ -45509,7 +45519,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="446" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="446" spans="2:35" ht="20" customHeight="1">
       <c r="B446" s="55">
         <v>419</v>
       </c>
@@ -45595,7 +45605,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="447" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="447" spans="2:35" ht="20" customHeight="1">
       <c r="B447" s="55">
         <v>420</v>
       </c>
@@ -45687,7 +45697,7 @@
         <v>ALTER TABLE TB_CMMN_CD DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="448" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="448" spans="2:35" ht="20" customHeight="1">
       <c r="B448" s="135">
         <v>421</v>
       </c>
@@ -45780,7 +45790,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN CD_DETAIL_SN;</v>
       </c>
     </row>
-    <row r="449" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="449" spans="2:35" ht="20" customHeight="1">
       <c r="B449" s="55">
         <v>422</v>
       </c>
@@ -45872,7 +45882,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN CD_NM;</v>
       </c>
     </row>
-    <row r="450" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="450" spans="2:35" ht="20" customHeight="1">
       <c r="B450" s="55">
         <v>423</v>
       </c>
@@ -45958,7 +45968,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN CD_DETAIL_SEQ;</v>
       </c>
     </row>
-    <row r="451" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="451" spans="2:35" ht="20" customHeight="1">
       <c r="B451" s="55">
         <v>424</v>
       </c>
@@ -46048,7 +46058,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN CD_DETAIL_NM;</v>
       </c>
     </row>
-    <row r="452" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="452" spans="2:35" ht="20" customHeight="1">
       <c r="B452" s="135">
         <v>425</v>
       </c>
@@ -46134,7 +46144,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN CD_DETAIL_DC;</v>
       </c>
     </row>
-    <row r="453" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="453" spans="2:35" ht="20" customHeight="1">
       <c r="B453" s="55">
         <v>426</v>
       </c>
@@ -46224,7 +46234,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN CD_DETAIL_VAL1;</v>
       </c>
     </row>
-    <row r="454" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="454" spans="2:35" ht="20" customHeight="1">
       <c r="B454" s="55">
         <v>427</v>
       </c>
@@ -46314,7 +46324,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN CD_DETAIL_VAL2;</v>
       </c>
     </row>
-    <row r="455" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="455" spans="2:35" ht="20" customHeight="1">
       <c r="B455" s="55">
         <v>428</v>
       </c>
@@ -46404,7 +46414,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN CD_DETAIL_VAL3;</v>
       </c>
     </row>
-    <row r="456" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="456" spans="2:35" ht="20" customHeight="1">
       <c r="B456" s="135">
         <v>429</v>
       </c>
@@ -46494,7 +46504,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN CD_DETAIL_VAL4;</v>
       </c>
     </row>
-    <row r="457" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="457" spans="2:35" ht="20" customHeight="1">
       <c r="B457" s="55">
         <v>430</v>
       </c>
@@ -46584,7 +46594,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN CD_DETAIL_VAL5;</v>
       </c>
     </row>
-    <row r="458" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="458" spans="2:35" ht="20" customHeight="1">
       <c r="B458" s="55">
         <v>431</v>
       </c>
@@ -46670,7 +46680,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN REMARK;</v>
       </c>
     </row>
-    <row r="459" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="459" spans="2:35" ht="20" customHeight="1">
       <c r="B459" s="55">
         <v>432</v>
       </c>
@@ -46760,7 +46770,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN USE_YN;</v>
       </c>
     </row>
-    <row r="460" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="460" spans="2:35" ht="20" customHeight="1">
       <c r="B460" s="135">
         <v>433</v>
       </c>
@@ -46852,7 +46862,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="461" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="461" spans="2:35" ht="20" customHeight="1">
       <c r="B461" s="55">
         <v>434</v>
       </c>
@@ -46942,7 +46952,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="462" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="462" spans="2:35" ht="20" customHeight="1">
       <c r="B462" s="55">
         <v>435</v>
       </c>
@@ -47030,7 +47040,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="463" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="463" spans="2:35" ht="20" customHeight="1">
       <c r="B463" s="55">
         <v>436</v>
       </c>
@@ -47120,7 +47130,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="464" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="464" spans="2:35" ht="20" customHeight="1">
       <c r="B464" s="135">
         <v>437</v>
       </c>
@@ -47208,7 +47218,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="465" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="465" spans="2:35" ht="20" customHeight="1">
       <c r="B465" s="55">
         <v>438</v>
       </c>
@@ -47294,7 +47304,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="466" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="466" spans="2:35" ht="20" customHeight="1">
       <c r="B466" s="55">
         <v>439</v>
       </c>
@@ -47386,7 +47396,7 @@
         <v>ALTER TABLE TB_CMMN_CD_DETAIL DROP COLUMN DEL_YN;</v>
       </c>
     </row>
-    <row r="467" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="467" spans="2:35" ht="20" customHeight="1">
       <c r="B467" s="55">
         <v>440</v>
       </c>
@@ -47479,7 +47489,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN BANNER_SN;</v>
       </c>
     </row>
-    <row r="468" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="468" spans="2:35" ht="20" customHeight="1">
       <c r="B468" s="135">
         <v>441</v>
       </c>
@@ -47571,7 +47581,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN BANNER_CL_CD;</v>
       </c>
     </row>
-    <row r="469" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="469" spans="2:35" ht="20" customHeight="1">
       <c r="B469" s="55">
         <v>442</v>
       </c>
@@ -47661,7 +47671,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN BANNER_CL_DETAIL_CD;</v>
       </c>
     </row>
-    <row r="470" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="470" spans="2:35" ht="20" customHeight="1">
       <c r="B470" s="55">
         <v>443</v>
       </c>
@@ -47749,7 +47759,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN BANNER_EXPSR_SEQ;</v>
       </c>
     </row>
-    <row r="471" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="471" spans="2:35" ht="20" customHeight="1">
       <c r="B471" s="55">
         <v>444</v>
       </c>
@@ -47837,7 +47847,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN BANNER_NM;</v>
       </c>
     </row>
-    <row r="472" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="472" spans="2:35" ht="20" customHeight="1">
       <c r="B472" s="135">
         <v>445</v>
       </c>
@@ -47923,7 +47933,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN BANNER_DC;</v>
       </c>
     </row>
-    <row r="473" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="473" spans="2:35" ht="20" customHeight="1">
       <c r="B473" s="55">
         <v>446</v>
       </c>
@@ -48019,7 +48029,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN ATCH_FILE_SN;</v>
       </c>
     </row>
-    <row r="474" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="474" spans="2:35" ht="20" customHeight="1">
       <c r="B474" s="55">
         <v>447</v>
       </c>
@@ -48107,7 +48117,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN URL;</v>
       </c>
     </row>
-    <row r="475" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="475" spans="2:35" ht="20" customHeight="1">
       <c r="B475" s="55">
         <v>448</v>
       </c>
@@ -48199,7 +48209,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN CLASS_MAPNG_YN;</v>
       </c>
     </row>
-    <row r="476" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="476" spans="2:35" ht="20" customHeight="1">
       <c r="B476" s="135">
         <v>449</v>
       </c>
@@ -48295,7 +48305,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN CLASS_SN;</v>
       </c>
     </row>
-    <row r="477" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="477" spans="2:35" ht="20" customHeight="1">
       <c r="B477" s="55">
         <v>450</v>
       </c>
@@ -48385,7 +48395,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN USE_YN;</v>
       </c>
     </row>
-    <row r="478" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="478" spans="2:35" ht="20" customHeight="1">
       <c r="B478" s="55">
         <v>451</v>
       </c>
@@ -48475,7 +48485,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN BANNER_PD_SET_YN;</v>
       </c>
     </row>
-    <row r="479" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="479" spans="2:35" ht="20" customHeight="1">
       <c r="B479" s="55">
         <v>452</v>
       </c>
@@ -48563,7 +48573,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN BANNER_BEGIN_DT;</v>
       </c>
     </row>
-    <row r="480" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="480" spans="2:35" ht="20" customHeight="1">
       <c r="B480" s="135">
         <v>453</v>
       </c>
@@ -48651,7 +48661,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN BANNER_END_DT;</v>
       </c>
     </row>
-    <row r="481" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="481" spans="2:35" ht="20" customHeight="1">
       <c r="B481" s="55">
         <v>454</v>
       </c>
@@ -48741,7 +48751,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN REGISTER_ID;</v>
       </c>
     </row>
-    <row r="482" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="482" spans="2:35" ht="20" customHeight="1">
       <c r="B482" s="55">
         <v>455</v>
       </c>
@@ -48831,7 +48841,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN REGISTER_IP;</v>
       </c>
     </row>
-    <row r="483" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="483" spans="2:35" ht="20" customHeight="1">
       <c r="B483" s="55">
         <v>456</v>
       </c>
@@ -48919,7 +48929,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN REG_DT;</v>
       </c>
     </row>
-    <row r="484" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="484" spans="2:35" ht="20" customHeight="1">
       <c r="B484" s="135">
         <v>457</v>
       </c>
@@ -49007,7 +49017,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN UPDUSR_ID;</v>
       </c>
     </row>
-    <row r="485" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="485" spans="2:35" ht="20" customHeight="1">
       <c r="B485" s="55">
         <v>458</v>
       </c>
@@ -49095,7 +49105,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN UPDUSR_IP;</v>
       </c>
     </row>
-    <row r="486" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="486" spans="2:35" ht="20" customHeight="1">
       <c r="B486" s="55">
         <v>459</v>
       </c>
@@ -49181,7 +49191,7 @@
         <v>ALTER TABLE TB_BANNER DROP COLUMN UPDT_DT;</v>
       </c>
     </row>
-    <row r="487" spans="2:35" ht="20.100000000000001" customHeight="1">
+    <row r="487" spans="2:35" ht="20" customHeight="1">
       <c r="B487" s="55">
         <v>460</v>
       </c>
@@ -49385,677 +49395,324 @@
         <v>ALTER TABLE  DROP COLUMN ;</v>
       </c>
     </row>
-    <row r="512" spans="2:24">
-      <c r="B512" s="124"/>
-      <c r="J512" s="124"/>
-      <c r="K512" s="124"/>
-      <c r="L512" s="124"/>
-      <c r="M512" s="124"/>
-      <c r="N512" s="124"/>
-      <c r="O512" s="124"/>
-      <c r="P512" s="124"/>
-      <c r="Q512" s="124"/>
-      <c r="R512" s="124"/>
-      <c r="S512" s="124"/>
-      <c r="T512" s="124"/>
-      <c r="W512" s="124"/>
-      <c r="X512" s="124"/>
-    </row>
-    <row r="513" spans="2:24">
-      <c r="B513" s="124"/>
+    <row r="512" spans="3:9" s="124" customFormat="1">
+      <c r="C512" s="84"/>
+      <c r="D512" s="84"/>
+      <c r="E512" s="88"/>
+      <c r="F512" s="88"/>
+      <c r="G512" s="89"/>
+      <c r="H512" s="88"/>
+      <c r="I512" s="88"/>
+    </row>
+    <row r="513" spans="3:9" s="124" customFormat="1">
       <c r="C513" s="111"/>
       <c r="D513" s="112"/>
       <c r="E513" s="113"/>
       <c r="F513" s="113"/>
-      <c r="J513" s="124"/>
-      <c r="K513" s="124"/>
-      <c r="L513" s="124"/>
-      <c r="M513" s="124"/>
-      <c r="N513" s="124"/>
-      <c r="O513" s="124"/>
-      <c r="P513" s="124"/>
-      <c r="Q513" s="124"/>
-      <c r="R513" s="124"/>
-      <c r="S513" s="124"/>
-      <c r="T513" s="124"/>
-      <c r="W513" s="124"/>
-      <c r="X513" s="124"/>
-    </row>
-    <row r="514" spans="2:24">
-      <c r="B514" s="124"/>
+      <c r="G513" s="89"/>
+      <c r="H513" s="88"/>
+      <c r="I513" s="88"/>
+    </row>
+    <row r="514" spans="3:9" s="124" customFormat="1">
       <c r="C514" s="111"/>
       <c r="D514" s="112"/>
       <c r="E514" s="113"/>
       <c r="F514" s="113"/>
-      <c r="J514" s="124"/>
-      <c r="K514" s="124"/>
-      <c r="L514" s="124"/>
-      <c r="M514" s="124"/>
-      <c r="N514" s="124"/>
-      <c r="O514" s="124"/>
-      <c r="P514" s="124"/>
-      <c r="Q514" s="124"/>
-      <c r="R514" s="124"/>
-      <c r="S514" s="124"/>
-      <c r="T514" s="124"/>
-      <c r="W514" s="124"/>
-      <c r="X514" s="124"/>
-    </row>
-    <row r="515" spans="2:24">
-      <c r="B515" s="124"/>
+      <c r="G514" s="89"/>
+      <c r="H514" s="88"/>
+      <c r="I514" s="88"/>
+    </row>
+    <row r="515" spans="3:9" s="124" customFormat="1">
       <c r="C515" s="111"/>
       <c r="D515" s="112"/>
       <c r="E515" s="113"/>
       <c r="F515" s="113"/>
-      <c r="J515" s="124"/>
-      <c r="K515" s="124"/>
-      <c r="L515" s="124"/>
-      <c r="M515" s="124"/>
-      <c r="N515" s="124"/>
-      <c r="O515" s="124"/>
-      <c r="P515" s="124"/>
-      <c r="Q515" s="124"/>
-      <c r="R515" s="124"/>
-      <c r="S515" s="124"/>
-      <c r="T515" s="124"/>
-      <c r="W515" s="124"/>
-      <c r="X515" s="124"/>
-    </row>
-    <row r="516" spans="2:24">
-      <c r="B516" s="124"/>
+      <c r="G515" s="89"/>
+      <c r="H515" s="88"/>
+      <c r="I515" s="88"/>
+    </row>
+    <row r="516" spans="3:9" s="124" customFormat="1">
       <c r="C516" s="111"/>
       <c r="D516" s="112"/>
       <c r="E516" s="21"/>
       <c r="F516" s="21"/>
-      <c r="J516" s="124"/>
-      <c r="K516" s="124"/>
-      <c r="L516" s="124"/>
-      <c r="M516" s="124"/>
-      <c r="N516" s="124"/>
-      <c r="O516" s="124"/>
-      <c r="P516" s="124"/>
-      <c r="Q516" s="124"/>
-      <c r="R516" s="124"/>
-      <c r="S516" s="124"/>
-      <c r="T516" s="124"/>
-      <c r="W516" s="124"/>
-      <c r="X516" s="124"/>
-    </row>
-    <row r="517" spans="2:24">
-      <c r="B517" s="124"/>
+      <c r="G516" s="89"/>
+      <c r="H516" s="88"/>
+      <c r="I516" s="88"/>
+    </row>
+    <row r="517" spans="3:9" s="124" customFormat="1">
       <c r="C517" s="111"/>
       <c r="D517" s="112"/>
       <c r="E517" s="114"/>
       <c r="F517" s="114"/>
-      <c r="J517" s="124"/>
-      <c r="K517" s="124"/>
-      <c r="L517" s="124"/>
-      <c r="M517" s="124"/>
-      <c r="N517" s="124"/>
-      <c r="O517" s="124"/>
-      <c r="P517" s="124"/>
-      <c r="Q517" s="124"/>
-      <c r="R517" s="124"/>
-      <c r="S517" s="124"/>
-      <c r="T517" s="124"/>
-      <c r="W517" s="124"/>
-      <c r="X517" s="124"/>
-    </row>
-    <row r="518" spans="2:24">
-      <c r="B518" s="124"/>
+      <c r="G517" s="89"/>
+      <c r="H517" s="88"/>
+      <c r="I517" s="88"/>
+    </row>
+    <row r="518" spans="3:9" s="124" customFormat="1">
       <c r="C518" s="111"/>
       <c r="D518" s="112"/>
       <c r="E518" s="114"/>
       <c r="F518" s="114"/>
-      <c r="J518" s="124"/>
-      <c r="K518" s="124"/>
-      <c r="L518" s="124"/>
-      <c r="M518" s="124"/>
-      <c r="N518" s="124"/>
-      <c r="O518" s="124"/>
-      <c r="P518" s="124"/>
-      <c r="Q518" s="124"/>
-      <c r="R518" s="124"/>
-      <c r="S518" s="124"/>
-      <c r="T518" s="124"/>
-      <c r="W518" s="124"/>
-      <c r="X518" s="124"/>
-    </row>
-    <row r="519" spans="2:24">
-      <c r="B519" s="124"/>
+      <c r="G518" s="89"/>
+      <c r="H518" s="88"/>
+      <c r="I518" s="88"/>
+    </row>
+    <row r="519" spans="3:9" s="124" customFormat="1">
       <c r="C519" s="111"/>
       <c r="D519" s="112"/>
       <c r="E519" s="114"/>
       <c r="F519" s="114"/>
-      <c r="J519" s="124"/>
-      <c r="K519" s="124"/>
-      <c r="L519" s="124"/>
-      <c r="M519" s="124"/>
-      <c r="N519" s="124"/>
-      <c r="O519" s="124"/>
-      <c r="P519" s="124"/>
-      <c r="Q519" s="124"/>
-      <c r="R519" s="124"/>
-      <c r="S519" s="124"/>
-      <c r="T519" s="124"/>
-      <c r="W519" s="124"/>
-      <c r="X519" s="124"/>
-    </row>
-    <row r="520" spans="2:24">
-      <c r="B520" s="124"/>
+      <c r="G519" s="89"/>
+      <c r="H519" s="88"/>
+      <c r="I519" s="88"/>
+    </row>
+    <row r="520" spans="3:9" s="124" customFormat="1">
       <c r="C520" s="111"/>
       <c r="D520" s="112"/>
       <c r="E520" s="114"/>
       <c r="F520" s="114"/>
-      <c r="J520" s="124"/>
-      <c r="K520" s="124"/>
-      <c r="L520" s="124"/>
-      <c r="M520" s="124"/>
-      <c r="N520" s="124"/>
-      <c r="O520" s="124"/>
-      <c r="P520" s="124"/>
-      <c r="Q520" s="124"/>
-      <c r="R520" s="124"/>
-      <c r="S520" s="124"/>
-      <c r="T520" s="124"/>
-      <c r="W520" s="124"/>
-      <c r="X520" s="124"/>
-    </row>
-    <row r="521" spans="2:24">
-      <c r="B521" s="124"/>
+      <c r="G520" s="89"/>
+      <c r="H520" s="88"/>
+      <c r="I520" s="88"/>
+    </row>
+    <row r="521" spans="3:9" s="124" customFormat="1">
       <c r="C521" s="111"/>
       <c r="D521" s="112"/>
       <c r="E521" s="114"/>
       <c r="F521" s="21"/>
-      <c r="J521" s="124"/>
-      <c r="K521" s="124"/>
-      <c r="L521" s="124"/>
-      <c r="M521" s="124"/>
-      <c r="N521" s="124"/>
-      <c r="O521" s="124"/>
-      <c r="P521" s="124"/>
-      <c r="Q521" s="124"/>
-      <c r="R521" s="124"/>
-      <c r="S521" s="124"/>
-      <c r="T521" s="124"/>
-      <c r="W521" s="124"/>
-      <c r="X521" s="124"/>
-    </row>
-    <row r="522" spans="2:24">
-      <c r="B522" s="124"/>
+      <c r="G521" s="89"/>
+      <c r="H521" s="88"/>
+      <c r="I521" s="88"/>
+    </row>
+    <row r="522" spans="3:9" s="124" customFormat="1">
       <c r="C522" s="111"/>
       <c r="D522" s="112"/>
       <c r="E522" s="114"/>
       <c r="F522" s="114"/>
-      <c r="J522" s="124"/>
-      <c r="K522" s="124"/>
-      <c r="L522" s="124"/>
-      <c r="M522" s="124"/>
-      <c r="N522" s="124"/>
-      <c r="O522" s="124"/>
-      <c r="P522" s="124"/>
-      <c r="Q522" s="124"/>
-      <c r="R522" s="124"/>
-      <c r="S522" s="124"/>
-      <c r="T522" s="124"/>
-      <c r="W522" s="124"/>
-      <c r="X522" s="124"/>
-    </row>
-    <row r="523" spans="2:24">
-      <c r="B523" s="124"/>
+      <c r="G522" s="89"/>
+      <c r="H522" s="88"/>
+      <c r="I522" s="88"/>
+    </row>
+    <row r="523" spans="3:9" s="124" customFormat="1">
       <c r="C523" s="111"/>
       <c r="D523" s="112"/>
       <c r="E523" s="21"/>
       <c r="F523" s="113"/>
-      <c r="J523" s="124"/>
-      <c r="K523" s="124"/>
-      <c r="L523" s="124"/>
-      <c r="M523" s="124"/>
-      <c r="N523" s="124"/>
-      <c r="O523" s="124"/>
-      <c r="P523" s="124"/>
-      <c r="Q523" s="124"/>
-      <c r="R523" s="124"/>
-      <c r="S523" s="124"/>
-      <c r="T523" s="124"/>
-      <c r="W523" s="124"/>
-      <c r="X523" s="124"/>
-    </row>
-    <row r="524" spans="2:24">
-      <c r="B524" s="124"/>
+      <c r="G523" s="89"/>
+      <c r="H523" s="88"/>
+      <c r="I523" s="88"/>
+    </row>
+    <row r="524" spans="3:9" s="124" customFormat="1">
       <c r="C524" s="111"/>
       <c r="D524" s="112"/>
       <c r="E524" s="21"/>
       <c r="F524" s="113"/>
-      <c r="J524" s="124"/>
-      <c r="K524" s="124"/>
-      <c r="L524" s="124"/>
-      <c r="M524" s="124"/>
-      <c r="N524" s="124"/>
-      <c r="O524" s="124"/>
-      <c r="P524" s="124"/>
-      <c r="Q524" s="124"/>
-      <c r="R524" s="124"/>
-      <c r="S524" s="124"/>
-      <c r="T524" s="124"/>
-      <c r="W524" s="124"/>
-      <c r="X524" s="124"/>
-    </row>
-    <row r="525" spans="2:24">
-      <c r="B525" s="124"/>
+      <c r="G524" s="89"/>
+      <c r="H524" s="88"/>
+      <c r="I524" s="88"/>
+    </row>
+    <row r="525" spans="3:9" s="124" customFormat="1">
       <c r="C525" s="111"/>
       <c r="D525" s="112"/>
       <c r="E525" s="21"/>
       <c r="F525" s="113"/>
-      <c r="J525" s="124"/>
-      <c r="K525" s="124"/>
-      <c r="L525" s="124"/>
-      <c r="M525" s="124"/>
-      <c r="N525" s="124"/>
-      <c r="O525" s="124"/>
-      <c r="P525" s="124"/>
-      <c r="Q525" s="124"/>
-      <c r="R525" s="124"/>
-      <c r="S525" s="124"/>
-      <c r="T525" s="124"/>
-      <c r="W525" s="124"/>
-      <c r="X525" s="124"/>
-    </row>
-    <row r="526" spans="2:24">
-      <c r="B526" s="124"/>
+      <c r="G525" s="89"/>
+      <c r="H525" s="88"/>
+      <c r="I525" s="88"/>
+    </row>
+    <row r="526" spans="3:9" s="124" customFormat="1">
       <c r="C526" s="111"/>
       <c r="D526" s="112"/>
       <c r="E526" s="114"/>
       <c r="F526" s="114"/>
-      <c r="J526" s="124"/>
-      <c r="K526" s="124"/>
-      <c r="L526" s="124"/>
-      <c r="M526" s="124"/>
-      <c r="N526" s="124"/>
-      <c r="O526" s="124"/>
-      <c r="P526" s="124"/>
-      <c r="Q526" s="124"/>
-      <c r="R526" s="124"/>
-      <c r="S526" s="124"/>
-      <c r="T526" s="124"/>
-      <c r="W526" s="124"/>
-      <c r="X526" s="124"/>
-    </row>
-    <row r="527" spans="2:24">
-      <c r="B527" s="124"/>
+      <c r="G526" s="89"/>
+      <c r="H526" s="88"/>
+      <c r="I526" s="88"/>
+    </row>
+    <row r="527" spans="3:9" s="124" customFormat="1">
       <c r="C527" s="111"/>
       <c r="D527" s="112"/>
       <c r="E527" s="21"/>
       <c r="F527" s="21"/>
-      <c r="J527" s="124"/>
-      <c r="K527" s="124"/>
-      <c r="L527" s="124"/>
-      <c r="M527" s="124"/>
-      <c r="N527" s="124"/>
-      <c r="O527" s="124"/>
-      <c r="P527" s="124"/>
-      <c r="Q527" s="124"/>
-      <c r="R527" s="124"/>
-      <c r="S527" s="124"/>
-      <c r="T527" s="124"/>
-      <c r="W527" s="124"/>
-      <c r="X527" s="124"/>
-    </row>
-    <row r="528" spans="2:24">
-      <c r="B528" s="124"/>
+      <c r="G527" s="89"/>
+      <c r="H527" s="88"/>
+      <c r="I527" s="88"/>
+    </row>
+    <row r="528" spans="3:9" s="124" customFormat="1">
       <c r="C528" s="111"/>
       <c r="D528" s="111"/>
       <c r="E528" s="21"/>
       <c r="F528" s="21"/>
-      <c r="J528" s="124"/>
-      <c r="K528" s="124"/>
-      <c r="L528" s="124"/>
-      <c r="M528" s="124"/>
-      <c r="N528" s="124"/>
-      <c r="O528" s="124"/>
-      <c r="P528" s="124"/>
-      <c r="Q528" s="124"/>
-      <c r="R528" s="124"/>
-      <c r="S528" s="124"/>
-      <c r="T528" s="124"/>
-      <c r="W528" s="124"/>
-      <c r="X528" s="124"/>
-    </row>
-    <row r="529" spans="2:24">
-      <c r="B529" s="124"/>
+      <c r="G528" s="89"/>
+      <c r="H528" s="88"/>
+      <c r="I528" s="88"/>
+    </row>
+    <row r="529" spans="3:9" s="124" customFormat="1">
       <c r="C529" s="111"/>
       <c r="D529" s="111"/>
       <c r="E529" s="21"/>
       <c r="F529" s="21"/>
-      <c r="J529" s="124"/>
-      <c r="K529" s="124"/>
-      <c r="L529" s="124"/>
-      <c r="M529" s="124"/>
-      <c r="N529" s="124"/>
-      <c r="O529" s="124"/>
-      <c r="P529" s="124"/>
-      <c r="Q529" s="124"/>
-      <c r="R529" s="124"/>
-      <c r="S529" s="124"/>
-      <c r="T529" s="124"/>
-      <c r="W529" s="124"/>
-      <c r="X529" s="124"/>
-    </row>
-    <row r="530" spans="2:24">
-      <c r="B530" s="124"/>
+      <c r="G529" s="89"/>
+      <c r="H529" s="88"/>
+      <c r="I529" s="88"/>
+    </row>
+    <row r="530" spans="3:9" s="124" customFormat="1">
       <c r="C530" s="111"/>
       <c r="D530" s="111"/>
       <c r="E530" s="21"/>
       <c r="F530" s="21"/>
-      <c r="J530" s="124"/>
-      <c r="K530" s="124"/>
-      <c r="L530" s="124"/>
-      <c r="M530" s="124"/>
-      <c r="N530" s="124"/>
-      <c r="O530" s="124"/>
-      <c r="P530" s="124"/>
-      <c r="Q530" s="124"/>
-      <c r="R530" s="124"/>
-      <c r="S530" s="124"/>
-      <c r="T530" s="124"/>
-      <c r="W530" s="124"/>
-      <c r="X530" s="124"/>
-    </row>
-    <row r="531" spans="2:24">
-      <c r="B531" s="124"/>
+      <c r="G530" s="89"/>
+      <c r="H530" s="88"/>
+      <c r="I530" s="88"/>
+    </row>
+    <row r="531" spans="3:9" s="124" customFormat="1">
       <c r="C531" s="111"/>
       <c r="D531" s="111"/>
       <c r="E531" s="21"/>
       <c r="F531" s="21"/>
-      <c r="J531" s="124"/>
-      <c r="K531" s="124"/>
-      <c r="L531" s="124"/>
-      <c r="M531" s="124"/>
-      <c r="N531" s="124"/>
-      <c r="O531" s="124"/>
-      <c r="P531" s="124"/>
-      <c r="Q531" s="124"/>
-      <c r="R531" s="124"/>
-      <c r="S531" s="124"/>
-      <c r="T531" s="124"/>
-      <c r="W531" s="124"/>
-      <c r="X531" s="124"/>
-    </row>
-    <row r="532" spans="2:24">
-      <c r="B532" s="124"/>
+      <c r="G531" s="89"/>
+      <c r="H531" s="88"/>
+      <c r="I531" s="88"/>
+    </row>
+    <row r="532" spans="3:9" s="124" customFormat="1">
       <c r="C532" s="111"/>
       <c r="D532" s="111"/>
       <c r="E532" s="21"/>
       <c r="F532" s="21"/>
-      <c r="J532" s="124"/>
-      <c r="K532" s="124"/>
-      <c r="L532" s="124"/>
-      <c r="M532" s="124"/>
-      <c r="N532" s="124"/>
-      <c r="O532" s="124"/>
-      <c r="P532" s="124"/>
-      <c r="Q532" s="124"/>
-      <c r="R532" s="124"/>
-      <c r="S532" s="124"/>
-      <c r="T532" s="124"/>
-      <c r="W532" s="124"/>
-      <c r="X532" s="124"/>
-    </row>
-    <row r="533" spans="2:24">
-      <c r="B533" s="124"/>
+      <c r="G532" s="89"/>
+      <c r="H532" s="88"/>
+      <c r="I532" s="88"/>
+    </row>
+    <row r="533" spans="3:9" s="124" customFormat="1">
       <c r="C533" s="111"/>
       <c r="D533" s="111"/>
       <c r="E533" s="21"/>
       <c r="F533" s="21"/>
-      <c r="J533" s="124"/>
-      <c r="K533" s="124"/>
-      <c r="L533" s="124"/>
-      <c r="M533" s="124"/>
-      <c r="N533" s="124"/>
-      <c r="O533" s="124"/>
-      <c r="P533" s="124"/>
-      <c r="Q533" s="124"/>
-      <c r="R533" s="124"/>
-      <c r="S533" s="124"/>
-      <c r="T533" s="124"/>
-      <c r="W533" s="124"/>
-      <c r="X533" s="124"/>
-    </row>
-    <row r="534" spans="2:24">
-      <c r="B534" s="124"/>
+      <c r="G533" s="89"/>
+      <c r="H533" s="88"/>
+      <c r="I533" s="88"/>
+    </row>
+    <row r="534" spans="3:9" s="124" customFormat="1">
       <c r="C534" s="111"/>
       <c r="D534" s="111"/>
       <c r="E534" s="21"/>
       <c r="F534" s="21"/>
-      <c r="J534" s="124"/>
-      <c r="K534" s="124"/>
-      <c r="L534" s="124"/>
-      <c r="M534" s="124"/>
-      <c r="N534" s="124"/>
-      <c r="O534" s="124"/>
-      <c r="P534" s="124"/>
-      <c r="Q534" s="124"/>
-      <c r="R534" s="124"/>
-      <c r="S534" s="124"/>
-      <c r="T534" s="124"/>
-      <c r="W534" s="124"/>
-      <c r="X534" s="124"/>
-    </row>
-    <row r="535" spans="2:24">
-      <c r="B535" s="124"/>
+      <c r="G534" s="89"/>
+      <c r="H534" s="88"/>
+      <c r="I534" s="88"/>
+    </row>
+    <row r="535" spans="3:9" s="124" customFormat="1">
       <c r="C535" s="111"/>
       <c r="D535" s="111"/>
       <c r="E535" s="21"/>
       <c r="F535" s="21"/>
-      <c r="J535" s="124"/>
-      <c r="K535" s="124"/>
-      <c r="L535" s="124"/>
-      <c r="M535" s="124"/>
-      <c r="N535" s="124"/>
-      <c r="O535" s="124"/>
-      <c r="P535" s="124"/>
-      <c r="Q535" s="124"/>
-      <c r="R535" s="124"/>
-      <c r="S535" s="124"/>
-      <c r="T535" s="124"/>
-      <c r="W535" s="124"/>
-      <c r="X535" s="124"/>
-    </row>
-    <row r="536" spans="2:24">
-      <c r="B536" s="124"/>
+      <c r="G535" s="89"/>
+      <c r="H535" s="88"/>
+      <c r="I535" s="88"/>
+    </row>
+    <row r="536" spans="3:9" s="124" customFormat="1">
       <c r="C536" s="111"/>
       <c r="D536" s="111"/>
       <c r="E536" s="21"/>
       <c r="F536" s="21"/>
-      <c r="J536" s="124"/>
-      <c r="K536" s="124"/>
-      <c r="L536" s="124"/>
-      <c r="M536" s="124"/>
-      <c r="N536" s="124"/>
-      <c r="O536" s="124"/>
-      <c r="P536" s="124"/>
-      <c r="Q536" s="124"/>
-      <c r="R536" s="124"/>
-      <c r="S536" s="124"/>
-      <c r="T536" s="124"/>
-      <c r="W536" s="124"/>
-      <c r="X536" s="124"/>
-    </row>
-    <row r="537" spans="2:24">
-      <c r="B537" s="124"/>
+      <c r="G536" s="89"/>
+      <c r="H536" s="88"/>
+      <c r="I536" s="88"/>
+    </row>
+    <row r="537" spans="3:9" s="124" customFormat="1">
       <c r="C537" s="111"/>
       <c r="D537" s="111"/>
       <c r="E537" s="21"/>
       <c r="F537" s="21"/>
-      <c r="J537" s="124"/>
-      <c r="K537" s="124"/>
-      <c r="L537" s="124"/>
-      <c r="M537" s="124"/>
-      <c r="N537" s="124"/>
-      <c r="O537" s="124"/>
-      <c r="P537" s="124"/>
-      <c r="Q537" s="124"/>
-      <c r="R537" s="124"/>
-      <c r="S537" s="124"/>
-      <c r="T537" s="124"/>
-      <c r="W537" s="124"/>
-      <c r="X537" s="124"/>
-    </row>
-    <row r="538" spans="2:24">
-      <c r="B538" s="124"/>
+      <c r="G537" s="89"/>
+      <c r="H537" s="88"/>
+      <c r="I537" s="88"/>
+    </row>
+    <row r="538" spans="3:9" s="124" customFormat="1">
       <c r="C538" s="111"/>
       <c r="D538" s="111"/>
       <c r="E538" s="21"/>
       <c r="F538" s="21"/>
-      <c r="J538" s="124"/>
-      <c r="K538" s="124"/>
-      <c r="L538" s="124"/>
-      <c r="M538" s="124"/>
-      <c r="N538" s="124"/>
-      <c r="O538" s="124"/>
-      <c r="P538" s="124"/>
-      <c r="Q538" s="124"/>
-      <c r="R538" s="124"/>
-      <c r="S538" s="124"/>
-      <c r="T538" s="124"/>
-      <c r="W538" s="124"/>
-      <c r="X538" s="124"/>
-    </row>
-    <row r="539" spans="2:24">
-      <c r="B539" s="124"/>
+      <c r="G538" s="89"/>
+      <c r="H538" s="88"/>
+      <c r="I538" s="88"/>
+    </row>
+    <row r="539" spans="3:9" s="124" customFormat="1">
       <c r="C539" s="111"/>
       <c r="D539" s="111"/>
       <c r="E539" s="5"/>
       <c r="F539" s="115"/>
-      <c r="J539" s="124"/>
-      <c r="K539" s="124"/>
-      <c r="L539" s="124"/>
-      <c r="M539" s="124"/>
-      <c r="N539" s="124"/>
-      <c r="O539" s="124"/>
-      <c r="P539" s="124"/>
-      <c r="Q539" s="124"/>
-      <c r="R539" s="124"/>
-      <c r="S539" s="124"/>
-      <c r="T539" s="124"/>
-      <c r="W539" s="124"/>
-      <c r="X539" s="124"/>
-    </row>
-    <row r="540" spans="2:24">
-      <c r="B540" s="124"/>
-      <c r="J540" s="124"/>
-      <c r="K540" s="124"/>
-      <c r="L540" s="124"/>
-      <c r="M540" s="124"/>
-      <c r="N540" s="124"/>
-      <c r="O540" s="124"/>
-      <c r="P540" s="124"/>
-      <c r="Q540" s="124"/>
-      <c r="R540" s="124"/>
-      <c r="S540" s="124"/>
-      <c r="T540" s="124"/>
-      <c r="W540" s="124"/>
-      <c r="X540" s="124"/>
-    </row>
-    <row r="541" spans="2:24">
-      <c r="B541" s="124"/>
-      <c r="J541" s="124"/>
-      <c r="K541" s="124"/>
-      <c r="L541" s="124"/>
-      <c r="M541" s="124"/>
-      <c r="N541" s="124"/>
-      <c r="O541" s="124"/>
-      <c r="P541" s="124"/>
-      <c r="Q541" s="124"/>
-      <c r="R541" s="124"/>
-      <c r="S541" s="124"/>
-      <c r="T541" s="124"/>
-      <c r="W541" s="124"/>
-      <c r="X541" s="124"/>
-    </row>
-    <row r="542" spans="2:24">
-      <c r="B542" s="124"/>
-      <c r="J542" s="124"/>
-      <c r="K542" s="124"/>
-      <c r="L542" s="124"/>
-      <c r="M542" s="124"/>
-      <c r="N542" s="124"/>
-      <c r="O542" s="124"/>
-      <c r="P542" s="124"/>
-      <c r="Q542" s="124"/>
-      <c r="R542" s="124"/>
-      <c r="S542" s="124"/>
-      <c r="T542" s="124"/>
-      <c r="W542" s="124"/>
-      <c r="X542" s="124"/>
-    </row>
-    <row r="543" spans="2:24">
-      <c r="B543" s="124"/>
-      <c r="J543" s="124"/>
-      <c r="K543" s="124"/>
-      <c r="L543" s="124"/>
-      <c r="M543" s="124"/>
-      <c r="N543" s="124"/>
-      <c r="O543" s="124"/>
-      <c r="P543" s="124"/>
-      <c r="Q543" s="124"/>
-      <c r="R543" s="124"/>
-      <c r="S543" s="124"/>
-      <c r="T543" s="124"/>
-      <c r="W543" s="124"/>
-      <c r="X543" s="124"/>
-    </row>
-    <row r="544" spans="2:24">
-      <c r="B544" s="124"/>
-      <c r="J544" s="124"/>
-      <c r="K544" s="124"/>
-      <c r="L544" s="124"/>
-      <c r="M544" s="124"/>
-      <c r="N544" s="124"/>
-      <c r="O544" s="124"/>
-      <c r="P544" s="124"/>
-      <c r="Q544" s="124"/>
-      <c r="R544" s="124"/>
-      <c r="S544" s="124"/>
-      <c r="T544" s="124"/>
-      <c r="W544" s="124"/>
-      <c r="X544" s="124"/>
-    </row>
-    <row r="545" spans="2:24">
-      <c r="B545" s="124"/>
-      <c r="J545" s="124"/>
-      <c r="K545" s="124"/>
-      <c r="L545" s="124"/>
-      <c r="M545" s="124"/>
-      <c r="N545" s="124"/>
-      <c r="O545" s="124"/>
-      <c r="P545" s="124"/>
-      <c r="Q545" s="124"/>
-      <c r="R545" s="124"/>
-      <c r="S545" s="124"/>
-      <c r="T545" s="124"/>
-      <c r="W545" s="124"/>
-      <c r="X545" s="124"/>
-    </row>
-    <row r="546" spans="2:24">
-      <c r="B546" s="124"/>
-      <c r="J546" s="124"/>
-      <c r="K546" s="124"/>
-      <c r="L546" s="124"/>
-      <c r="M546" s="124"/>
-      <c r="N546" s="124"/>
-      <c r="O546" s="124"/>
-      <c r="P546" s="124"/>
-      <c r="Q546" s="124"/>
-      <c r="R546" s="124"/>
-      <c r="S546" s="124"/>
-      <c r="T546" s="124"/>
-      <c r="W546" s="124"/>
-      <c r="X546" s="124"/>
+      <c r="G539" s="89"/>
+      <c r="H539" s="88"/>
+      <c r="I539" s="88"/>
+    </row>
+    <row r="540" spans="3:9" s="124" customFormat="1">
+      <c r="C540" s="84"/>
+      <c r="D540" s="84"/>
+      <c r="E540" s="88"/>
+      <c r="F540" s="88"/>
+      <c r="G540" s="89"/>
+      <c r="H540" s="88"/>
+      <c r="I540" s="88"/>
+    </row>
+    <row r="541" spans="3:9" s="124" customFormat="1">
+      <c r="C541" s="84"/>
+      <c r="D541" s="84"/>
+      <c r="E541" s="88"/>
+      <c r="F541" s="88"/>
+      <c r="G541" s="89"/>
+      <c r="H541" s="88"/>
+      <c r="I541" s="88"/>
+    </row>
+    <row r="542" spans="3:9" s="124" customFormat="1">
+      <c r="C542" s="84"/>
+      <c r="D542" s="84"/>
+      <c r="E542" s="88"/>
+      <c r="F542" s="88"/>
+      <c r="G542" s="89"/>
+      <c r="H542" s="88"/>
+      <c r="I542" s="88"/>
+    </row>
+    <row r="543" spans="3:9" s="124" customFormat="1">
+      <c r="C543" s="84"/>
+      <c r="D543" s="84"/>
+      <c r="E543" s="88"/>
+      <c r="F543" s="88"/>
+      <c r="G543" s="89"/>
+      <c r="H543" s="88"/>
+      <c r="I543" s="88"/>
+    </row>
+    <row r="544" spans="3:9" s="124" customFormat="1">
+      <c r="C544" s="84"/>
+      <c r="D544" s="84"/>
+      <c r="E544" s="88"/>
+      <c r="F544" s="88"/>
+      <c r="G544" s="89"/>
+      <c r="H544" s="88"/>
+      <c r="I544" s="88"/>
+    </row>
+    <row r="545" spans="3:9" s="124" customFormat="1">
+      <c r="C545" s="84"/>
+      <c r="D545" s="84"/>
+      <c r="E545" s="88"/>
+      <c r="F545" s="88"/>
+      <c r="G545" s="89"/>
+      <c r="H545" s="88"/>
+      <c r="I545" s="88"/>
+    </row>
+    <row r="546" spans="3:9" s="124" customFormat="1">
+      <c r="C546" s="84"/>
+      <c r="D546" s="84"/>
+      <c r="E546" s="88"/>
+      <c r="F546" s="88"/>
+      <c r="G546" s="89"/>
+      <c r="H546" s="88"/>
+      <c r="I546" s="88"/>
     </row>
   </sheetData>
   <autoFilter ref="B4:Y495" xr:uid="{85B6E963-2664-4494-AE6E-E89C8C9EB8F2}">
-    <sortState ref="B21:Y486">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B21:Y486">
       <sortCondition ref="B4:B487"/>
     </sortState>
   </autoFilter>
@@ -50075,9 +49732,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{347A98EC-0656-4264-90AF-D00CF14BBF94}">
   <dimension ref="A1:AH12"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:34" s="124" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="1" spans="1:34" s="124" customFormat="1" ht="20" customHeight="1">
       <c r="A1" s="55">
         <v>217</v>
       </c>
@@ -50169,7 +49826,7 @@
         <v>COMMENT ON COLUMN TB_LCTRE_REQST.DEL_YN IS '삭제 여부' ;</v>
       </c>
     </row>
-    <row r="2" spans="1:34" s="124" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="2" spans="1:34" s="124" customFormat="1" ht="20" customHeight="1">
       <c r="A2" s="55">
         <v>217</v>
       </c>
@@ -50221,7 +49878,7 @@
       <c r="AG2" s="50"/>
       <c r="AH2" s="50"/>
     </row>
-    <row r="3" spans="1:34" s="124" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="3" spans="1:34" s="124" customFormat="1" ht="20" customHeight="1">
       <c r="A3" s="55">
         <v>217</v>
       </c>
@@ -50273,7 +49930,7 @@
       <c r="AG3" s="50"/>
       <c r="AH3" s="50"/>
     </row>
-    <row r="4" spans="1:34" s="124" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="4" spans="1:34" s="124" customFormat="1" ht="20" customHeight="1">
       <c r="A4" s="55">
         <v>217</v>
       </c>
@@ -50325,7 +49982,7 @@
       <c r="AG4" s="50"/>
       <c r="AH4" s="50"/>
     </row>
-    <row r="5" spans="1:34" s="124" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="5" spans="1:34" s="124" customFormat="1" ht="20" customHeight="1">
       <c r="A5" s="55">
         <v>217</v>
       </c>
@@ -50377,7 +50034,7 @@
       <c r="AG5" s="50"/>
       <c r="AH5" s="50"/>
     </row>
-    <row r="6" spans="1:34" s="124" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="1:34" s="124" customFormat="1" ht="20" customHeight="1">
       <c r="A6" s="55">
         <v>217</v>
       </c>
@@ -50429,7 +50086,7 @@
       <c r="AG6" s="50"/>
       <c r="AH6" s="50"/>
     </row>
-    <row r="7" spans="1:34" s="124" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="7" spans="1:34" s="124" customFormat="1" ht="20" customHeight="1">
       <c r="A7" s="55">
         <v>217</v>
       </c>
@@ -50481,7 +50138,7 @@
       <c r="AG7" s="50"/>
       <c r="AH7" s="50"/>
     </row>
-    <row r="8" spans="1:34" s="124" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="8" spans="1:34" s="124" customFormat="1" ht="20" customHeight="1">
       <c r="A8" s="55">
         <v>217</v>
       </c>
@@ -50533,7 +50190,7 @@
       <c r="AG8" s="50"/>
       <c r="AH8" s="50"/>
     </row>
-    <row r="9" spans="1:34" s="124" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="9" spans="1:34" s="124" customFormat="1" ht="20" customHeight="1">
       <c r="A9" s="55">
         <v>217</v>
       </c>
@@ -50585,7 +50242,7 @@
       <c r="AG9" s="50"/>
       <c r="AH9" s="50"/>
     </row>
-    <row r="10" spans="1:34" s="124" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="10" spans="1:34" s="124" customFormat="1" ht="20" customHeight="1">
       <c r="A10" s="55">
         <v>217</v>
       </c>
@@ -50637,7 +50294,7 @@
       <c r="AG10" s="50"/>
       <c r="AH10" s="50"/>
     </row>
-    <row r="11" spans="1:34" s="124" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="11" spans="1:34" s="124" customFormat="1" ht="20" customHeight="1">
       <c r="A11" s="55">
         <v>217</v>
       </c>
@@ -50689,7 +50346,7 @@
       <c r="AG11" s="50"/>
       <c r="AH11" s="50"/>
     </row>
-    <row r="12" spans="1:34" s="124" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="12" spans="1:34" s="124" customFormat="1" ht="20" customHeight="1">
       <c r="A12" s="55">
         <v>217</v>
       </c>
@@ -50750,646 +50407,646 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q31"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="9.5" style="7" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="28.77734375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.1640625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="28.83203125" style="6" customWidth="1"/>
     <col min="6" max="6" width="39.6640625" style="7" customWidth="1"/>
-    <col min="7" max="7" width="35.44140625" style="5" customWidth="1"/>
-    <col min="8" max="253" width="8.77734375" style="5"/>
-    <col min="254" max="254" width="8.77734375" style="5" customWidth="1"/>
-    <col min="255" max="255" width="10.44140625" style="5" customWidth="1"/>
-    <col min="256" max="256" width="22.109375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="35.5" style="5" customWidth="1"/>
+    <col min="8" max="253" width="8.83203125" style="5"/>
+    <col min="254" max="254" width="8.83203125" style="5" customWidth="1"/>
+    <col min="255" max="255" width="10.5" style="5" customWidth="1"/>
+    <col min="256" max="256" width="22.1640625" style="5" customWidth="1"/>
     <col min="257" max="257" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="258" max="258" width="7.44140625" style="5" customWidth="1"/>
-    <col min="259" max="259" width="6.77734375" style="5" customWidth="1"/>
-    <col min="260" max="260" width="7.44140625" style="5" customWidth="1"/>
-    <col min="261" max="261" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="258" max="258" width="7.5" style="5" customWidth="1"/>
+    <col min="259" max="259" width="6.83203125" style="5" customWidth="1"/>
+    <col min="260" max="260" width="7.5" style="5" customWidth="1"/>
+    <col min="261" max="261" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="262" max="262" width="19.33203125" style="5" customWidth="1"/>
-    <col min="263" max="509" width="8.77734375" style="5"/>
-    <col min="510" max="510" width="8.77734375" style="5" customWidth="1"/>
-    <col min="511" max="511" width="10.44140625" style="5" customWidth="1"/>
-    <col min="512" max="512" width="22.109375" style="5" customWidth="1"/>
+    <col min="263" max="509" width="8.83203125" style="5"/>
+    <col min="510" max="510" width="8.83203125" style="5" customWidth="1"/>
+    <col min="511" max="511" width="10.5" style="5" customWidth="1"/>
+    <col min="512" max="512" width="22.1640625" style="5" customWidth="1"/>
     <col min="513" max="513" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="514" max="514" width="7.44140625" style="5" customWidth="1"/>
-    <col min="515" max="515" width="6.77734375" style="5" customWidth="1"/>
-    <col min="516" max="516" width="7.44140625" style="5" customWidth="1"/>
-    <col min="517" max="517" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="514" max="514" width="7.5" style="5" customWidth="1"/>
+    <col min="515" max="515" width="6.83203125" style="5" customWidth="1"/>
+    <col min="516" max="516" width="7.5" style="5" customWidth="1"/>
+    <col min="517" max="517" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="518" max="518" width="19.33203125" style="5" customWidth="1"/>
-    <col min="519" max="765" width="8.77734375" style="5"/>
-    <col min="766" max="766" width="8.77734375" style="5" customWidth="1"/>
-    <col min="767" max="767" width="10.44140625" style="5" customWidth="1"/>
-    <col min="768" max="768" width="22.109375" style="5" customWidth="1"/>
+    <col min="519" max="765" width="8.83203125" style="5"/>
+    <col min="766" max="766" width="8.83203125" style="5" customWidth="1"/>
+    <col min="767" max="767" width="10.5" style="5" customWidth="1"/>
+    <col min="768" max="768" width="22.1640625" style="5" customWidth="1"/>
     <col min="769" max="769" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="770" max="770" width="7.44140625" style="5" customWidth="1"/>
-    <col min="771" max="771" width="6.77734375" style="5" customWidth="1"/>
-    <col min="772" max="772" width="7.44140625" style="5" customWidth="1"/>
-    <col min="773" max="773" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="770" max="770" width="7.5" style="5" customWidth="1"/>
+    <col min="771" max="771" width="6.83203125" style="5" customWidth="1"/>
+    <col min="772" max="772" width="7.5" style="5" customWidth="1"/>
+    <col min="773" max="773" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="774" max="774" width="19.33203125" style="5" customWidth="1"/>
-    <col min="775" max="1021" width="8.77734375" style="5"/>
-    <col min="1022" max="1022" width="8.77734375" style="5" customWidth="1"/>
-    <col min="1023" max="1023" width="10.44140625" style="5" customWidth="1"/>
-    <col min="1024" max="1024" width="22.109375" style="5" customWidth="1"/>
+    <col min="775" max="1021" width="8.83203125" style="5"/>
+    <col min="1022" max="1022" width="8.83203125" style="5" customWidth="1"/>
+    <col min="1023" max="1023" width="10.5" style="5" customWidth="1"/>
+    <col min="1024" max="1024" width="22.1640625" style="5" customWidth="1"/>
     <col min="1025" max="1025" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="1026" max="1026" width="7.44140625" style="5" customWidth="1"/>
-    <col min="1027" max="1027" width="6.77734375" style="5" customWidth="1"/>
-    <col min="1028" max="1028" width="7.44140625" style="5" customWidth="1"/>
-    <col min="1029" max="1029" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="1026" max="1026" width="7.5" style="5" customWidth="1"/>
+    <col min="1027" max="1027" width="6.83203125" style="5" customWidth="1"/>
+    <col min="1028" max="1028" width="7.5" style="5" customWidth="1"/>
+    <col min="1029" max="1029" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="1030" max="1030" width="19.33203125" style="5" customWidth="1"/>
-    <col min="1031" max="1277" width="8.77734375" style="5"/>
-    <col min="1278" max="1278" width="8.77734375" style="5" customWidth="1"/>
-    <col min="1279" max="1279" width="10.44140625" style="5" customWidth="1"/>
-    <col min="1280" max="1280" width="22.109375" style="5" customWidth="1"/>
+    <col min="1031" max="1277" width="8.83203125" style="5"/>
+    <col min="1278" max="1278" width="8.83203125" style="5" customWidth="1"/>
+    <col min="1279" max="1279" width="10.5" style="5" customWidth="1"/>
+    <col min="1280" max="1280" width="22.1640625" style="5" customWidth="1"/>
     <col min="1281" max="1281" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="1282" max="1282" width="7.44140625" style="5" customWidth="1"/>
-    <col min="1283" max="1283" width="6.77734375" style="5" customWidth="1"/>
-    <col min="1284" max="1284" width="7.44140625" style="5" customWidth="1"/>
-    <col min="1285" max="1285" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="1282" max="1282" width="7.5" style="5" customWidth="1"/>
+    <col min="1283" max="1283" width="6.83203125" style="5" customWidth="1"/>
+    <col min="1284" max="1284" width="7.5" style="5" customWidth="1"/>
+    <col min="1285" max="1285" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="1286" max="1286" width="19.33203125" style="5" customWidth="1"/>
-    <col min="1287" max="1533" width="8.77734375" style="5"/>
-    <col min="1534" max="1534" width="8.77734375" style="5" customWidth="1"/>
-    <col min="1535" max="1535" width="10.44140625" style="5" customWidth="1"/>
-    <col min="1536" max="1536" width="22.109375" style="5" customWidth="1"/>
+    <col min="1287" max="1533" width="8.83203125" style="5"/>
+    <col min="1534" max="1534" width="8.83203125" style="5" customWidth="1"/>
+    <col min="1535" max="1535" width="10.5" style="5" customWidth="1"/>
+    <col min="1536" max="1536" width="22.1640625" style="5" customWidth="1"/>
     <col min="1537" max="1537" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="1538" max="1538" width="7.44140625" style="5" customWidth="1"/>
-    <col min="1539" max="1539" width="6.77734375" style="5" customWidth="1"/>
-    <col min="1540" max="1540" width="7.44140625" style="5" customWidth="1"/>
-    <col min="1541" max="1541" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="1538" max="1538" width="7.5" style="5" customWidth="1"/>
+    <col min="1539" max="1539" width="6.83203125" style="5" customWidth="1"/>
+    <col min="1540" max="1540" width="7.5" style="5" customWidth="1"/>
+    <col min="1541" max="1541" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="1542" max="1542" width="19.33203125" style="5" customWidth="1"/>
-    <col min="1543" max="1789" width="8.77734375" style="5"/>
-    <col min="1790" max="1790" width="8.77734375" style="5" customWidth="1"/>
-    <col min="1791" max="1791" width="10.44140625" style="5" customWidth="1"/>
-    <col min="1792" max="1792" width="22.109375" style="5" customWidth="1"/>
+    <col min="1543" max="1789" width="8.83203125" style="5"/>
+    <col min="1790" max="1790" width="8.83203125" style="5" customWidth="1"/>
+    <col min="1791" max="1791" width="10.5" style="5" customWidth="1"/>
+    <col min="1792" max="1792" width="22.1640625" style="5" customWidth="1"/>
     <col min="1793" max="1793" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="1794" max="1794" width="7.44140625" style="5" customWidth="1"/>
-    <col min="1795" max="1795" width="6.77734375" style="5" customWidth="1"/>
-    <col min="1796" max="1796" width="7.44140625" style="5" customWidth="1"/>
-    <col min="1797" max="1797" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="1794" max="1794" width="7.5" style="5" customWidth="1"/>
+    <col min="1795" max="1795" width="6.83203125" style="5" customWidth="1"/>
+    <col min="1796" max="1796" width="7.5" style="5" customWidth="1"/>
+    <col min="1797" max="1797" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="1798" max="1798" width="19.33203125" style="5" customWidth="1"/>
-    <col min="1799" max="2045" width="8.77734375" style="5"/>
-    <col min="2046" max="2046" width="8.77734375" style="5" customWidth="1"/>
-    <col min="2047" max="2047" width="10.44140625" style="5" customWidth="1"/>
-    <col min="2048" max="2048" width="22.109375" style="5" customWidth="1"/>
+    <col min="1799" max="2045" width="8.83203125" style="5"/>
+    <col min="2046" max="2046" width="8.83203125" style="5" customWidth="1"/>
+    <col min="2047" max="2047" width="10.5" style="5" customWidth="1"/>
+    <col min="2048" max="2048" width="22.1640625" style="5" customWidth="1"/>
     <col min="2049" max="2049" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2050" max="2050" width="7.44140625" style="5" customWidth="1"/>
-    <col min="2051" max="2051" width="6.77734375" style="5" customWidth="1"/>
-    <col min="2052" max="2052" width="7.44140625" style="5" customWidth="1"/>
-    <col min="2053" max="2053" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2050" max="2050" width="7.5" style="5" customWidth="1"/>
+    <col min="2051" max="2051" width="6.83203125" style="5" customWidth="1"/>
+    <col min="2052" max="2052" width="7.5" style="5" customWidth="1"/>
+    <col min="2053" max="2053" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="2054" max="2054" width="19.33203125" style="5" customWidth="1"/>
-    <col min="2055" max="2301" width="8.77734375" style="5"/>
-    <col min="2302" max="2302" width="8.77734375" style="5" customWidth="1"/>
-    <col min="2303" max="2303" width="10.44140625" style="5" customWidth="1"/>
-    <col min="2304" max="2304" width="22.109375" style="5" customWidth="1"/>
+    <col min="2055" max="2301" width="8.83203125" style="5"/>
+    <col min="2302" max="2302" width="8.83203125" style="5" customWidth="1"/>
+    <col min="2303" max="2303" width="10.5" style="5" customWidth="1"/>
+    <col min="2304" max="2304" width="22.1640625" style="5" customWidth="1"/>
     <col min="2305" max="2305" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2306" max="2306" width="7.44140625" style="5" customWidth="1"/>
-    <col min="2307" max="2307" width="6.77734375" style="5" customWidth="1"/>
-    <col min="2308" max="2308" width="7.44140625" style="5" customWidth="1"/>
-    <col min="2309" max="2309" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2306" max="2306" width="7.5" style="5" customWidth="1"/>
+    <col min="2307" max="2307" width="6.83203125" style="5" customWidth="1"/>
+    <col min="2308" max="2308" width="7.5" style="5" customWidth="1"/>
+    <col min="2309" max="2309" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="2310" max="2310" width="19.33203125" style="5" customWidth="1"/>
-    <col min="2311" max="2557" width="8.77734375" style="5"/>
-    <col min="2558" max="2558" width="8.77734375" style="5" customWidth="1"/>
-    <col min="2559" max="2559" width="10.44140625" style="5" customWidth="1"/>
-    <col min="2560" max="2560" width="22.109375" style="5" customWidth="1"/>
+    <col min="2311" max="2557" width="8.83203125" style="5"/>
+    <col min="2558" max="2558" width="8.83203125" style="5" customWidth="1"/>
+    <col min="2559" max="2559" width="10.5" style="5" customWidth="1"/>
+    <col min="2560" max="2560" width="22.1640625" style="5" customWidth="1"/>
     <col min="2561" max="2561" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2562" max="2562" width="7.44140625" style="5" customWidth="1"/>
-    <col min="2563" max="2563" width="6.77734375" style="5" customWidth="1"/>
-    <col min="2564" max="2564" width="7.44140625" style="5" customWidth="1"/>
-    <col min="2565" max="2565" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2562" max="2562" width="7.5" style="5" customWidth="1"/>
+    <col min="2563" max="2563" width="6.83203125" style="5" customWidth="1"/>
+    <col min="2564" max="2564" width="7.5" style="5" customWidth="1"/>
+    <col min="2565" max="2565" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="2566" max="2566" width="19.33203125" style="5" customWidth="1"/>
-    <col min="2567" max="2813" width="8.77734375" style="5"/>
-    <col min="2814" max="2814" width="8.77734375" style="5" customWidth="1"/>
-    <col min="2815" max="2815" width="10.44140625" style="5" customWidth="1"/>
-    <col min="2816" max="2816" width="22.109375" style="5" customWidth="1"/>
+    <col min="2567" max="2813" width="8.83203125" style="5"/>
+    <col min="2814" max="2814" width="8.83203125" style="5" customWidth="1"/>
+    <col min="2815" max="2815" width="10.5" style="5" customWidth="1"/>
+    <col min="2816" max="2816" width="22.1640625" style="5" customWidth="1"/>
     <col min="2817" max="2817" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2818" max="2818" width="7.44140625" style="5" customWidth="1"/>
-    <col min="2819" max="2819" width="6.77734375" style="5" customWidth="1"/>
-    <col min="2820" max="2820" width="7.44140625" style="5" customWidth="1"/>
-    <col min="2821" max="2821" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2818" max="2818" width="7.5" style="5" customWidth="1"/>
+    <col min="2819" max="2819" width="6.83203125" style="5" customWidth="1"/>
+    <col min="2820" max="2820" width="7.5" style="5" customWidth="1"/>
+    <col min="2821" max="2821" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="2822" max="2822" width="19.33203125" style="5" customWidth="1"/>
-    <col min="2823" max="3069" width="8.77734375" style="5"/>
-    <col min="3070" max="3070" width="8.77734375" style="5" customWidth="1"/>
-    <col min="3071" max="3071" width="10.44140625" style="5" customWidth="1"/>
-    <col min="3072" max="3072" width="22.109375" style="5" customWidth="1"/>
+    <col min="2823" max="3069" width="8.83203125" style="5"/>
+    <col min="3070" max="3070" width="8.83203125" style="5" customWidth="1"/>
+    <col min="3071" max="3071" width="10.5" style="5" customWidth="1"/>
+    <col min="3072" max="3072" width="22.1640625" style="5" customWidth="1"/>
     <col min="3073" max="3073" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3074" max="3074" width="7.44140625" style="5" customWidth="1"/>
-    <col min="3075" max="3075" width="6.77734375" style="5" customWidth="1"/>
-    <col min="3076" max="3076" width="7.44140625" style="5" customWidth="1"/>
-    <col min="3077" max="3077" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3074" max="3074" width="7.5" style="5" customWidth="1"/>
+    <col min="3075" max="3075" width="6.83203125" style="5" customWidth="1"/>
+    <col min="3076" max="3076" width="7.5" style="5" customWidth="1"/>
+    <col min="3077" max="3077" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="3078" max="3078" width="19.33203125" style="5" customWidth="1"/>
-    <col min="3079" max="3325" width="8.77734375" style="5"/>
-    <col min="3326" max="3326" width="8.77734375" style="5" customWidth="1"/>
-    <col min="3327" max="3327" width="10.44140625" style="5" customWidth="1"/>
-    <col min="3328" max="3328" width="22.109375" style="5" customWidth="1"/>
+    <col min="3079" max="3325" width="8.83203125" style="5"/>
+    <col min="3326" max="3326" width="8.83203125" style="5" customWidth="1"/>
+    <col min="3327" max="3327" width="10.5" style="5" customWidth="1"/>
+    <col min="3328" max="3328" width="22.1640625" style="5" customWidth="1"/>
     <col min="3329" max="3329" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3330" max="3330" width="7.44140625" style="5" customWidth="1"/>
-    <col min="3331" max="3331" width="6.77734375" style="5" customWidth="1"/>
-    <col min="3332" max="3332" width="7.44140625" style="5" customWidth="1"/>
-    <col min="3333" max="3333" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3330" max="3330" width="7.5" style="5" customWidth="1"/>
+    <col min="3331" max="3331" width="6.83203125" style="5" customWidth="1"/>
+    <col min="3332" max="3332" width="7.5" style="5" customWidth="1"/>
+    <col min="3333" max="3333" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="3334" max="3334" width="19.33203125" style="5" customWidth="1"/>
-    <col min="3335" max="3581" width="8.77734375" style="5"/>
-    <col min="3582" max="3582" width="8.77734375" style="5" customWidth="1"/>
-    <col min="3583" max="3583" width="10.44140625" style="5" customWidth="1"/>
-    <col min="3584" max="3584" width="22.109375" style="5" customWidth="1"/>
+    <col min="3335" max="3581" width="8.83203125" style="5"/>
+    <col min="3582" max="3582" width="8.83203125" style="5" customWidth="1"/>
+    <col min="3583" max="3583" width="10.5" style="5" customWidth="1"/>
+    <col min="3584" max="3584" width="22.1640625" style="5" customWidth="1"/>
     <col min="3585" max="3585" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3586" max="3586" width="7.44140625" style="5" customWidth="1"/>
-    <col min="3587" max="3587" width="6.77734375" style="5" customWidth="1"/>
-    <col min="3588" max="3588" width="7.44140625" style="5" customWidth="1"/>
-    <col min="3589" max="3589" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3586" max="3586" width="7.5" style="5" customWidth="1"/>
+    <col min="3587" max="3587" width="6.83203125" style="5" customWidth="1"/>
+    <col min="3588" max="3588" width="7.5" style="5" customWidth="1"/>
+    <col min="3589" max="3589" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="3590" max="3590" width="19.33203125" style="5" customWidth="1"/>
-    <col min="3591" max="3837" width="8.77734375" style="5"/>
-    <col min="3838" max="3838" width="8.77734375" style="5" customWidth="1"/>
-    <col min="3839" max="3839" width="10.44140625" style="5" customWidth="1"/>
-    <col min="3840" max="3840" width="22.109375" style="5" customWidth="1"/>
+    <col min="3591" max="3837" width="8.83203125" style="5"/>
+    <col min="3838" max="3838" width="8.83203125" style="5" customWidth="1"/>
+    <col min="3839" max="3839" width="10.5" style="5" customWidth="1"/>
+    <col min="3840" max="3840" width="22.1640625" style="5" customWidth="1"/>
     <col min="3841" max="3841" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3842" max="3842" width="7.44140625" style="5" customWidth="1"/>
-    <col min="3843" max="3843" width="6.77734375" style="5" customWidth="1"/>
-    <col min="3844" max="3844" width="7.44140625" style="5" customWidth="1"/>
-    <col min="3845" max="3845" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3842" max="3842" width="7.5" style="5" customWidth="1"/>
+    <col min="3843" max="3843" width="6.83203125" style="5" customWidth="1"/>
+    <col min="3844" max="3844" width="7.5" style="5" customWidth="1"/>
+    <col min="3845" max="3845" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="3846" max="3846" width="19.33203125" style="5" customWidth="1"/>
-    <col min="3847" max="4093" width="8.77734375" style="5"/>
-    <col min="4094" max="4094" width="8.77734375" style="5" customWidth="1"/>
-    <col min="4095" max="4095" width="10.44140625" style="5" customWidth="1"/>
-    <col min="4096" max="4096" width="22.109375" style="5" customWidth="1"/>
+    <col min="3847" max="4093" width="8.83203125" style="5"/>
+    <col min="4094" max="4094" width="8.83203125" style="5" customWidth="1"/>
+    <col min="4095" max="4095" width="10.5" style="5" customWidth="1"/>
+    <col min="4096" max="4096" width="22.1640625" style="5" customWidth="1"/>
     <col min="4097" max="4097" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4098" max="4098" width="7.44140625" style="5" customWidth="1"/>
-    <col min="4099" max="4099" width="6.77734375" style="5" customWidth="1"/>
-    <col min="4100" max="4100" width="7.44140625" style="5" customWidth="1"/>
-    <col min="4101" max="4101" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4098" max="4098" width="7.5" style="5" customWidth="1"/>
+    <col min="4099" max="4099" width="6.83203125" style="5" customWidth="1"/>
+    <col min="4100" max="4100" width="7.5" style="5" customWidth="1"/>
+    <col min="4101" max="4101" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="4102" max="4102" width="19.33203125" style="5" customWidth="1"/>
-    <col min="4103" max="4349" width="8.77734375" style="5"/>
-    <col min="4350" max="4350" width="8.77734375" style="5" customWidth="1"/>
-    <col min="4351" max="4351" width="10.44140625" style="5" customWidth="1"/>
-    <col min="4352" max="4352" width="22.109375" style="5" customWidth="1"/>
+    <col min="4103" max="4349" width="8.83203125" style="5"/>
+    <col min="4350" max="4350" width="8.83203125" style="5" customWidth="1"/>
+    <col min="4351" max="4351" width="10.5" style="5" customWidth="1"/>
+    <col min="4352" max="4352" width="22.1640625" style="5" customWidth="1"/>
     <col min="4353" max="4353" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4354" max="4354" width="7.44140625" style="5" customWidth="1"/>
-    <col min="4355" max="4355" width="6.77734375" style="5" customWidth="1"/>
-    <col min="4356" max="4356" width="7.44140625" style="5" customWidth="1"/>
-    <col min="4357" max="4357" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4354" max="4354" width="7.5" style="5" customWidth="1"/>
+    <col min="4355" max="4355" width="6.83203125" style="5" customWidth="1"/>
+    <col min="4356" max="4356" width="7.5" style="5" customWidth="1"/>
+    <col min="4357" max="4357" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="4358" max="4358" width="19.33203125" style="5" customWidth="1"/>
-    <col min="4359" max="4605" width="8.77734375" style="5"/>
-    <col min="4606" max="4606" width="8.77734375" style="5" customWidth="1"/>
-    <col min="4607" max="4607" width="10.44140625" style="5" customWidth="1"/>
-    <col min="4608" max="4608" width="22.109375" style="5" customWidth="1"/>
+    <col min="4359" max="4605" width="8.83203125" style="5"/>
+    <col min="4606" max="4606" width="8.83203125" style="5" customWidth="1"/>
+    <col min="4607" max="4607" width="10.5" style="5" customWidth="1"/>
+    <col min="4608" max="4608" width="22.1640625" style="5" customWidth="1"/>
     <col min="4609" max="4609" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4610" max="4610" width="7.44140625" style="5" customWidth="1"/>
-    <col min="4611" max="4611" width="6.77734375" style="5" customWidth="1"/>
-    <col min="4612" max="4612" width="7.44140625" style="5" customWidth="1"/>
-    <col min="4613" max="4613" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4610" max="4610" width="7.5" style="5" customWidth="1"/>
+    <col min="4611" max="4611" width="6.83203125" style="5" customWidth="1"/>
+    <col min="4612" max="4612" width="7.5" style="5" customWidth="1"/>
+    <col min="4613" max="4613" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="4614" max="4614" width="19.33203125" style="5" customWidth="1"/>
-    <col min="4615" max="4861" width="8.77734375" style="5"/>
-    <col min="4862" max="4862" width="8.77734375" style="5" customWidth="1"/>
-    <col min="4863" max="4863" width="10.44140625" style="5" customWidth="1"/>
-    <col min="4864" max="4864" width="22.109375" style="5" customWidth="1"/>
+    <col min="4615" max="4861" width="8.83203125" style="5"/>
+    <col min="4862" max="4862" width="8.83203125" style="5" customWidth="1"/>
+    <col min="4863" max="4863" width="10.5" style="5" customWidth="1"/>
+    <col min="4864" max="4864" width="22.1640625" style="5" customWidth="1"/>
     <col min="4865" max="4865" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4866" max="4866" width="7.44140625" style="5" customWidth="1"/>
-    <col min="4867" max="4867" width="6.77734375" style="5" customWidth="1"/>
-    <col min="4868" max="4868" width="7.44140625" style="5" customWidth="1"/>
-    <col min="4869" max="4869" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4866" max="4866" width="7.5" style="5" customWidth="1"/>
+    <col min="4867" max="4867" width="6.83203125" style="5" customWidth="1"/>
+    <col min="4868" max="4868" width="7.5" style="5" customWidth="1"/>
+    <col min="4869" max="4869" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="4870" max="4870" width="19.33203125" style="5" customWidth="1"/>
-    <col min="4871" max="5117" width="8.77734375" style="5"/>
-    <col min="5118" max="5118" width="8.77734375" style="5" customWidth="1"/>
-    <col min="5119" max="5119" width="10.44140625" style="5" customWidth="1"/>
-    <col min="5120" max="5120" width="22.109375" style="5" customWidth="1"/>
+    <col min="4871" max="5117" width="8.83203125" style="5"/>
+    <col min="5118" max="5118" width="8.83203125" style="5" customWidth="1"/>
+    <col min="5119" max="5119" width="10.5" style="5" customWidth="1"/>
+    <col min="5120" max="5120" width="22.1640625" style="5" customWidth="1"/>
     <col min="5121" max="5121" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5122" max="5122" width="7.44140625" style="5" customWidth="1"/>
-    <col min="5123" max="5123" width="6.77734375" style="5" customWidth="1"/>
-    <col min="5124" max="5124" width="7.44140625" style="5" customWidth="1"/>
-    <col min="5125" max="5125" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5122" max="5122" width="7.5" style="5" customWidth="1"/>
+    <col min="5123" max="5123" width="6.83203125" style="5" customWidth="1"/>
+    <col min="5124" max="5124" width="7.5" style="5" customWidth="1"/>
+    <col min="5125" max="5125" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="5126" max="5126" width="19.33203125" style="5" customWidth="1"/>
-    <col min="5127" max="5373" width="8.77734375" style="5"/>
-    <col min="5374" max="5374" width="8.77734375" style="5" customWidth="1"/>
-    <col min="5375" max="5375" width="10.44140625" style="5" customWidth="1"/>
-    <col min="5376" max="5376" width="22.109375" style="5" customWidth="1"/>
+    <col min="5127" max="5373" width="8.83203125" style="5"/>
+    <col min="5374" max="5374" width="8.83203125" style="5" customWidth="1"/>
+    <col min="5375" max="5375" width="10.5" style="5" customWidth="1"/>
+    <col min="5376" max="5376" width="22.1640625" style="5" customWidth="1"/>
     <col min="5377" max="5377" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5378" max="5378" width="7.44140625" style="5" customWidth="1"/>
-    <col min="5379" max="5379" width="6.77734375" style="5" customWidth="1"/>
-    <col min="5380" max="5380" width="7.44140625" style="5" customWidth="1"/>
-    <col min="5381" max="5381" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5378" max="5378" width="7.5" style="5" customWidth="1"/>
+    <col min="5379" max="5379" width="6.83203125" style="5" customWidth="1"/>
+    <col min="5380" max="5380" width="7.5" style="5" customWidth="1"/>
+    <col min="5381" max="5381" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="5382" max="5382" width="19.33203125" style="5" customWidth="1"/>
-    <col min="5383" max="5629" width="8.77734375" style="5"/>
-    <col min="5630" max="5630" width="8.77734375" style="5" customWidth="1"/>
-    <col min="5631" max="5631" width="10.44140625" style="5" customWidth="1"/>
-    <col min="5632" max="5632" width="22.109375" style="5" customWidth="1"/>
+    <col min="5383" max="5629" width="8.83203125" style="5"/>
+    <col min="5630" max="5630" width="8.83203125" style="5" customWidth="1"/>
+    <col min="5631" max="5631" width="10.5" style="5" customWidth="1"/>
+    <col min="5632" max="5632" width="22.1640625" style="5" customWidth="1"/>
     <col min="5633" max="5633" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5634" max="5634" width="7.44140625" style="5" customWidth="1"/>
-    <col min="5635" max="5635" width="6.77734375" style="5" customWidth="1"/>
-    <col min="5636" max="5636" width="7.44140625" style="5" customWidth="1"/>
-    <col min="5637" max="5637" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5634" max="5634" width="7.5" style="5" customWidth="1"/>
+    <col min="5635" max="5635" width="6.83203125" style="5" customWidth="1"/>
+    <col min="5636" max="5636" width="7.5" style="5" customWidth="1"/>
+    <col min="5637" max="5637" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="5638" max="5638" width="19.33203125" style="5" customWidth="1"/>
-    <col min="5639" max="5885" width="8.77734375" style="5"/>
-    <col min="5886" max="5886" width="8.77734375" style="5" customWidth="1"/>
-    <col min="5887" max="5887" width="10.44140625" style="5" customWidth="1"/>
-    <col min="5888" max="5888" width="22.109375" style="5" customWidth="1"/>
+    <col min="5639" max="5885" width="8.83203125" style="5"/>
+    <col min="5886" max="5886" width="8.83203125" style="5" customWidth="1"/>
+    <col min="5887" max="5887" width="10.5" style="5" customWidth="1"/>
+    <col min="5888" max="5888" width="22.1640625" style="5" customWidth="1"/>
     <col min="5889" max="5889" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5890" max="5890" width="7.44140625" style="5" customWidth="1"/>
-    <col min="5891" max="5891" width="6.77734375" style="5" customWidth="1"/>
-    <col min="5892" max="5892" width="7.44140625" style="5" customWidth="1"/>
-    <col min="5893" max="5893" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5890" max="5890" width="7.5" style="5" customWidth="1"/>
+    <col min="5891" max="5891" width="6.83203125" style="5" customWidth="1"/>
+    <col min="5892" max="5892" width="7.5" style="5" customWidth="1"/>
+    <col min="5893" max="5893" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="5894" max="5894" width="19.33203125" style="5" customWidth="1"/>
-    <col min="5895" max="6141" width="8.77734375" style="5"/>
-    <col min="6142" max="6142" width="8.77734375" style="5" customWidth="1"/>
-    <col min="6143" max="6143" width="10.44140625" style="5" customWidth="1"/>
-    <col min="6144" max="6144" width="22.109375" style="5" customWidth="1"/>
+    <col min="5895" max="6141" width="8.83203125" style="5"/>
+    <col min="6142" max="6142" width="8.83203125" style="5" customWidth="1"/>
+    <col min="6143" max="6143" width="10.5" style="5" customWidth="1"/>
+    <col min="6144" max="6144" width="22.1640625" style="5" customWidth="1"/>
     <col min="6145" max="6145" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6146" max="6146" width="7.44140625" style="5" customWidth="1"/>
-    <col min="6147" max="6147" width="6.77734375" style="5" customWidth="1"/>
-    <col min="6148" max="6148" width="7.44140625" style="5" customWidth="1"/>
-    <col min="6149" max="6149" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="6146" max="6146" width="7.5" style="5" customWidth="1"/>
+    <col min="6147" max="6147" width="6.83203125" style="5" customWidth="1"/>
+    <col min="6148" max="6148" width="7.5" style="5" customWidth="1"/>
+    <col min="6149" max="6149" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="6150" max="6150" width="19.33203125" style="5" customWidth="1"/>
-    <col min="6151" max="6397" width="8.77734375" style="5"/>
-    <col min="6398" max="6398" width="8.77734375" style="5" customWidth="1"/>
-    <col min="6399" max="6399" width="10.44140625" style="5" customWidth="1"/>
-    <col min="6400" max="6400" width="22.109375" style="5" customWidth="1"/>
+    <col min="6151" max="6397" width="8.83203125" style="5"/>
+    <col min="6398" max="6398" width="8.83203125" style="5" customWidth="1"/>
+    <col min="6399" max="6399" width="10.5" style="5" customWidth="1"/>
+    <col min="6400" max="6400" width="22.1640625" style="5" customWidth="1"/>
     <col min="6401" max="6401" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6402" max="6402" width="7.44140625" style="5" customWidth="1"/>
-    <col min="6403" max="6403" width="6.77734375" style="5" customWidth="1"/>
-    <col min="6404" max="6404" width="7.44140625" style="5" customWidth="1"/>
-    <col min="6405" max="6405" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="6402" max="6402" width="7.5" style="5" customWidth="1"/>
+    <col min="6403" max="6403" width="6.83203125" style="5" customWidth="1"/>
+    <col min="6404" max="6404" width="7.5" style="5" customWidth="1"/>
+    <col min="6405" max="6405" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="6406" max="6406" width="19.33203125" style="5" customWidth="1"/>
-    <col min="6407" max="6653" width="8.77734375" style="5"/>
-    <col min="6654" max="6654" width="8.77734375" style="5" customWidth="1"/>
-    <col min="6655" max="6655" width="10.44140625" style="5" customWidth="1"/>
-    <col min="6656" max="6656" width="22.109375" style="5" customWidth="1"/>
+    <col min="6407" max="6653" width="8.83203125" style="5"/>
+    <col min="6654" max="6654" width="8.83203125" style="5" customWidth="1"/>
+    <col min="6655" max="6655" width="10.5" style="5" customWidth="1"/>
+    <col min="6656" max="6656" width="22.1640625" style="5" customWidth="1"/>
     <col min="6657" max="6657" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6658" max="6658" width="7.44140625" style="5" customWidth="1"/>
-    <col min="6659" max="6659" width="6.77734375" style="5" customWidth="1"/>
-    <col min="6660" max="6660" width="7.44140625" style="5" customWidth="1"/>
-    <col min="6661" max="6661" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="6658" max="6658" width="7.5" style="5" customWidth="1"/>
+    <col min="6659" max="6659" width="6.83203125" style="5" customWidth="1"/>
+    <col min="6660" max="6660" width="7.5" style="5" customWidth="1"/>
+    <col min="6661" max="6661" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="6662" max="6662" width="19.33203125" style="5" customWidth="1"/>
-    <col min="6663" max="6909" width="8.77734375" style="5"/>
-    <col min="6910" max="6910" width="8.77734375" style="5" customWidth="1"/>
-    <col min="6911" max="6911" width="10.44140625" style="5" customWidth="1"/>
-    <col min="6912" max="6912" width="22.109375" style="5" customWidth="1"/>
+    <col min="6663" max="6909" width="8.83203125" style="5"/>
+    <col min="6910" max="6910" width="8.83203125" style="5" customWidth="1"/>
+    <col min="6911" max="6911" width="10.5" style="5" customWidth="1"/>
+    <col min="6912" max="6912" width="22.1640625" style="5" customWidth="1"/>
     <col min="6913" max="6913" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6914" max="6914" width="7.44140625" style="5" customWidth="1"/>
-    <col min="6915" max="6915" width="6.77734375" style="5" customWidth="1"/>
-    <col min="6916" max="6916" width="7.44140625" style="5" customWidth="1"/>
-    <col min="6917" max="6917" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="6914" max="6914" width="7.5" style="5" customWidth="1"/>
+    <col min="6915" max="6915" width="6.83203125" style="5" customWidth="1"/>
+    <col min="6916" max="6916" width="7.5" style="5" customWidth="1"/>
+    <col min="6917" max="6917" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="6918" max="6918" width="19.33203125" style="5" customWidth="1"/>
-    <col min="6919" max="7165" width="8.77734375" style="5"/>
-    <col min="7166" max="7166" width="8.77734375" style="5" customWidth="1"/>
-    <col min="7167" max="7167" width="10.44140625" style="5" customWidth="1"/>
-    <col min="7168" max="7168" width="22.109375" style="5" customWidth="1"/>
+    <col min="6919" max="7165" width="8.83203125" style="5"/>
+    <col min="7166" max="7166" width="8.83203125" style="5" customWidth="1"/>
+    <col min="7167" max="7167" width="10.5" style="5" customWidth="1"/>
+    <col min="7168" max="7168" width="22.1640625" style="5" customWidth="1"/>
     <col min="7169" max="7169" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7170" max="7170" width="7.44140625" style="5" customWidth="1"/>
-    <col min="7171" max="7171" width="6.77734375" style="5" customWidth="1"/>
-    <col min="7172" max="7172" width="7.44140625" style="5" customWidth="1"/>
-    <col min="7173" max="7173" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7170" max="7170" width="7.5" style="5" customWidth="1"/>
+    <col min="7171" max="7171" width="6.83203125" style="5" customWidth="1"/>
+    <col min="7172" max="7172" width="7.5" style="5" customWidth="1"/>
+    <col min="7173" max="7173" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="7174" max="7174" width="19.33203125" style="5" customWidth="1"/>
-    <col min="7175" max="7421" width="8.77734375" style="5"/>
-    <col min="7422" max="7422" width="8.77734375" style="5" customWidth="1"/>
-    <col min="7423" max="7423" width="10.44140625" style="5" customWidth="1"/>
-    <col min="7424" max="7424" width="22.109375" style="5" customWidth="1"/>
+    <col min="7175" max="7421" width="8.83203125" style="5"/>
+    <col min="7422" max="7422" width="8.83203125" style="5" customWidth="1"/>
+    <col min="7423" max="7423" width="10.5" style="5" customWidth="1"/>
+    <col min="7424" max="7424" width="22.1640625" style="5" customWidth="1"/>
     <col min="7425" max="7425" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7426" max="7426" width="7.44140625" style="5" customWidth="1"/>
-    <col min="7427" max="7427" width="6.77734375" style="5" customWidth="1"/>
-    <col min="7428" max="7428" width="7.44140625" style="5" customWidth="1"/>
-    <col min="7429" max="7429" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7426" max="7426" width="7.5" style="5" customWidth="1"/>
+    <col min="7427" max="7427" width="6.83203125" style="5" customWidth="1"/>
+    <col min="7428" max="7428" width="7.5" style="5" customWidth="1"/>
+    <col min="7429" max="7429" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="7430" max="7430" width="19.33203125" style="5" customWidth="1"/>
-    <col min="7431" max="7677" width="8.77734375" style="5"/>
-    <col min="7678" max="7678" width="8.77734375" style="5" customWidth="1"/>
-    <col min="7679" max="7679" width="10.44140625" style="5" customWidth="1"/>
-    <col min="7680" max="7680" width="22.109375" style="5" customWidth="1"/>
+    <col min="7431" max="7677" width="8.83203125" style="5"/>
+    <col min="7678" max="7678" width="8.83203125" style="5" customWidth="1"/>
+    <col min="7679" max="7679" width="10.5" style="5" customWidth="1"/>
+    <col min="7680" max="7680" width="22.1640625" style="5" customWidth="1"/>
     <col min="7681" max="7681" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7682" max="7682" width="7.44140625" style="5" customWidth="1"/>
-    <col min="7683" max="7683" width="6.77734375" style="5" customWidth="1"/>
-    <col min="7684" max="7684" width="7.44140625" style="5" customWidth="1"/>
-    <col min="7685" max="7685" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7682" max="7682" width="7.5" style="5" customWidth="1"/>
+    <col min="7683" max="7683" width="6.83203125" style="5" customWidth="1"/>
+    <col min="7684" max="7684" width="7.5" style="5" customWidth="1"/>
+    <col min="7685" max="7685" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="7686" max="7686" width="19.33203125" style="5" customWidth="1"/>
-    <col min="7687" max="7933" width="8.77734375" style="5"/>
-    <col min="7934" max="7934" width="8.77734375" style="5" customWidth="1"/>
-    <col min="7935" max="7935" width="10.44140625" style="5" customWidth="1"/>
-    <col min="7936" max="7936" width="22.109375" style="5" customWidth="1"/>
+    <col min="7687" max="7933" width="8.83203125" style="5"/>
+    <col min="7934" max="7934" width="8.83203125" style="5" customWidth="1"/>
+    <col min="7935" max="7935" width="10.5" style="5" customWidth="1"/>
+    <col min="7936" max="7936" width="22.1640625" style="5" customWidth="1"/>
     <col min="7937" max="7937" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7938" max="7938" width="7.44140625" style="5" customWidth="1"/>
-    <col min="7939" max="7939" width="6.77734375" style="5" customWidth="1"/>
-    <col min="7940" max="7940" width="7.44140625" style="5" customWidth="1"/>
-    <col min="7941" max="7941" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7938" max="7938" width="7.5" style="5" customWidth="1"/>
+    <col min="7939" max="7939" width="6.83203125" style="5" customWidth="1"/>
+    <col min="7940" max="7940" width="7.5" style="5" customWidth="1"/>
+    <col min="7941" max="7941" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="7942" max="7942" width="19.33203125" style="5" customWidth="1"/>
-    <col min="7943" max="8189" width="8.77734375" style="5"/>
-    <col min="8190" max="8190" width="8.77734375" style="5" customWidth="1"/>
-    <col min="8191" max="8191" width="10.44140625" style="5" customWidth="1"/>
-    <col min="8192" max="8192" width="22.109375" style="5" customWidth="1"/>
+    <col min="7943" max="8189" width="8.83203125" style="5"/>
+    <col min="8190" max="8190" width="8.83203125" style="5" customWidth="1"/>
+    <col min="8191" max="8191" width="10.5" style="5" customWidth="1"/>
+    <col min="8192" max="8192" width="22.1640625" style="5" customWidth="1"/>
     <col min="8193" max="8193" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8194" max="8194" width="7.44140625" style="5" customWidth="1"/>
-    <col min="8195" max="8195" width="6.77734375" style="5" customWidth="1"/>
-    <col min="8196" max="8196" width="7.44140625" style="5" customWidth="1"/>
-    <col min="8197" max="8197" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="8194" max="8194" width="7.5" style="5" customWidth="1"/>
+    <col min="8195" max="8195" width="6.83203125" style="5" customWidth="1"/>
+    <col min="8196" max="8196" width="7.5" style="5" customWidth="1"/>
+    <col min="8197" max="8197" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="8198" max="8198" width="19.33203125" style="5" customWidth="1"/>
-    <col min="8199" max="8445" width="8.77734375" style="5"/>
-    <col min="8446" max="8446" width="8.77734375" style="5" customWidth="1"/>
-    <col min="8447" max="8447" width="10.44140625" style="5" customWidth="1"/>
-    <col min="8448" max="8448" width="22.109375" style="5" customWidth="1"/>
+    <col min="8199" max="8445" width="8.83203125" style="5"/>
+    <col min="8446" max="8446" width="8.83203125" style="5" customWidth="1"/>
+    <col min="8447" max="8447" width="10.5" style="5" customWidth="1"/>
+    <col min="8448" max="8448" width="22.1640625" style="5" customWidth="1"/>
     <col min="8449" max="8449" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8450" max="8450" width="7.44140625" style="5" customWidth="1"/>
-    <col min="8451" max="8451" width="6.77734375" style="5" customWidth="1"/>
-    <col min="8452" max="8452" width="7.44140625" style="5" customWidth="1"/>
-    <col min="8453" max="8453" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="8450" max="8450" width="7.5" style="5" customWidth="1"/>
+    <col min="8451" max="8451" width="6.83203125" style="5" customWidth="1"/>
+    <col min="8452" max="8452" width="7.5" style="5" customWidth="1"/>
+    <col min="8453" max="8453" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="8454" max="8454" width="19.33203125" style="5" customWidth="1"/>
-    <col min="8455" max="8701" width="8.77734375" style="5"/>
-    <col min="8702" max="8702" width="8.77734375" style="5" customWidth="1"/>
-    <col min="8703" max="8703" width="10.44140625" style="5" customWidth="1"/>
-    <col min="8704" max="8704" width="22.109375" style="5" customWidth="1"/>
+    <col min="8455" max="8701" width="8.83203125" style="5"/>
+    <col min="8702" max="8702" width="8.83203125" style="5" customWidth="1"/>
+    <col min="8703" max="8703" width="10.5" style="5" customWidth="1"/>
+    <col min="8704" max="8704" width="22.1640625" style="5" customWidth="1"/>
     <col min="8705" max="8705" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8706" max="8706" width="7.44140625" style="5" customWidth="1"/>
-    <col min="8707" max="8707" width="6.77734375" style="5" customWidth="1"/>
-    <col min="8708" max="8708" width="7.44140625" style="5" customWidth="1"/>
-    <col min="8709" max="8709" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="8706" max="8706" width="7.5" style="5" customWidth="1"/>
+    <col min="8707" max="8707" width="6.83203125" style="5" customWidth="1"/>
+    <col min="8708" max="8708" width="7.5" style="5" customWidth="1"/>
+    <col min="8709" max="8709" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="8710" max="8710" width="19.33203125" style="5" customWidth="1"/>
-    <col min="8711" max="8957" width="8.77734375" style="5"/>
-    <col min="8958" max="8958" width="8.77734375" style="5" customWidth="1"/>
-    <col min="8959" max="8959" width="10.44140625" style="5" customWidth="1"/>
-    <col min="8960" max="8960" width="22.109375" style="5" customWidth="1"/>
+    <col min="8711" max="8957" width="8.83203125" style="5"/>
+    <col min="8958" max="8958" width="8.83203125" style="5" customWidth="1"/>
+    <col min="8959" max="8959" width="10.5" style="5" customWidth="1"/>
+    <col min="8960" max="8960" width="22.1640625" style="5" customWidth="1"/>
     <col min="8961" max="8961" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8962" max="8962" width="7.44140625" style="5" customWidth="1"/>
-    <col min="8963" max="8963" width="6.77734375" style="5" customWidth="1"/>
-    <col min="8964" max="8964" width="7.44140625" style="5" customWidth="1"/>
-    <col min="8965" max="8965" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="8962" max="8962" width="7.5" style="5" customWidth="1"/>
+    <col min="8963" max="8963" width="6.83203125" style="5" customWidth="1"/>
+    <col min="8964" max="8964" width="7.5" style="5" customWidth="1"/>
+    <col min="8965" max="8965" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="8966" max="8966" width="19.33203125" style="5" customWidth="1"/>
-    <col min="8967" max="9213" width="8.77734375" style="5"/>
-    <col min="9214" max="9214" width="8.77734375" style="5" customWidth="1"/>
-    <col min="9215" max="9215" width="10.44140625" style="5" customWidth="1"/>
-    <col min="9216" max="9216" width="22.109375" style="5" customWidth="1"/>
+    <col min="8967" max="9213" width="8.83203125" style="5"/>
+    <col min="9214" max="9214" width="8.83203125" style="5" customWidth="1"/>
+    <col min="9215" max="9215" width="10.5" style="5" customWidth="1"/>
+    <col min="9216" max="9216" width="22.1640625" style="5" customWidth="1"/>
     <col min="9217" max="9217" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9218" max="9218" width="7.44140625" style="5" customWidth="1"/>
-    <col min="9219" max="9219" width="6.77734375" style="5" customWidth="1"/>
-    <col min="9220" max="9220" width="7.44140625" style="5" customWidth="1"/>
-    <col min="9221" max="9221" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="9218" max="9218" width="7.5" style="5" customWidth="1"/>
+    <col min="9219" max="9219" width="6.83203125" style="5" customWidth="1"/>
+    <col min="9220" max="9220" width="7.5" style="5" customWidth="1"/>
+    <col min="9221" max="9221" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="9222" max="9222" width="19.33203125" style="5" customWidth="1"/>
-    <col min="9223" max="9469" width="8.77734375" style="5"/>
-    <col min="9470" max="9470" width="8.77734375" style="5" customWidth="1"/>
-    <col min="9471" max="9471" width="10.44140625" style="5" customWidth="1"/>
-    <col min="9472" max="9472" width="22.109375" style="5" customWidth="1"/>
+    <col min="9223" max="9469" width="8.83203125" style="5"/>
+    <col min="9470" max="9470" width="8.83203125" style="5" customWidth="1"/>
+    <col min="9471" max="9471" width="10.5" style="5" customWidth="1"/>
+    <col min="9472" max="9472" width="22.1640625" style="5" customWidth="1"/>
     <col min="9473" max="9473" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9474" max="9474" width="7.44140625" style="5" customWidth="1"/>
-    <col min="9475" max="9475" width="6.77734375" style="5" customWidth="1"/>
-    <col min="9476" max="9476" width="7.44140625" style="5" customWidth="1"/>
-    <col min="9477" max="9477" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="9474" max="9474" width="7.5" style="5" customWidth="1"/>
+    <col min="9475" max="9475" width="6.83203125" style="5" customWidth="1"/>
+    <col min="9476" max="9476" width="7.5" style="5" customWidth="1"/>
+    <col min="9477" max="9477" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="9478" max="9478" width="19.33203125" style="5" customWidth="1"/>
-    <col min="9479" max="9725" width="8.77734375" style="5"/>
-    <col min="9726" max="9726" width="8.77734375" style="5" customWidth="1"/>
-    <col min="9727" max="9727" width="10.44140625" style="5" customWidth="1"/>
-    <col min="9728" max="9728" width="22.109375" style="5" customWidth="1"/>
+    <col min="9479" max="9725" width="8.83203125" style="5"/>
+    <col min="9726" max="9726" width="8.83203125" style="5" customWidth="1"/>
+    <col min="9727" max="9727" width="10.5" style="5" customWidth="1"/>
+    <col min="9728" max="9728" width="22.1640625" style="5" customWidth="1"/>
     <col min="9729" max="9729" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9730" max="9730" width="7.44140625" style="5" customWidth="1"/>
-    <col min="9731" max="9731" width="6.77734375" style="5" customWidth="1"/>
-    <col min="9732" max="9732" width="7.44140625" style="5" customWidth="1"/>
-    <col min="9733" max="9733" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="9730" max="9730" width="7.5" style="5" customWidth="1"/>
+    <col min="9731" max="9731" width="6.83203125" style="5" customWidth="1"/>
+    <col min="9732" max="9732" width="7.5" style="5" customWidth="1"/>
+    <col min="9733" max="9733" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="9734" max="9734" width="19.33203125" style="5" customWidth="1"/>
-    <col min="9735" max="9981" width="8.77734375" style="5"/>
-    <col min="9982" max="9982" width="8.77734375" style="5" customWidth="1"/>
-    <col min="9983" max="9983" width="10.44140625" style="5" customWidth="1"/>
-    <col min="9984" max="9984" width="22.109375" style="5" customWidth="1"/>
+    <col min="9735" max="9981" width="8.83203125" style="5"/>
+    <col min="9982" max="9982" width="8.83203125" style="5" customWidth="1"/>
+    <col min="9983" max="9983" width="10.5" style="5" customWidth="1"/>
+    <col min="9984" max="9984" width="22.1640625" style="5" customWidth="1"/>
     <col min="9985" max="9985" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9986" max="9986" width="7.44140625" style="5" customWidth="1"/>
-    <col min="9987" max="9987" width="6.77734375" style="5" customWidth="1"/>
-    <col min="9988" max="9988" width="7.44140625" style="5" customWidth="1"/>
-    <col min="9989" max="9989" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="9986" max="9986" width="7.5" style="5" customWidth="1"/>
+    <col min="9987" max="9987" width="6.83203125" style="5" customWidth="1"/>
+    <col min="9988" max="9988" width="7.5" style="5" customWidth="1"/>
+    <col min="9989" max="9989" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="9990" max="9990" width="19.33203125" style="5" customWidth="1"/>
-    <col min="9991" max="10237" width="8.77734375" style="5"/>
-    <col min="10238" max="10238" width="8.77734375" style="5" customWidth="1"/>
-    <col min="10239" max="10239" width="10.44140625" style="5" customWidth="1"/>
-    <col min="10240" max="10240" width="22.109375" style="5" customWidth="1"/>
+    <col min="9991" max="10237" width="8.83203125" style="5"/>
+    <col min="10238" max="10238" width="8.83203125" style="5" customWidth="1"/>
+    <col min="10239" max="10239" width="10.5" style="5" customWidth="1"/>
+    <col min="10240" max="10240" width="22.1640625" style="5" customWidth="1"/>
     <col min="10241" max="10241" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="10242" max="10242" width="7.44140625" style="5" customWidth="1"/>
-    <col min="10243" max="10243" width="6.77734375" style="5" customWidth="1"/>
-    <col min="10244" max="10244" width="7.44140625" style="5" customWidth="1"/>
-    <col min="10245" max="10245" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="10242" max="10242" width="7.5" style="5" customWidth="1"/>
+    <col min="10243" max="10243" width="6.83203125" style="5" customWidth="1"/>
+    <col min="10244" max="10244" width="7.5" style="5" customWidth="1"/>
+    <col min="10245" max="10245" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="10246" max="10246" width="19.33203125" style="5" customWidth="1"/>
-    <col min="10247" max="10493" width="8.77734375" style="5"/>
-    <col min="10494" max="10494" width="8.77734375" style="5" customWidth="1"/>
-    <col min="10495" max="10495" width="10.44140625" style="5" customWidth="1"/>
-    <col min="10496" max="10496" width="22.109375" style="5" customWidth="1"/>
+    <col min="10247" max="10493" width="8.83203125" style="5"/>
+    <col min="10494" max="10494" width="8.83203125" style="5" customWidth="1"/>
+    <col min="10495" max="10495" width="10.5" style="5" customWidth="1"/>
+    <col min="10496" max="10496" width="22.1640625" style="5" customWidth="1"/>
     <col min="10497" max="10497" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="10498" max="10498" width="7.44140625" style="5" customWidth="1"/>
-    <col min="10499" max="10499" width="6.77734375" style="5" customWidth="1"/>
-    <col min="10500" max="10500" width="7.44140625" style="5" customWidth="1"/>
-    <col min="10501" max="10501" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="10498" max="10498" width="7.5" style="5" customWidth="1"/>
+    <col min="10499" max="10499" width="6.83203125" style="5" customWidth="1"/>
+    <col min="10500" max="10500" width="7.5" style="5" customWidth="1"/>
+    <col min="10501" max="10501" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="10502" max="10502" width="19.33203125" style="5" customWidth="1"/>
-    <col min="10503" max="10749" width="8.77734375" style="5"/>
-    <col min="10750" max="10750" width="8.77734375" style="5" customWidth="1"/>
-    <col min="10751" max="10751" width="10.44140625" style="5" customWidth="1"/>
-    <col min="10752" max="10752" width="22.109375" style="5" customWidth="1"/>
+    <col min="10503" max="10749" width="8.83203125" style="5"/>
+    <col min="10750" max="10750" width="8.83203125" style="5" customWidth="1"/>
+    <col min="10751" max="10751" width="10.5" style="5" customWidth="1"/>
+    <col min="10752" max="10752" width="22.1640625" style="5" customWidth="1"/>
     <col min="10753" max="10753" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="10754" max="10754" width="7.44140625" style="5" customWidth="1"/>
-    <col min="10755" max="10755" width="6.77734375" style="5" customWidth="1"/>
-    <col min="10756" max="10756" width="7.44140625" style="5" customWidth="1"/>
-    <col min="10757" max="10757" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="10754" max="10754" width="7.5" style="5" customWidth="1"/>
+    <col min="10755" max="10755" width="6.83203125" style="5" customWidth="1"/>
+    <col min="10756" max="10756" width="7.5" style="5" customWidth="1"/>
+    <col min="10757" max="10757" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="10758" max="10758" width="19.33203125" style="5" customWidth="1"/>
-    <col min="10759" max="11005" width="8.77734375" style="5"/>
-    <col min="11006" max="11006" width="8.77734375" style="5" customWidth="1"/>
-    <col min="11007" max="11007" width="10.44140625" style="5" customWidth="1"/>
-    <col min="11008" max="11008" width="22.109375" style="5" customWidth="1"/>
+    <col min="10759" max="11005" width="8.83203125" style="5"/>
+    <col min="11006" max="11006" width="8.83203125" style="5" customWidth="1"/>
+    <col min="11007" max="11007" width="10.5" style="5" customWidth="1"/>
+    <col min="11008" max="11008" width="22.1640625" style="5" customWidth="1"/>
     <col min="11009" max="11009" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="11010" max="11010" width="7.44140625" style="5" customWidth="1"/>
-    <col min="11011" max="11011" width="6.77734375" style="5" customWidth="1"/>
-    <col min="11012" max="11012" width="7.44140625" style="5" customWidth="1"/>
-    <col min="11013" max="11013" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="11010" max="11010" width="7.5" style="5" customWidth="1"/>
+    <col min="11011" max="11011" width="6.83203125" style="5" customWidth="1"/>
+    <col min="11012" max="11012" width="7.5" style="5" customWidth="1"/>
+    <col min="11013" max="11013" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="11014" max="11014" width="19.33203125" style="5" customWidth="1"/>
-    <col min="11015" max="11261" width="8.77734375" style="5"/>
-    <col min="11262" max="11262" width="8.77734375" style="5" customWidth="1"/>
-    <col min="11263" max="11263" width="10.44140625" style="5" customWidth="1"/>
-    <col min="11264" max="11264" width="22.109375" style="5" customWidth="1"/>
+    <col min="11015" max="11261" width="8.83203125" style="5"/>
+    <col min="11262" max="11262" width="8.83203125" style="5" customWidth="1"/>
+    <col min="11263" max="11263" width="10.5" style="5" customWidth="1"/>
+    <col min="11264" max="11264" width="22.1640625" style="5" customWidth="1"/>
     <col min="11265" max="11265" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="11266" max="11266" width="7.44140625" style="5" customWidth="1"/>
-    <col min="11267" max="11267" width="6.77734375" style="5" customWidth="1"/>
-    <col min="11268" max="11268" width="7.44140625" style="5" customWidth="1"/>
-    <col min="11269" max="11269" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="11266" max="11266" width="7.5" style="5" customWidth="1"/>
+    <col min="11267" max="11267" width="6.83203125" style="5" customWidth="1"/>
+    <col min="11268" max="11268" width="7.5" style="5" customWidth="1"/>
+    <col min="11269" max="11269" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="11270" max="11270" width="19.33203125" style="5" customWidth="1"/>
-    <col min="11271" max="11517" width="8.77734375" style="5"/>
-    <col min="11518" max="11518" width="8.77734375" style="5" customWidth="1"/>
-    <col min="11519" max="11519" width="10.44140625" style="5" customWidth="1"/>
-    <col min="11520" max="11520" width="22.109375" style="5" customWidth="1"/>
+    <col min="11271" max="11517" width="8.83203125" style="5"/>
+    <col min="11518" max="11518" width="8.83203125" style="5" customWidth="1"/>
+    <col min="11519" max="11519" width="10.5" style="5" customWidth="1"/>
+    <col min="11520" max="11520" width="22.1640625" style="5" customWidth="1"/>
     <col min="11521" max="11521" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="11522" max="11522" width="7.44140625" style="5" customWidth="1"/>
-    <col min="11523" max="11523" width="6.77734375" style="5" customWidth="1"/>
-    <col min="11524" max="11524" width="7.44140625" style="5" customWidth="1"/>
-    <col min="11525" max="11525" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="11522" max="11522" width="7.5" style="5" customWidth="1"/>
+    <col min="11523" max="11523" width="6.83203125" style="5" customWidth="1"/>
+    <col min="11524" max="11524" width="7.5" style="5" customWidth="1"/>
+    <col min="11525" max="11525" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="11526" max="11526" width="19.33203125" style="5" customWidth="1"/>
-    <col min="11527" max="11773" width="8.77734375" style="5"/>
-    <col min="11774" max="11774" width="8.77734375" style="5" customWidth="1"/>
-    <col min="11775" max="11775" width="10.44140625" style="5" customWidth="1"/>
-    <col min="11776" max="11776" width="22.109375" style="5" customWidth="1"/>
+    <col min="11527" max="11773" width="8.83203125" style="5"/>
+    <col min="11774" max="11774" width="8.83203125" style="5" customWidth="1"/>
+    <col min="11775" max="11775" width="10.5" style="5" customWidth="1"/>
+    <col min="11776" max="11776" width="22.1640625" style="5" customWidth="1"/>
     <col min="11777" max="11777" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="11778" max="11778" width="7.44140625" style="5" customWidth="1"/>
-    <col min="11779" max="11779" width="6.77734375" style="5" customWidth="1"/>
-    <col min="11780" max="11780" width="7.44140625" style="5" customWidth="1"/>
-    <col min="11781" max="11781" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="11778" max="11778" width="7.5" style="5" customWidth="1"/>
+    <col min="11779" max="11779" width="6.83203125" style="5" customWidth="1"/>
+    <col min="11780" max="11780" width="7.5" style="5" customWidth="1"/>
+    <col min="11781" max="11781" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="11782" max="11782" width="19.33203125" style="5" customWidth="1"/>
-    <col min="11783" max="12029" width="8.77734375" style="5"/>
-    <col min="12030" max="12030" width="8.77734375" style="5" customWidth="1"/>
-    <col min="12031" max="12031" width="10.44140625" style="5" customWidth="1"/>
-    <col min="12032" max="12032" width="22.109375" style="5" customWidth="1"/>
+    <col min="11783" max="12029" width="8.83203125" style="5"/>
+    <col min="12030" max="12030" width="8.83203125" style="5" customWidth="1"/>
+    <col min="12031" max="12031" width="10.5" style="5" customWidth="1"/>
+    <col min="12032" max="12032" width="22.1640625" style="5" customWidth="1"/>
     <col min="12033" max="12033" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12034" max="12034" width="7.44140625" style="5" customWidth="1"/>
-    <col min="12035" max="12035" width="6.77734375" style="5" customWidth="1"/>
-    <col min="12036" max="12036" width="7.44140625" style="5" customWidth="1"/>
-    <col min="12037" max="12037" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="12034" max="12034" width="7.5" style="5" customWidth="1"/>
+    <col min="12035" max="12035" width="6.83203125" style="5" customWidth="1"/>
+    <col min="12036" max="12036" width="7.5" style="5" customWidth="1"/>
+    <col min="12037" max="12037" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="12038" max="12038" width="19.33203125" style="5" customWidth="1"/>
-    <col min="12039" max="12285" width="8.77734375" style="5"/>
-    <col min="12286" max="12286" width="8.77734375" style="5" customWidth="1"/>
-    <col min="12287" max="12287" width="10.44140625" style="5" customWidth="1"/>
-    <col min="12288" max="12288" width="22.109375" style="5" customWidth="1"/>
+    <col min="12039" max="12285" width="8.83203125" style="5"/>
+    <col min="12286" max="12286" width="8.83203125" style="5" customWidth="1"/>
+    <col min="12287" max="12287" width="10.5" style="5" customWidth="1"/>
+    <col min="12288" max="12288" width="22.1640625" style="5" customWidth="1"/>
     <col min="12289" max="12289" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12290" max="12290" width="7.44140625" style="5" customWidth="1"/>
-    <col min="12291" max="12291" width="6.77734375" style="5" customWidth="1"/>
-    <col min="12292" max="12292" width="7.44140625" style="5" customWidth="1"/>
-    <col min="12293" max="12293" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="12290" max="12290" width="7.5" style="5" customWidth="1"/>
+    <col min="12291" max="12291" width="6.83203125" style="5" customWidth="1"/>
+    <col min="12292" max="12292" width="7.5" style="5" customWidth="1"/>
+    <col min="12293" max="12293" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="12294" max="12294" width="19.33203125" style="5" customWidth="1"/>
-    <col min="12295" max="12541" width="8.77734375" style="5"/>
-    <col min="12542" max="12542" width="8.77734375" style="5" customWidth="1"/>
-    <col min="12543" max="12543" width="10.44140625" style="5" customWidth="1"/>
-    <col min="12544" max="12544" width="22.109375" style="5" customWidth="1"/>
+    <col min="12295" max="12541" width="8.83203125" style="5"/>
+    <col min="12542" max="12542" width="8.83203125" style="5" customWidth="1"/>
+    <col min="12543" max="12543" width="10.5" style="5" customWidth="1"/>
+    <col min="12544" max="12544" width="22.1640625" style="5" customWidth="1"/>
     <col min="12545" max="12545" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12546" max="12546" width="7.44140625" style="5" customWidth="1"/>
-    <col min="12547" max="12547" width="6.77734375" style="5" customWidth="1"/>
-    <col min="12548" max="12548" width="7.44140625" style="5" customWidth="1"/>
-    <col min="12549" max="12549" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="12546" max="12546" width="7.5" style="5" customWidth="1"/>
+    <col min="12547" max="12547" width="6.83203125" style="5" customWidth="1"/>
+    <col min="12548" max="12548" width="7.5" style="5" customWidth="1"/>
+    <col min="12549" max="12549" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="12550" max="12550" width="19.33203125" style="5" customWidth="1"/>
-    <col min="12551" max="12797" width="8.77734375" style="5"/>
-    <col min="12798" max="12798" width="8.77734375" style="5" customWidth="1"/>
-    <col min="12799" max="12799" width="10.44140625" style="5" customWidth="1"/>
-    <col min="12800" max="12800" width="22.109375" style="5" customWidth="1"/>
+    <col min="12551" max="12797" width="8.83203125" style="5"/>
+    <col min="12798" max="12798" width="8.83203125" style="5" customWidth="1"/>
+    <col min="12799" max="12799" width="10.5" style="5" customWidth="1"/>
+    <col min="12800" max="12800" width="22.1640625" style="5" customWidth="1"/>
     <col min="12801" max="12801" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12802" max="12802" width="7.44140625" style="5" customWidth="1"/>
-    <col min="12803" max="12803" width="6.77734375" style="5" customWidth="1"/>
-    <col min="12804" max="12804" width="7.44140625" style="5" customWidth="1"/>
-    <col min="12805" max="12805" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="12802" max="12802" width="7.5" style="5" customWidth="1"/>
+    <col min="12803" max="12803" width="6.83203125" style="5" customWidth="1"/>
+    <col min="12804" max="12804" width="7.5" style="5" customWidth="1"/>
+    <col min="12805" max="12805" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="12806" max="12806" width="19.33203125" style="5" customWidth="1"/>
-    <col min="12807" max="13053" width="8.77734375" style="5"/>
-    <col min="13054" max="13054" width="8.77734375" style="5" customWidth="1"/>
-    <col min="13055" max="13055" width="10.44140625" style="5" customWidth="1"/>
-    <col min="13056" max="13056" width="22.109375" style="5" customWidth="1"/>
+    <col min="12807" max="13053" width="8.83203125" style="5"/>
+    <col min="13054" max="13054" width="8.83203125" style="5" customWidth="1"/>
+    <col min="13055" max="13055" width="10.5" style="5" customWidth="1"/>
+    <col min="13056" max="13056" width="22.1640625" style="5" customWidth="1"/>
     <col min="13057" max="13057" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="13058" max="13058" width="7.44140625" style="5" customWidth="1"/>
-    <col min="13059" max="13059" width="6.77734375" style="5" customWidth="1"/>
-    <col min="13060" max="13060" width="7.44140625" style="5" customWidth="1"/>
-    <col min="13061" max="13061" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="13058" max="13058" width="7.5" style="5" customWidth="1"/>
+    <col min="13059" max="13059" width="6.83203125" style="5" customWidth="1"/>
+    <col min="13060" max="13060" width="7.5" style="5" customWidth="1"/>
+    <col min="13061" max="13061" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="13062" max="13062" width="19.33203125" style="5" customWidth="1"/>
-    <col min="13063" max="13309" width="8.77734375" style="5"/>
-    <col min="13310" max="13310" width="8.77734375" style="5" customWidth="1"/>
-    <col min="13311" max="13311" width="10.44140625" style="5" customWidth="1"/>
-    <col min="13312" max="13312" width="22.109375" style="5" customWidth="1"/>
+    <col min="13063" max="13309" width="8.83203125" style="5"/>
+    <col min="13310" max="13310" width="8.83203125" style="5" customWidth="1"/>
+    <col min="13311" max="13311" width="10.5" style="5" customWidth="1"/>
+    <col min="13312" max="13312" width="22.1640625" style="5" customWidth="1"/>
     <col min="13313" max="13313" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="13314" max="13314" width="7.44140625" style="5" customWidth="1"/>
-    <col min="13315" max="13315" width="6.77734375" style="5" customWidth="1"/>
-    <col min="13316" max="13316" width="7.44140625" style="5" customWidth="1"/>
-    <col min="13317" max="13317" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="13314" max="13314" width="7.5" style="5" customWidth="1"/>
+    <col min="13315" max="13315" width="6.83203125" style="5" customWidth="1"/>
+    <col min="13316" max="13316" width="7.5" style="5" customWidth="1"/>
+    <col min="13317" max="13317" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="13318" max="13318" width="19.33203125" style="5" customWidth="1"/>
-    <col min="13319" max="13565" width="8.77734375" style="5"/>
-    <col min="13566" max="13566" width="8.77734375" style="5" customWidth="1"/>
-    <col min="13567" max="13567" width="10.44140625" style="5" customWidth="1"/>
-    <col min="13568" max="13568" width="22.109375" style="5" customWidth="1"/>
+    <col min="13319" max="13565" width="8.83203125" style="5"/>
+    <col min="13566" max="13566" width="8.83203125" style="5" customWidth="1"/>
+    <col min="13567" max="13567" width="10.5" style="5" customWidth="1"/>
+    <col min="13568" max="13568" width="22.1640625" style="5" customWidth="1"/>
     <col min="13569" max="13569" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="13570" max="13570" width="7.44140625" style="5" customWidth="1"/>
-    <col min="13571" max="13571" width="6.77734375" style="5" customWidth="1"/>
-    <col min="13572" max="13572" width="7.44140625" style="5" customWidth="1"/>
-    <col min="13573" max="13573" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="13570" max="13570" width="7.5" style="5" customWidth="1"/>
+    <col min="13571" max="13571" width="6.83203125" style="5" customWidth="1"/>
+    <col min="13572" max="13572" width="7.5" style="5" customWidth="1"/>
+    <col min="13573" max="13573" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="13574" max="13574" width="19.33203125" style="5" customWidth="1"/>
-    <col min="13575" max="13821" width="8.77734375" style="5"/>
-    <col min="13822" max="13822" width="8.77734375" style="5" customWidth="1"/>
-    <col min="13823" max="13823" width="10.44140625" style="5" customWidth="1"/>
-    <col min="13824" max="13824" width="22.109375" style="5" customWidth="1"/>
+    <col min="13575" max="13821" width="8.83203125" style="5"/>
+    <col min="13822" max="13822" width="8.83203125" style="5" customWidth="1"/>
+    <col min="13823" max="13823" width="10.5" style="5" customWidth="1"/>
+    <col min="13824" max="13824" width="22.1640625" style="5" customWidth="1"/>
     <col min="13825" max="13825" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="13826" max="13826" width="7.44140625" style="5" customWidth="1"/>
-    <col min="13827" max="13827" width="6.77734375" style="5" customWidth="1"/>
-    <col min="13828" max="13828" width="7.44140625" style="5" customWidth="1"/>
-    <col min="13829" max="13829" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="13826" max="13826" width="7.5" style="5" customWidth="1"/>
+    <col min="13827" max="13827" width="6.83203125" style="5" customWidth="1"/>
+    <col min="13828" max="13828" width="7.5" style="5" customWidth="1"/>
+    <col min="13829" max="13829" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="13830" max="13830" width="19.33203125" style="5" customWidth="1"/>
-    <col min="13831" max="14077" width="8.77734375" style="5"/>
-    <col min="14078" max="14078" width="8.77734375" style="5" customWidth="1"/>
-    <col min="14079" max="14079" width="10.44140625" style="5" customWidth="1"/>
-    <col min="14080" max="14080" width="22.109375" style="5" customWidth="1"/>
+    <col min="13831" max="14077" width="8.83203125" style="5"/>
+    <col min="14078" max="14078" width="8.83203125" style="5" customWidth="1"/>
+    <col min="14079" max="14079" width="10.5" style="5" customWidth="1"/>
+    <col min="14080" max="14080" width="22.1640625" style="5" customWidth="1"/>
     <col min="14081" max="14081" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="14082" max="14082" width="7.44140625" style="5" customWidth="1"/>
-    <col min="14083" max="14083" width="6.77734375" style="5" customWidth="1"/>
-    <col min="14084" max="14084" width="7.44140625" style="5" customWidth="1"/>
-    <col min="14085" max="14085" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="14082" max="14082" width="7.5" style="5" customWidth="1"/>
+    <col min="14083" max="14083" width="6.83203125" style="5" customWidth="1"/>
+    <col min="14084" max="14084" width="7.5" style="5" customWidth="1"/>
+    <col min="14085" max="14085" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="14086" max="14086" width="19.33203125" style="5" customWidth="1"/>
-    <col min="14087" max="14333" width="8.77734375" style="5"/>
-    <col min="14334" max="14334" width="8.77734375" style="5" customWidth="1"/>
-    <col min="14335" max="14335" width="10.44140625" style="5" customWidth="1"/>
-    <col min="14336" max="14336" width="22.109375" style="5" customWidth="1"/>
+    <col min="14087" max="14333" width="8.83203125" style="5"/>
+    <col min="14334" max="14334" width="8.83203125" style="5" customWidth="1"/>
+    <col min="14335" max="14335" width="10.5" style="5" customWidth="1"/>
+    <col min="14336" max="14336" width="22.1640625" style="5" customWidth="1"/>
     <col min="14337" max="14337" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="14338" max="14338" width="7.44140625" style="5" customWidth="1"/>
-    <col min="14339" max="14339" width="6.77734375" style="5" customWidth="1"/>
-    <col min="14340" max="14340" width="7.44140625" style="5" customWidth="1"/>
-    <col min="14341" max="14341" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="14338" max="14338" width="7.5" style="5" customWidth="1"/>
+    <col min="14339" max="14339" width="6.83203125" style="5" customWidth="1"/>
+    <col min="14340" max="14340" width="7.5" style="5" customWidth="1"/>
+    <col min="14341" max="14341" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="14342" max="14342" width="19.33203125" style="5" customWidth="1"/>
-    <col min="14343" max="14589" width="8.77734375" style="5"/>
-    <col min="14590" max="14590" width="8.77734375" style="5" customWidth="1"/>
-    <col min="14591" max="14591" width="10.44140625" style="5" customWidth="1"/>
-    <col min="14592" max="14592" width="22.109375" style="5" customWidth="1"/>
+    <col min="14343" max="14589" width="8.83203125" style="5"/>
+    <col min="14590" max="14590" width="8.83203125" style="5" customWidth="1"/>
+    <col min="14591" max="14591" width="10.5" style="5" customWidth="1"/>
+    <col min="14592" max="14592" width="22.1640625" style="5" customWidth="1"/>
     <col min="14593" max="14593" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="14594" max="14594" width="7.44140625" style="5" customWidth="1"/>
-    <col min="14595" max="14595" width="6.77734375" style="5" customWidth="1"/>
-    <col min="14596" max="14596" width="7.44140625" style="5" customWidth="1"/>
-    <col min="14597" max="14597" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="14594" max="14594" width="7.5" style="5" customWidth="1"/>
+    <col min="14595" max="14595" width="6.83203125" style="5" customWidth="1"/>
+    <col min="14596" max="14596" width="7.5" style="5" customWidth="1"/>
+    <col min="14597" max="14597" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="14598" max="14598" width="19.33203125" style="5" customWidth="1"/>
-    <col min="14599" max="14845" width="8.77734375" style="5"/>
-    <col min="14846" max="14846" width="8.77734375" style="5" customWidth="1"/>
-    <col min="14847" max="14847" width="10.44140625" style="5" customWidth="1"/>
-    <col min="14848" max="14848" width="22.109375" style="5" customWidth="1"/>
+    <col min="14599" max="14845" width="8.83203125" style="5"/>
+    <col min="14846" max="14846" width="8.83203125" style="5" customWidth="1"/>
+    <col min="14847" max="14847" width="10.5" style="5" customWidth="1"/>
+    <col min="14848" max="14848" width="22.1640625" style="5" customWidth="1"/>
     <col min="14849" max="14849" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="14850" max="14850" width="7.44140625" style="5" customWidth="1"/>
-    <col min="14851" max="14851" width="6.77734375" style="5" customWidth="1"/>
-    <col min="14852" max="14852" width="7.44140625" style="5" customWidth="1"/>
-    <col min="14853" max="14853" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="14850" max="14850" width="7.5" style="5" customWidth="1"/>
+    <col min="14851" max="14851" width="6.83203125" style="5" customWidth="1"/>
+    <col min="14852" max="14852" width="7.5" style="5" customWidth="1"/>
+    <col min="14853" max="14853" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="14854" max="14854" width="19.33203125" style="5" customWidth="1"/>
-    <col min="14855" max="15101" width="8.77734375" style="5"/>
-    <col min="15102" max="15102" width="8.77734375" style="5" customWidth="1"/>
-    <col min="15103" max="15103" width="10.44140625" style="5" customWidth="1"/>
-    <col min="15104" max="15104" width="22.109375" style="5" customWidth="1"/>
+    <col min="14855" max="15101" width="8.83203125" style="5"/>
+    <col min="15102" max="15102" width="8.83203125" style="5" customWidth="1"/>
+    <col min="15103" max="15103" width="10.5" style="5" customWidth="1"/>
+    <col min="15104" max="15104" width="22.1640625" style="5" customWidth="1"/>
     <col min="15105" max="15105" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="15106" max="15106" width="7.44140625" style="5" customWidth="1"/>
-    <col min="15107" max="15107" width="6.77734375" style="5" customWidth="1"/>
-    <col min="15108" max="15108" width="7.44140625" style="5" customWidth="1"/>
-    <col min="15109" max="15109" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="15106" max="15106" width="7.5" style="5" customWidth="1"/>
+    <col min="15107" max="15107" width="6.83203125" style="5" customWidth="1"/>
+    <col min="15108" max="15108" width="7.5" style="5" customWidth="1"/>
+    <col min="15109" max="15109" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="15110" max="15110" width="19.33203125" style="5" customWidth="1"/>
-    <col min="15111" max="15357" width="8.77734375" style="5"/>
-    <col min="15358" max="15358" width="8.77734375" style="5" customWidth="1"/>
-    <col min="15359" max="15359" width="10.44140625" style="5" customWidth="1"/>
-    <col min="15360" max="15360" width="22.109375" style="5" customWidth="1"/>
+    <col min="15111" max="15357" width="8.83203125" style="5"/>
+    <col min="15358" max="15358" width="8.83203125" style="5" customWidth="1"/>
+    <col min="15359" max="15359" width="10.5" style="5" customWidth="1"/>
+    <col min="15360" max="15360" width="22.1640625" style="5" customWidth="1"/>
     <col min="15361" max="15361" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="15362" max="15362" width="7.44140625" style="5" customWidth="1"/>
-    <col min="15363" max="15363" width="6.77734375" style="5" customWidth="1"/>
-    <col min="15364" max="15364" width="7.44140625" style="5" customWidth="1"/>
-    <col min="15365" max="15365" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="15362" max="15362" width="7.5" style="5" customWidth="1"/>
+    <col min="15363" max="15363" width="6.83203125" style="5" customWidth="1"/>
+    <col min="15364" max="15364" width="7.5" style="5" customWidth="1"/>
+    <col min="15365" max="15365" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="15366" max="15366" width="19.33203125" style="5" customWidth="1"/>
-    <col min="15367" max="15613" width="8.77734375" style="5"/>
-    <col min="15614" max="15614" width="8.77734375" style="5" customWidth="1"/>
-    <col min="15615" max="15615" width="10.44140625" style="5" customWidth="1"/>
-    <col min="15616" max="15616" width="22.109375" style="5" customWidth="1"/>
+    <col min="15367" max="15613" width="8.83203125" style="5"/>
+    <col min="15614" max="15614" width="8.83203125" style="5" customWidth="1"/>
+    <col min="15615" max="15615" width="10.5" style="5" customWidth="1"/>
+    <col min="15616" max="15616" width="22.1640625" style="5" customWidth="1"/>
     <col min="15617" max="15617" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="15618" max="15618" width="7.44140625" style="5" customWidth="1"/>
-    <col min="15619" max="15619" width="6.77734375" style="5" customWidth="1"/>
-    <col min="15620" max="15620" width="7.44140625" style="5" customWidth="1"/>
-    <col min="15621" max="15621" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="15618" max="15618" width="7.5" style="5" customWidth="1"/>
+    <col min="15619" max="15619" width="6.83203125" style="5" customWidth="1"/>
+    <col min="15620" max="15620" width="7.5" style="5" customWidth="1"/>
+    <col min="15621" max="15621" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="15622" max="15622" width="19.33203125" style="5" customWidth="1"/>
-    <col min="15623" max="15869" width="8.77734375" style="5"/>
-    <col min="15870" max="15870" width="8.77734375" style="5" customWidth="1"/>
-    <col min="15871" max="15871" width="10.44140625" style="5" customWidth="1"/>
-    <col min="15872" max="15872" width="22.109375" style="5" customWidth="1"/>
+    <col min="15623" max="15869" width="8.83203125" style="5"/>
+    <col min="15870" max="15870" width="8.83203125" style="5" customWidth="1"/>
+    <col min="15871" max="15871" width="10.5" style="5" customWidth="1"/>
+    <col min="15872" max="15872" width="22.1640625" style="5" customWidth="1"/>
     <col min="15873" max="15873" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="15874" max="15874" width="7.44140625" style="5" customWidth="1"/>
-    <col min="15875" max="15875" width="6.77734375" style="5" customWidth="1"/>
-    <col min="15876" max="15876" width="7.44140625" style="5" customWidth="1"/>
-    <col min="15877" max="15877" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="15874" max="15874" width="7.5" style="5" customWidth="1"/>
+    <col min="15875" max="15875" width="6.83203125" style="5" customWidth="1"/>
+    <col min="15876" max="15876" width="7.5" style="5" customWidth="1"/>
+    <col min="15877" max="15877" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="15878" max="15878" width="19.33203125" style="5" customWidth="1"/>
-    <col min="15879" max="16125" width="8.77734375" style="5"/>
-    <col min="16126" max="16126" width="8.77734375" style="5" customWidth="1"/>
-    <col min="16127" max="16127" width="10.44140625" style="5" customWidth="1"/>
-    <col min="16128" max="16128" width="22.109375" style="5" customWidth="1"/>
+    <col min="15879" max="16125" width="8.83203125" style="5"/>
+    <col min="16126" max="16126" width="8.83203125" style="5" customWidth="1"/>
+    <col min="16127" max="16127" width="10.5" style="5" customWidth="1"/>
+    <col min="16128" max="16128" width="22.1640625" style="5" customWidth="1"/>
     <col min="16129" max="16129" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="16130" max="16130" width="7.44140625" style="5" customWidth="1"/>
-    <col min="16131" max="16131" width="6.77734375" style="5" customWidth="1"/>
-    <col min="16132" max="16132" width="7.44140625" style="5" customWidth="1"/>
-    <col min="16133" max="16133" width="19.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="16130" max="16130" width="7.5" style="5" customWidth="1"/>
+    <col min="16131" max="16131" width="6.83203125" style="5" customWidth="1"/>
+    <col min="16132" max="16132" width="7.5" style="5" customWidth="1"/>
+    <col min="16133" max="16133" width="19.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="16134" max="16134" width="19.33203125" style="5" customWidth="1"/>
-    <col min="16135" max="16384" width="8.77734375" style="5"/>
+    <col min="16135" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" ht="26.25" customHeight="1" thickBot="1">
@@ -51732,7 +51389,7 @@
     <row r="19" spans="1:17">
       <c r="E19" s="21"/>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" ht="16">
       <c r="A20" s="33" t="s">
         <v>55</v>
       </c>
@@ -51815,7 +51472,7 @@
       <c r="K25" s="66"/>
       <c r="L25" s="66"/>
     </row>
-    <row r="26" spans="1:17" ht="27">
+    <row r="26" spans="1:17" ht="32">
       <c r="D26" s="59" t="s">
         <v>91</v>
       </c>
@@ -51838,7 +51495,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="27">
+    <row r="27" spans="1:17" ht="32">
       <c r="D27" s="59" t="s">
         <v>92</v>
       </c>
@@ -51861,7 +51518,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="27">
+    <row r="28" spans="1:17" ht="32">
       <c r="D28" s="59" t="s">
         <v>93</v>
       </c>
@@ -51882,7 +51539,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="27">
+    <row r="29" spans="1:17" ht="32">
       <c r="D29" s="59" t="s">
         <v>94</v>
       </c>
@@ -51903,7 +51560,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="27">
+    <row r="30" spans="1:17" ht="32">
       <c r="D30" s="65" t="s">
         <v>95</v>
       </c>
@@ -51924,7 +51581,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="27">
+    <row r="31" spans="1:17" ht="32">
       <c r="D31" s="59" t="s">
         <v>96</v>
       </c>
@@ -51963,7 +51620,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7692D35F-3925-4FF8-8A8F-D4AFF2A1384B}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
